--- a/workspaces/nasdaq_hourly_24hrs/ma/ma_ratio_50.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/ma/ma_ratio_50.xlsx
@@ -625,76 +625,76 @@
         <v>15</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.280849297238966</v>
+        <v>6.313940253120144</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.6730317862602035</v>
+        <v>-0.6395918377378464</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.520378336259007</v>
+        <v>4.555539847585351</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>17.06449441822819</v>
+        <v>17.10059265105738</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.07847734312664</v>
+        <v>10.14383515266485</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>16.89728321506408</v>
+        <v>16.96250739179469</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16.13348113114885</v>
+        <v>16.19962735355249</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>15.86107000979231</v>
+        <v>15.92757109199231</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.634581767848488</v>
+        <v>2.700995703106216</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.865240507230375</v>
+        <v>1.932585005466386</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-4.501092412480517</v>
+        <v>-4.434056943383752</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-4.780570409983468</v>
+        <v>-4.71317022361567</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-5.902263742836098</v>
+        <v>-5.833521848495913</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.12485603756523</v>
+        <v>-6.055813889011262</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-6.783294047419709</v>
+        <v>-6.713445790112878</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.4587402737027446</v>
+        <v>0.527962886786888</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-6.326970980165129</v>
+        <v>-6.257569277647391</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-6.433648146084991</v>
+        <v>-6.364080201795126</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-6.219634500466498</v>
+        <v>-6.150273776703706</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.6238168989420956</v>
+        <v>0.6930141746817853</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-6.579082173650562</v>
+        <v>-6.50921823806835</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.005642207670440769</v>
+        <v>0.07564437598959728</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>6.945071683168116</v>
+        <v>7.014797829722355</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.2046783625730981</v>
+        <v>0.2745327102803756</v>
       </c>
     </row>
     <row r="7">
@@ -707,158 +707,158 @@
         <v>29</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-15.63406231451098</v>
+        <v>-15.60116134110639</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.271397777378901</v>
+        <v>-2.237974137010902</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2767103578148564</v>
+        <v>-0.2415885779711999</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.867409686844127</v>
+        <v>5.903424662391267</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.934907275863068</v>
+        <v>9.000253723250253</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.12284608808848</v>
+        <v>9.188016123384955</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.356792594219236</v>
+        <v>8.422887465970582</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.082089450428029</v>
+        <v>8.148542118769072</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.126349171202463</v>
+        <v>8.19279026595521</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>14.22579849383325</v>
+        <v>14.2932041912909</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.06919634040241</v>
+        <v>11.136303475013</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>7.358847769419853</v>
+        <v>7.426298656431513</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>9.677580601588922</v>
+        <v>9.746382971155391</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.459737613399419</v>
+        <v>9.52883475147263</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>12.24485447814906</v>
+        <v>12.31476375746855</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>9.402274162599021</v>
+        <v>9.471521368078015</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>9.27188206404611</v>
+        <v>9.341322281304485</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>5.728020608254965</v>
+        <v>5.797613823946719</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>2.502738241470652</v>
+        <v>2.572113583808047</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>2.690230188632711</v>
+        <v>2.759429443033476</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>2.148594044325492</v>
+        <v>2.218466744660837</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-1.3728249239484</v>
+        <v>-1.302824375520395</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-1.098467128675289</v>
+        <v>-1.028744227792707</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-1.174631982254496</v>
+        <v>-1.10477763454643</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.03451</t>
+          <t>X ≈ -0.0345</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>28</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.990061573549355</v>
+        <v>7.023151383723324</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10.20546591492164</v>
+        <v>10.23898922881294</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>19.42283570884899</v>
+        <v>19.45811071346846</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.069841448877177</v>
+        <v>8.105870888245505</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.159078552763404</v>
+        <v>4.224385933472675</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>18.55213006359369</v>
+        <v>18.61736051641967</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>21.34183498063705</v>
+        <v>21.40800969248702</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>10.40970881101539</v>
+        <v>10.47617163660216</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10.45473378371044</v>
+        <v>10.52118440057036</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.687694214338087</v>
+        <v>9.755073212190936</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>6.407338181423569</v>
+        <v>6.474419367204185</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>13.24779413984065</v>
+        <v>13.31526873781361</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.572367801278268</v>
+        <v>8.641162802179061</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.354245601456235</v>
+        <v>8.423336008461447</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>11.26175750624143</v>
+        <v>11.33166141186911</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>11.85881980776339</v>
+        <v>11.92807248064696</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>11.72925153150409</v>
+        <v>11.7986964907202</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>11.62819895915206</v>
+        <v>11.69780384643988</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>11.84780877334253</v>
+        <v>11.91720021295441</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>12.03819735579502</v>
+        <v>12.10740952059979</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>11.49947930989938</v>
+        <v>11.56936165788215</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>11.42714493077737</v>
+        <v>11.49715446071408</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>8.135132201733093</v>
+        <v>8.204858236399474</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>8.061821219715959</v>
+        <v>8.131675567422427</v>
       </c>
     </row>
     <row r="9">
@@ -871,158 +871,158 @@
         <v>36</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>10.14097846845848</v>
+        <v>10.17409401986665</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.22518314808061</v>
+        <v>-1.191758788009302</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-5.416468607700622</v>
+        <v>-5.381394803564568</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.367562719012476</v>
+        <v>-3.331624190843804</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.731052201619626</v>
+        <v>-3.665809740201766</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.547728741344351</v>
+        <v>-3.482655291715091</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.317606958160169</v>
+        <v>-4.251603497905982</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-12.88742570848082</v>
+        <v>-12.82111208689307</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-12.84958845055931</v>
+        <v>-12.7832778065819</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-13.62375466012561</v>
+        <v>-13.55650663423818</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-16.12060929459655</v>
+        <v>-16.0536464460872</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-10.86900528032903</v>
+        <v>-10.80164615028099</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.848865033380243</v>
+        <v>1.917627870978436</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.909511920780339</v>
+        <v>-3.840472411007134</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-4.567323708444597</v>
+        <v>-4.497477818113389</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-9.516843029493103</v>
+        <v>-9.447659145983074</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-6.881291391974436</v>
+        <v>-6.811899136882182</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-12.53322149288788</v>
+        <v>-12.46367482079778</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-9.547654889563262</v>
+        <v>-9.478306559301984</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-12.13819203305964</v>
+        <v>-12.06901868594593</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-12.6843802222169</v>
+        <v>-12.6145270535576</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-12.76420666772324</v>
+        <v>-12.6942166024288</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-12.4933846228715</v>
+        <v>-12.4236669775057</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-12.57309941520531</v>
+        <v>-12.5032450674974</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.02872</t>
+          <t>X ≈ -0.02871</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>55</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-13.57632343209353</v>
+        <v>-13.54342916056335</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-10.30281244236948</v>
+        <v>-10.26947581647264</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-15.34909748505385</v>
+        <v>-15.31411689446194</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-12.45061728728992</v>
+        <v>-12.41475987812306</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-20.04591578649084</v>
+        <v>-19.98081126153997</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-14.44441363122066</v>
+        <v>-14.37943131038118</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-17.02604848208426</v>
+        <v>-16.96014394837066</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-13.68966687020067</v>
+        <v>-13.62337278245678</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-8.223577404778965</v>
+        <v>-8.15725226145198</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-8.996286446193217</v>
+        <v>-8.929025253532586</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.91447380750752</v>
+        <v>-6.847475461789976</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-5.383811876014882</v>
+        <v>-5.316436570368978</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.070443999594197</v>
+        <v>-1.00170066412327</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-6.728522817032918</v>
+        <v>-6.659501949058118</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-3.761226736369451</v>
+        <v>-3.691384682134668</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-6.795858015468156</v>
+        <v>-6.726672186434342</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-6.931275964797571</v>
+        <v>-6.86188948734474</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-5.223298635259368</v>
+        <v>-5.153739842676714</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-8.639592935669356</v>
+        <v>-8.570247113960292</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-10.27146045848977</v>
+        <v>-10.20228777873785</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-14.45003394023308</v>
+        <v>-14.380185756132</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-12.71350998507485</v>
+        <v>-12.64352177315323</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-14.2603892921727</v>
+        <v>-14.19067330069758</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-17.97713981924467</v>
+        <v>-17.90728547153781</v>
       </c>
     </row>
     <row r="11">
@@ -1035,76 +1035,76 @@
         <v>57</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.517544485494383</v>
+        <v>-4.484581548383886</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.115109038385576</v>
+        <v>2.148544277396546</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5.913211256116291</v>
+        <v>5.948360099868154</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.204748213076812</v>
+        <v>5.240737405964715</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.844864216093825</v>
+        <v>4.910140246862696</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.541651762467744</v>
+        <v>1.606732899062713</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.7737249367576666</v>
+        <v>0.8397342551833162</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.988142907375554</v>
+        <v>4.054536231679542</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.952846521957554</v>
+        <v>-2.886503776276939</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.2309024332768317</v>
+        <v>-0.1636048314145881</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.789825315989532</v>
+        <v>1.856857913390606</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.259446204954308</v>
+        <v>3.326853390716025</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.887999174866309</v>
+        <v>3.956755994040243</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.669079201828964</v>
+        <v>3.738133416237481</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-5.732805314365734</v>
+        <v>-5.662979233682506</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-8.640571193547871</v>
+        <v>-8.571399792887433</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-7.026222508551029</v>
+        <v>-6.95684362007124</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-8.884093732574208</v>
+        <v>-8.814550149068111</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-6.919409342241764</v>
+        <v>-6.850065412896264</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-8.487032908082206</v>
+        <v>-8.417861800994316</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-5.526802656439699</v>
+        <v>-5.456947078256157</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-5.604596376677286</v>
+        <v>-5.534604650443995</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-3.577887340232614</v>
+        <v>-3.508168131262067</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.900584795321635</v>
+        <v>-1.830730447614357</v>
       </c>
     </row>
     <row r="12">
@@ -1117,76 +1117,76 @@
         <v>71</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.1511320922417312</v>
+        <v>-0.8694875261508486</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.680508810073448</v>
+        <v>-4.647148050335915</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.5176385671329058</v>
+        <v>-0.4825551300874267</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.627157710559416</v>
+        <v>-2.591243643986004</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-7.188263445726228</v>
+        <v>-7.123102486370605</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-11.20699342275925</v>
+        <v>-11.14202864746451</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.575645004894582</v>
+        <v>-3.509683807257424</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.853562811927091</v>
+        <v>-3.787237585216388</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.411420813632766</v>
+        <v>-2.34509053789008</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.584320141719864</v>
+        <v>-4.517063073755253</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.312217245945561</v>
+        <v>-4.245231340764271</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.189416779544253</v>
+        <v>-3.122053860219431</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.907730371181614</v>
+        <v>-2.839015736319048</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.532585928406284</v>
+        <v>-4.463576413738068</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-2.381651177214742</v>
+        <v>-2.311822872131458</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-4.598017634991734</v>
+        <v>-4.528842605192857</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-6.138085072175073</v>
+        <v>-6.068712385662622</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.43339914904837</v>
+        <v>-3.363849282897725</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.9997158562158219</v>
+        <v>1.069070788754587</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>5.406513442939996</v>
+        <v>5.475703665675852</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>3.458795200432988</v>
+        <v>3.528658894598365</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>6.198936878684357</v>
+        <v>6.268936500567385</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>9.29162207876508</v>
+        <v>9.361345782962786</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>9.218762869615027</v>
+        <v>9.288617217322631</v>
       </c>
     </row>
     <row r="13">
@@ -1199,76 +1199,76 @@
         <v>83</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-6.082785144752364</v>
+        <v>-6.696889298328827</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-8.165240999068828</v>
+        <v>-8.231149700166675</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-9.598880223184281</v>
+        <v>-9.030385220457198</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.132026196885008</v>
+        <v>-2.56712144193159</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.099533463981118</v>
+        <v>-1.710156955125356</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.113096877103281</v>
+        <v>-2.048087479615162</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-5.278764587829222</v>
+        <v>-5.212840496798272</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-5.557227402147426</v>
+        <v>-5.49093746770567</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.51734790113273</v>
+        <v>-5.451059553538755</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.089972878754395</v>
+        <v>-5.022739745230638</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.017655433889438</v>
+        <v>-5.950698818229085</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.698772083570788</v>
+        <v>-2.631423284038945</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.619907396040603</v>
+        <v>-2.551206805596181</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.7614124550852353</v>
+        <v>0.8304315502154935</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.296749120025723</v>
+        <v>-2.226933333126922</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.703571055442296</v>
+        <v>-1.634397502586111</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.6354832903334895</v>
+        <v>-0.5661040171692093</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>1.664267696872265</v>
+        <v>1.733822789648563</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.880529889315277</v>
+        <v>1.949880410182473</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>4.474096538358992</v>
+        <v>4.543280711557827</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>7.544035985420315</v>
+        <v>7.613901790407716</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>8.674547079638479</v>
+        <v>8.744546879901399</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>5.338965974317297</v>
+        <v>5.408686928137755</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>8.879377157754369</v>
+        <v>8.949231505461093</v>
       </c>
     </row>
     <row r="14">
@@ -1281,76 +1281,76 @@
         <v>98</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.618599872272753</v>
+        <v>-1.668021226359876</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.98956506817688</v>
+        <v>-6.061517573744617</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-8.447495407314619</v>
+        <v>-9.544981352716924</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.082006642824403</v>
+        <v>-3.613860524589825</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.430219446691233</v>
+        <v>-2.365778104591634</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.232821570187838</v>
+        <v>-1.16783481905081</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.055414004087694</v>
+        <v>2.121367675436225</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>7.867574253086715</v>
+        <v>7.933939868008849</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.882006657530326</v>
+        <v>5.948350874863173</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>9.175815711939869</v>
+        <v>9.243120898953691</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>9.452638037751782</v>
+        <v>9.519668642302882</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.096206452240601</v>
+        <v>4.163574435577878</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.960754188563627</v>
+        <v>2.029460074877875</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2924324266687393</v>
+        <v>-0.2234346515851087</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>5.154747494985777</v>
+        <v>5.224580128727261</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>4.732897502900933</v>
+        <v>4.80208230575478</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>7.65491133589066</v>
+        <v>7.724307209635285</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>7.552729293953377</v>
+        <v>7.62229225338929</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>6.752467549772597</v>
+        <v>6.821822203491699</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>4.903378194732639</v>
+        <v>4.972557531110482</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>7.420737238922349</v>
+        <v>7.490599032014082</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>6.327653522524251</v>
+        <v>6.397648596248125</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>6.604687392202017</v>
+        <v>6.674407596094838</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>5.510800811552464</v>
+        <v>5.580655159259969</v>
       </c>
     </row>
     <row r="15">
@@ -1363,76 +1363,76 @@
         <v>98</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.177845082392658</v>
+        <v>-3.149718309999983</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.513897218278515</v>
+        <v>-3.485886014052355</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.708496063264121</v>
+        <v>3.183545184219824</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.984361401407774</v>
+        <v>1.455786364483075</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.637750899994423</v>
+        <v>2.131601609114583</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>6.877460743274341</v>
+        <v>6.377091543536402</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.096681286907604</v>
+        <v>5.162632745615383</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.820870755762648</v>
+        <v>4.887188955930199</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.850012188311936</v>
+        <v>3.916317790412933</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.096460409118379</v>
+        <v>4.163709746734213</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.371608810750459</v>
+        <v>4.438587765240598</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.110774254863259</v>
+        <v>5.178129133204834</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>6.025319343066279</v>
+        <v>6.094029086070073</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.790944770755694</v>
+        <v>4.859949723737401</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>5.153516236419698</v>
+        <v>5.223334006364915</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>10.83649567220461</v>
+        <v>10.90569308722286</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>10.70696722157248</v>
+        <v>10.77636406334081</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>11.6242728157888</v>
+        <v>11.69383982755977</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.714517660543102</v>
+        <v>4.783859146732944</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>6.940686615110295</v>
+        <v>7.00986370230936</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>5.381585469398878</v>
+        <v>5.451439479796655</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>6.327315153779914</v>
+        <v>6.39730709776871</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>6.604510825746736</v>
+        <v>6.674229493825266</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>5.510800811552691</v>
+        <v>5.580655159259969</v>
       </c>
     </row>
     <row r="16">
@@ -1445,76 +1445,76 @@
         <v>111</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.274353810468</v>
+        <v>1.308862338736773</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.739164955842789</v>
+        <v>-1.708897606714899</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4886933311236064</v>
+        <v>-0.4543577833412016</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.095017691398184</v>
+        <v>-2.061016707082793</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.456378324967645</v>
+        <v>-2.39283675694373</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4095710143631734</v>
+        <v>0.4750105877750883</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.149029809427049</v>
+        <v>-2.083180133335091</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.322806357765373</v>
+        <v>-3.25659255993753</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.281512655627381</v>
+        <v>-3.215297702460802</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.260536146401471</v>
+        <v>-2.193365189948146</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.88419390401129</v>
+        <v>-2.817294219583722</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.060509580413189</v>
+        <v>-3.993240349489611</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-7.873290812996736</v>
+        <v>-7.804689274277777</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.878952323493003</v>
+        <v>0.9479153469262229</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>2.916663678597004</v>
+        <v>2.986452337077417</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>2.612988584331688</v>
+        <v>2.682136330424207</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.277699370341381</v>
+        <v>4.347059828536615</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>4.174629631643057</v>
+        <v>4.244162376466456</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>6.191023956438961</v>
+        <v>6.260359800228649</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>4.580855637504811</v>
+        <v>4.650020196580371</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>4.040456368079852</v>
+        <v>4.110302244874759</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>1.26550350096425</v>
+        <v>1.335485905731929</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.2601526190362264</v>
+        <v>-0.1904397327963281</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.3358621779674422</v>
+        <v>-0.2660078302603708</v>
       </c>
     </row>
     <row r="17">
@@ -1527,76 +1527,76 @@
         <v>138</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6716705517645281</v>
+        <v>0.7053322973103135</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.059181333086457</v>
+        <v>1.093613487344385</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.221176456259599</v>
+        <v>3.261383895770209</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.521077695858082</v>
+        <v>-2.487812597024153</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.151739584558982</v>
+        <v>2.218801880189503</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1756181917864836</v>
+        <v>0.2409591885906934</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.031346313227743</v>
+        <v>-1.965550828800509</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.1493750248229517</v>
+        <v>-0.08318290286185714</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.054030747332163</v>
+        <v>2.120245863143111</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.5641663386873574</v>
+        <v>0.6313161295560832</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.559003024605353</v>
+        <v>1.625895623923746</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.882057388321499</v>
+        <v>-0.8148059785631148</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.327317982368562</v>
+        <v>2.39594742093432</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.6637653586770753</v>
+        <v>0.7326965851745086</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.7298611231234418</v>
+        <v>0.7996113992391471</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.8434005246015346</v>
+        <v>-0.7742934521927864</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.913290029423415</v>
+        <v>1.982621051820033</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.809462096480885</v>
+        <v>1.878969562424359</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>7.81202678184102</v>
+        <v>7.881355468383923</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>5.831456336951973</v>
+        <v>5.900613660496418</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>8.18689465677253</v>
+        <v>8.256740358414142</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>5.218290329366944</v>
+        <v>5.288271773670964</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>5.495438925992993</v>
+        <v>5.565152334418514</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>5.422069666920756</v>
+        <v>5.491924014628204</v>
       </c>
     </row>
     <row r="18">
@@ -1609,486 +1609,486 @@
         <v>158</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.637509499609777</v>
+        <v>-3.611208903699016</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-8.359137255796504</v>
+        <v>-8.34080508745641</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-7.281628929059224</v>
+        <v>-7.258865483035777</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.600977677326824</v>
+        <v>-3.569482132163131</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.708758405925884</v>
+        <v>-2.645727007883295</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.900341085800342</v>
+        <v>-1.835927701748979</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.667514330751807</v>
+        <v>-2.601804167059591</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.060805551046663</v>
+        <v>-0.9946919013412412</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.382698988269794</v>
+        <v>3.448870066303904</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.614793590253129</v>
+        <v>2.681905782329366</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.257598261859151</v>
+        <v>-0.1907754174293714</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.794493784090683</v>
+        <v>-1.727303646043701</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.544570627663688</v>
+        <v>-3.476032676395889</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.245860517716345</v>
+        <v>-1.176985905912076</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-3.79379358798019</v>
+        <v>-3.724111991838981</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-2.571080504938571</v>
+        <v>-2.502019791017567</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-3.336982081755991</v>
+        <v>-3.267706616833031</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.9177828509603003</v>
+        <v>-0.8483119345608259</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.5606991416330942</v>
+        <v>0.629985654792641</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.1161728849134462</v>
+        <v>0.1852998893946491</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.4256486577481766</v>
+        <v>-0.3558311702393055</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.660696656561669</v>
+        <v>2.730667250327436</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>2.937048064382907</v>
+        <v>3.006756102178926</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.86290621067451</v>
+        <v>2.932760558381787</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.002692</t>
+          <t>X ≈ -0.002693</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>165</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.331975984242405</v>
+        <v>-3.306152190681146</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.258449251011427</v>
+        <v>-1.229266707562118</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.291725055201333</v>
+        <v>-6.26901124836558</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-5.204185625432672</v>
+        <v>-5.175625240824921</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-6.770283775859809</v>
+        <v>-6.711437616579047</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-8.997358276979035</v>
+        <v>-8.936465668380919</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-9.766945761902036</v>
+        <v>-9.701443267238574</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-10.05027604571799</v>
+        <v>-9.984377179204039</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-11.82060486739787</v>
+        <v>-11.75469960420938</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-10.78814107030946</v>
+        <v>-10.72125894723403</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-9.91598236253359</v>
+        <v>-9.849340295307378</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-9.59458406966742</v>
+        <v>-9.527546440631895</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-7.702500462029327</v>
+        <v>-7.634073617626576</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-10.3404885501852</v>
+        <v>-10.27175166676689</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-8.586116848342179</v>
+        <v>-8.516532180017009</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-6.185497533446814</v>
+        <v>-6.116512470245489</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-5.113826474195051</v>
+        <v>-5.044607276552263</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-4.012430429826885</v>
+        <v>-3.943011131324432</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-6.217440783427371</v>
+        <v>-6.148210975596889</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-5.428214799222644</v>
+        <v>-5.35912917024676</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-7.788053866352705</v>
+        <v>-7.718272677035834</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-6.656079767942025</v>
+        <v>-6.586135356333301</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-6.989582486009027</v>
+        <v>-6.919887985419521</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-5.249867091972497</v>
+        <v>-5.180012744265085</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.0002</t>
+          <t>X ≈ 0.000199</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>208</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.992321857825445</v>
+        <v>3.029675684838381</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.228812219207121</v>
+        <v>1.262231374215411</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.163033899570308</v>
+        <v>-1.132230069926365</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.939712098753439</v>
+        <v>-5.185324796132001</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-4.554123315784359</v>
+        <v>-5.044890151516903</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.51780527716118</v>
+        <v>-1.993830946450764</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.712836637564664</v>
+        <v>-4.198979430719419</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.470859410793338</v>
+        <v>-4.680728444335458</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.524409058816978</v>
+        <v>-2.458539803852418</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.9079765633498837</v>
+        <v>-0.8411162150013212</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.32076759791547</v>
+        <v>0.3873969092523097</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.911707516794074</v>
+        <v>-0.8447008606875741</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.509217529054098</v>
+        <v>-2.440853945061967</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.73122105513427</v>
+        <v>-2.662524583555566</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-2.431045071415319</v>
+        <v>-2.36150679243886</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.8828365754807024</v>
+        <v>-0.8138925848990652</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.933670748977342</v>
+        <v>-2.864507561001332</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-3.999257277504029</v>
+        <v>-3.929896718403626</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-3.78561683934052</v>
+        <v>-3.716426360892001</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-2.641136166339976</v>
+        <v>-2.572079197050684</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-2.703831022869906</v>
+        <v>-2.634066957119906</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-3.261214699283386</v>
+        <v>-3.191284327029649</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-4.909745588762775</v>
+        <v>-4.84005956782012</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-7.872244714349875</v>
+        <v>-7.802390366642697</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.003092</t>
+          <t>X ≈ 0.00309</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>297</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.812060768061741</v>
+        <v>1.847807783880071</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.140251778343071</v>
+        <v>2.175795065094206</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.97485571064253</v>
+        <v>-1.947400514589653</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.02166376820357385</v>
+        <v>0.01172534943790282</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.0583513190006</v>
+        <v>-3.003037978781201</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.012047043790012</v>
+        <v>-4.146425032352731</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.923516906644075</v>
+        <v>-2.250774264703722</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.677319377181099</v>
+        <v>-4.201060447209855</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.974087637104603</v>
+        <v>-4.491299953687275</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-5.41639582429741</v>
+        <v>-5.742854039667208</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.145883318398425</v>
+        <v>-5.275145154711424</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.091989209055072</v>
+        <v>-5.024785873383088</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.881918736230574</v>
+        <v>-5.81332606673336</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.771786147512572</v>
+        <v>-5.702832616757327</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-6.098171435345435</v>
+        <v>-6.028355252277834</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-6.178288733391213</v>
+        <v>-6.109058330724658</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-6.315926078701331</v>
+        <v>-6.246439394949832</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-6.22212902770444</v>
+        <v>-6.354798587082165</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-5.003521325862643</v>
+        <v>-5.134353563588746</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-6.499688655677147</v>
+        <v>-6.629875993353743</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-5.36423207658747</v>
+        <v>-5.496149398924025</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-5.779526069301767</v>
+        <v>-5.709639657955996</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-8.199707350734791</v>
+        <v>-8.130045551757966</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-7.943469785575054</v>
+        <v>-7.873615437867777</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.005984</t>
+          <t>X ≈ 0.005982</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-5.100656492056906</v>
+        <v>-5.269938721891442</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.04970671494371004</v>
+        <v>-0.186122760594543</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.104479154407002</v>
+        <v>1.98713276067059</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.467885123081025</v>
+        <v>2.357906503591167</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.6690561597598332</v>
+        <v>0.5761785856576864</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.376537014631523</v>
+        <v>-2.487624045805561</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.4420344207360145</v>
+        <v>0.3525768318288911</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.707505054032659</v>
+        <v>-2.816127938598825</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.534499229455442</v>
+        <v>-3.85818431036769</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.512062561332669</v>
+        <v>-2.825163362151578</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.600443522724255</v>
+        <v>-2.912208150934319</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.880204635231379</v>
+        <v>-3.191325971741811</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.923943271355924</v>
+        <v>-3.013329472334327</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.589064493199032</v>
+        <v>-4.683445124328642</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-4.890576330185006</v>
+        <v>-4.621068398078727</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-5.38297670241743</v>
+        <v>-5.117797334592332</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-4.077515672420901</v>
+        <v>-3.806632658764968</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-3.099466597541408</v>
+        <v>-2.826856149199394</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-5.556040713661623</v>
+        <v>-5.515227724930149</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-6.818937600111397</v>
+        <v>-6.78427176926936</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-7.004036033783009</v>
+        <v>-7.333733137167265</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-7.447192007194325</v>
+        <v>-7.409053423616825</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-6.091320899045407</v>
+        <v>-5.826845343748751</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-5.447495550470386</v>
+        <v>-5.180012744265085</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.008875</t>
+          <t>X ≈ 0.008874</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.167855865336321</v>
+        <v>1.405928256264133</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.374588039634439</v>
+        <v>-2.132551063894788</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.971243915701159</v>
+        <v>-1.73580001291095</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.3938429734143938</v>
+        <v>-0.1602810394699006</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.831750666775342</v>
+        <v>4.084227506545005</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.182327769289294</v>
+        <v>2.43897828428058</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.03716648801984235</v>
+        <v>0.294903814029837</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.6799323528382075</v>
+        <v>0.933997585169891</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.094550701767275</v>
+        <v>2.347929889901714</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.2218922734679083</v>
+        <v>0.2028884275047815</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.258228554010635</v>
+        <v>-2.269698526478741</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.158286508592298</v>
+        <v>-1.174086788369948</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.356324852863402</v>
+        <v>-1.378985629962905</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.957327071757582</v>
+        <v>-2.690011974504671</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.5259840926667252</v>
+        <v>0.3168490485964384</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.2677439102954935</v>
+        <v>-0.4712126297653256</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.404270792059549</v>
+        <v>-0.6075976064987927</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.433381542277999</v>
+        <v>-1.634482650540754</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.601133228925057</v>
+        <v>-2.800337325768218</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.878845866216238</v>
+        <v>-3.076975420677108</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.500187623476286</v>
+        <v>-2.241268191114941</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-4.428519033154821</v>
+        <v>-4.619475734942952</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-4.621120897207369</v>
+        <v>-4.805251148816666</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-4.239766081871345</v>
+        <v>-4.425928119212706</v>
       </c>
     </row>
     <row r="24">
@@ -2101,240 +2101,240 @@
         <v>248</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.526801888390963</v>
+        <v>1.558651344071301</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.193545904186756</v>
+        <v>1.222831837827997</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.753240788011986</v>
+        <v>1.785141241783499</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.038247768293751</v>
+        <v>1.072838914774124</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.872231285928422</v>
+        <v>1.937454055597442</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.25481014071358</v>
+        <v>3.326911270852214</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.4897468998989325</v>
+        <v>0.5507239793750003</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5841509647716023</v>
+        <v>-0.5300170747274393</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.139799753288926</v>
+        <v>-2.090069972371438</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.905832272818884</v>
+        <v>-4.867224255994749</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.044400156120723</v>
+        <v>-0.98803761912081</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.471324100054147</v>
+        <v>1.536853070687201</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.146279450389635</v>
+        <v>3.215897373733604</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.529597613694484</v>
+        <v>6.599293799565672</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.467345453056978</v>
+        <v>3.537986263621733</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.46072135031104</v>
+        <v>2.530895630719868</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.9698166723008583</v>
+        <v>0.7900557294599722</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.667636085729875</v>
+        <v>1.4906745491839</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.6793412963474807</v>
+        <v>0.4976750221770132</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.09087590539683532</v>
+        <v>-0.5271127119660974</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.5715876939463911</v>
+        <v>0.384841430565892</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.3105399845982006</v>
+        <v>-0.4981460082570948</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.767145613932307</v>
+        <v>0.5814005881070514</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.2853235238634255</v>
+        <v>0.355177871570703</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.01466</t>
+          <t>X ≈ 0.01465</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-4.243195120754606</v>
+        <v>-4.206588370985294</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3168469801180223</v>
+        <v>-0.2816722369044626</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.260568570823331</v>
+        <v>-2.222509808447327</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.490217937181605</v>
+        <v>-2.4518716966409</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-4.295270448302162</v>
+        <v>-4.226203586677414</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.518976299887548</v>
+        <v>-5.449813158050709</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6158342793804579</v>
+        <v>-0.5479974445375078</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.03414460920224371</v>
+        <v>0.1025225906821845</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.8691360069726244</v>
+        <v>-0.8004523911362398</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.7072746790155904</v>
+        <v>0.7764262927776713</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.939776788341646</v>
+        <v>2.010678782433125</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.759524814245893</v>
+        <v>5.534247986433911</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.964371095722562</v>
+        <v>3.445649510830819</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.315843440906761</v>
+        <v>1.801759900655469</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.9941209035701277</v>
+        <v>0.1755264239196634</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.36558555171014</v>
+        <v>1.553346693491335</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.8020330577475363</v>
+        <v>0.2844241375769982</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.2554345583260513</v>
+        <v>-0.7692956327247273</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.03948719535730305</v>
+        <v>-0.2629475875775995</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.576722400138294</v>
+        <v>1.646663332777656</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>1.98484351049062</v>
+        <v>2.056498117192575</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.86153141765071</v>
+        <v>2.933033108164452</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>5.350278611344926</v>
+        <v>5.112269725408325</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>5.27644869750133</v>
+        <v>5.036437472185106</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.01756</t>
+          <t>X ≈ 0.01754</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>187</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.251708685646925</v>
+        <v>1.89451309806833</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.3855291452860641</v>
+        <v>0.4917197161698894</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.101834681889855</v>
+        <v>2.236720555380252</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.331715734374306</v>
+        <v>-2.74529553219935</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.475394019623792</v>
+        <v>0.6457060399569272</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.142470299135617</v>
+        <v>0.3054235329100194</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1021207302572833</v>
+        <v>0.0652299412506494</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.1257683424422282</v>
+        <v>0.3067565244973451</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.237479228064089</v>
+        <v>1.419264556018497</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.9728164585680759</v>
+        <v>1.167589041010665</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.073288070810243</v>
+        <v>-1.220131044040052</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.001225898641671</v>
+        <v>-4.15765590864288</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.012588223494426</v>
+        <v>-3.693063363950621</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.307174603660897</v>
+        <v>-2.312868431588718</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.978437213372686</v>
+        <v>-2.648528486508937</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-1.372278930144255</v>
+        <v>-2.047372458764869</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.512538309630365</v>
+        <v>-2.185050210076298</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.077623091616587</v>
+        <v>-1.419684757019688</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-1.932665237430832</v>
+        <v>-2.273312092672874</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.813087339354226</v>
+        <v>-3.155984999282381</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-3.557997377957065</v>
+        <v>-4.233290525537186</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.695540288242249</v>
+        <v>-2.704858412080014</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-2.488773218681452</v>
+        <v>-3.499902416175459</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-2.04131094223974</v>
+        <v>-3.040975311109975</v>
       </c>
     </row>
     <row r="27">
@@ -2344,79 +2344,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.008265944582789</v>
+        <v>-0.3698190760487918</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.482614239462279</v>
+        <v>3.968301321863073</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.070424971793294</v>
+        <v>1.595702833579701</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.354803672127225</v>
+        <v>1.817328253389398</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.9243679500232247</v>
+        <v>-1.322200536914941</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.079632418399015</v>
+        <v>2.603083406191843</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>1.352557347491064</v>
+        <v>0.8965552830491532</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.962312728478338</v>
+        <v>2.487502716800691</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.104550848157793</v>
+        <v>0.6598310202107243</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.316091545605147</v>
+        <v>-0.1130846558257659</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.453077629282127</v>
+        <v>2.964713304093166</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.183123658171603</v>
+        <v>2.68596390064517</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>5.855360343897964</v>
+        <v>6.235699030050732</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.683450566955621</v>
+        <v>5.08004071435181</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>4.958620415570344</v>
+        <v>6.291056295275929</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>4.61775139106674</v>
+        <v>5.016284338714243</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>6.379279669315224</v>
+        <v>6.751526080241504</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>4.380502267295498</v>
+        <v>4.777526497915588</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>3.635104545481816</v>
+        <v>4.058838439587532</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>2.866111415775528</v>
+        <v>3.311104810303263</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.267980013266893</v>
+        <v>3.703138081589572</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.28909103933529</v>
+        <v>1.758133241675857</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.293276651325442</v>
+        <v>-0.7711303635991555</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-2.65246449456982</v>
+        <v>-2.716121495327108</v>
       </c>
     </row>
     <row r="28">
@@ -2426,79 +2426,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.663906763263292</v>
+        <v>3.303597331012476</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.713522272507795</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.29748148875818</v>
+        <v>2.919690372520563</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.217490992466431</v>
+        <v>7.762291908633372</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.62686909476632</v>
+        <v>3.259834769419435</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.819769109128302</v>
+        <v>-2.108754600038743</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.592635241182244</v>
+        <v>-2.880703283929094</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.054288478250221</v>
+        <v>-0.3811369509044269</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.012772413227587</v>
+        <v>-0.3396497689897231</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.786607823996974</v>
+        <v>-1.112565445026178</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-7.146051373783095</v>
+        <v>-6.394061358419769</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.608243868807165</v>
+        <v>-3.89503298409003</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.507382974618331</v>
+        <v>-0.8515283842794759</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-7.362542602554136</v>
+        <v>-6.628162816281666</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.837681087986027</v>
+        <v>1.04702721947119</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.3841602708432603</v>
+        <v>0.2525252525252526</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>3.70709814768388</v>
+        <v>4.285274782214444</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.6021147315886</v>
+        <v>4.180434078393262</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>6.635139302971034</v>
+        <v>7.174103237095444</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>11.04753521126753</v>
+        <v>11.52761571373007</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>13.32123621072031</v>
+        <v>13.76284732354177</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>11.83683045085248</v>
+        <v>12.29811247324374</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>10.70315491310929</v>
+        <v>11.18369829683702</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>10.62721357384083</v>
+        <v>11.10786604361375</v>
       </c>
     </row>
     <row r="29">
@@ -2511,76 +2511,76 @@
         <v>57</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.466229471442183</v>
+        <v>2.499503763761012</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.639825886622418</v>
+        <v>5.67349889523576</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.954511387448569</v>
+        <v>5.989865811117056</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.995104039167686</v>
+        <v>7.031297756586589</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.629834254143695</v>
+        <v>6.695507284039373</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>8.571384832062705</v>
+        <v>8.636859435048976</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.798518700008621</v>
+        <v>7.864910751158568</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.274350019402448</v>
+        <v>9.34108527131788</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.315866084425124</v>
+        <v>9.382572453232626</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>12.05080260348016</v>
+        <v>12.1184287070206</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.81638994077089</v>
+        <v>8.883716419357917</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.274138142559202</v>
+        <v>3.341809121173135</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3952609591598275</v>
+        <v>0.4642610894047863</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.334867781699089</v>
+        <v>-3.265589716866366</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-3.993799020736446</v>
+        <v>-3.923733014446981</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-6.90751090093957</v>
+        <v>-6.838118022328494</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-7.041604595088494</v>
+        <v>-6.972035159305968</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-5.392202046271542</v>
+        <v>-5.322489898214918</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.08707901139716512</v>
+        <v>0.1565593774462997</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-3.234649122807021</v>
+        <v>-3.165366742410292</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-2.023463566892644</v>
+        <v>-1.953526945463992</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.3450326576230225</v>
+        <v>-0.2749869419608615</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-1.824643456053167</v>
+        <v>-1.754898194391082</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.900584795321635</v>
+        <v>-1.830730447614357</v>
       </c>
     </row>
     <row r="30">
@@ -2593,322 +2593,322 @@
         <v>57</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>9.483773331091307</v>
+        <v>9.517047623410136</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.394211851534706</v>
+        <v>7.427884860148048</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.6913534927117198</v>
+        <v>0.7267079163802066</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.531211750306042</v>
+        <v>-3.495018032887138</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.121062324319034</v>
+        <v>3.186735354214711</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.30822693732582</v>
+        <v>3.373701540312091</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.7809748403596615</v>
+        <v>0.8473668915096084</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-3.006351734983561</v>
+        <v>-2.939616483068129</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.543936259863635</v>
+        <v>0.6106426286711368</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.278872778918711</v>
+        <v>3.346498882459152</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.798846081121873</v>
+        <v>1.8661725597089</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.989019752177647</v>
+        <v>-1.921348773563714</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.11351097066489</v>
+        <v>-3.044510840419932</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.334867781699145</v>
+        <v>-3.265589716866423</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-2.239413055824215</v>
+        <v>-2.16934704953475</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-1.644353006202834</v>
+        <v>-1.574960127591758</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.730325229472861</v>
+        <v>1.799894665255387</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-5.392202046271599</v>
+        <v>-5.322489898214975</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-1.667306953515222</v>
+        <v>-1.597826587466088</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-4.989035087719294</v>
+        <v>-4.919752707322566</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-7.286621461629579</v>
+        <v>-7.216684840200926</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-3.853804587447584</v>
+        <v>-3.783758871785423</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.07025749114093571</v>
+        <v>-0.0005122294788506565</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>1.60818713450287</v>
+        <v>1.678041482210148</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.03202</t>
+          <t>X ≈ 0.032</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>57</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7.729387366179033</v>
+        <v>7.762661658497862</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>9.148597816446959</v>
+        <v>9.1822708250603</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>9.463283317273124</v>
+        <v>9.498637740941611</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.995104039167742</v>
+        <v>7.031297756586646</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.366676359406782</v>
+        <v>1.432349389302459</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.954930957410895</v>
+        <v>-1.889456354424624</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.7809748403595052</v>
+        <v>0.8473668915094521</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.256806159753275</v>
+        <v>2.323541411668707</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.298322224775845</v>
+        <v>2.365028593583347</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.524486814006536</v>
+        <v>1.592112917546977</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.04446011620948553</v>
+        <v>0.1117865947965129</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-3.743405717089921</v>
+        <v>-3.675734738475988</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.35912500575246</v>
+        <v>-1.290124875507502</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.928290113037725</v>
+        <v>1.997568177870448</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4.778130803824958</v>
+        <v>4.848196810114423</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>3.618804888534058</v>
+        <v>3.688197767145134</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-1.778446700351758</v>
+        <v>-1.708877264569232</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-3.637816081359212</v>
+        <v>-3.568103933302588</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.08707901139710827</v>
+        <v>0.1565593774462428</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.782894736842103</v>
+        <v>3.852177117238831</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>8.502852222581033</v>
+        <v>8.572788844009686</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>3.163739272201539</v>
+        <v>3.2337849878637</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.07025749114089308</v>
+        <v>-0.0005122294788080239</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>1.608187134502927</v>
+        <v>1.678041482210205</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.0349</t>
+          <t>X ≈ 0.03489</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>41</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.423439569858964</v>
+        <v>2.456713862177793</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.966312835702468</v>
+        <v>6.999985844315809</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.40466115210411</v>
+        <v>10.4400155757726</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.251843448667046</v>
+        <v>7.28803716608595</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.325598053886978</v>
+        <v>9.391271083782655</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.634713886405848</v>
+        <v>4.700188489392119</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.300872144595758</v>
+        <v>6.367264195745705</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.583293108833296</v>
+        <v>3.650028360748728</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.624809173855958</v>
+        <v>3.69151554266346</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.8509737630865</v>
+        <v>2.918599866626941</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.564357420445738</v>
+        <v>5.631683899032765</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.285263516970836</v>
+        <v>5.352934495584769</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-3.156300872248011</v>
+        <v>-3.087300742003052</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.377657683282408</v>
+        <v>-3.308379618449685</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-6.475613312563567</v>
+        <v>-6.405547306274102</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-8.319577653186094</v>
+        <v>-8.250184774575018</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-6.014646957091109</v>
+        <v>-5.945077521308583</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-6.119630373186389</v>
+        <v>-6.049918225129765</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-8.342531600498482</v>
+        <v>-8.273051234449348</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-5.716463414634141</v>
+        <v>-5.647181034237413</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-8.698688213876004</v>
+        <v>-8.628751592447351</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-3.896594489030804</v>
+        <v>-3.826548773368643</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>1.256229457939128</v>
+        <v>1.325974719601213</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-1.258736271573248</v>
+        <v>-1.188881923865971</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.03779</t>
+          <t>X ≈ 0.03778</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>14.61856152107848</v>
+        <v>16.35915288656803</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>11.84436161619025</v>
+        <v>13.52437608821823</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>20.16075871307972</v>
+        <v>22.08635703918723</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>19.44696539988656</v>
+        <v>21.37340301974449</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>21.5207200051064</v>
+        <v>23.53761254719717</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>24.14690900835711</v>
+        <v>26.22457873329458</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>18.4959940958153</v>
+        <v>20.45263004940424</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>23.09548823078453</v>
+        <v>25.17441860465115</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>20.69797990556326</v>
+        <v>20.21590578656587</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>17.48512010454991</v>
+        <v>16.94299011052938</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>17.75947937166525</v>
+        <v>17.2170497526913</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>19.91940985843425</v>
+        <v>19.43830034924331</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>21.23394303019102</v>
+        <v>20.81513828238719</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>25.89063499964445</v>
+        <v>25.5940594059406</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>22.79267937036325</v>
+        <v>22.43591610836</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>20.94871502974075</v>
+        <v>20.53030303030303</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>15.93657255510398</v>
+        <v>15.39638589332556</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>13.39256474876478</v>
+        <v>12.79154518950438</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>13.60868791169664</v>
+        <v>13.00743657042867</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>16.23475609756098</v>
+        <v>15.6942823803967</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>8.374482517831275</v>
+        <v>7.651736212430698</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>8.298527462188666</v>
+        <v>7.575890251021598</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>11.01232701891474</v>
+        <v>10.35036496350365</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>6.058336899158469</v>
+        <v>5.274532710280376</v>
       </c>
     </row>
     <row r="34">
@@ -2918,79 +2918,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-5.848034449229054</v>
+        <v>-7.807513780098638</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-6.183209963873381</v>
+        <v>-8.142290578448481</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>9.76839391986654</v>
+        <v>7.086357039187192</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.706774519716916</v>
+        <v>2.206736353077844</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.689330821649335</v>
+        <v>6.037612547197213</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>8.87649543465615</v>
+        <v>6.224578733294628</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>12.45145538955861</v>
+        <v>9.619296716070899</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>16.52072683099659</v>
+        <v>13.50775193798452</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>16.56224289601921</v>
+        <v>17.71590578656587</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>7.092755311336767</v>
+        <v>8.609656777196037</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>7.367114578452103</v>
+        <v>8.88371641935796</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>11.43584676193372</v>
+        <v>12.77163368257665</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>5.963529456490058</v>
+        <v>7.481804949053846</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>18.78565090632527</v>
+        <v>19.76072607260726</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>26.82237184120101</v>
+        <v>27.4359161083601</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>31.76525797777894</v>
+        <v>32.19696969696973</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>31.63116428363006</v>
+        <v>32.06305255999222</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>31.52618086753478</v>
+        <v>31.95821185617103</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>27.39447794351</v>
+        <v>28.00743657042876</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>31.92934782608695</v>
+        <v>32.36094904706346</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>31.38614741708907</v>
+        <v>31.81840287909736</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>26.96236627448993</v>
+        <v>27.5758902510216</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>27.237141440972</v>
+        <v>27.85036496350365</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>22.81337401474698</v>
+        <v>23.60786604361368</v>
       </c>
     </row>
   </sheetData>
@@ -3184,79 +3184,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3303</v>
+        <v>3307</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1563823798939126</v>
+        <v>-0.1573636299484846</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.2348608301695592</v>
+        <v>-0.2357620914153102</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2745088164908864</v>
+        <v>-0.2754218069666194</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3698325273463965</v>
+        <v>-0.3706607013255478</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3269767981710672</v>
+        <v>-0.3288937666933478</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.4842261918837849</v>
+        <v>-0.4859475824948873</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.5173764595770365</v>
+        <v>-0.5190907688869757</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.5679719651310933</v>
+        <v>-0.5696379707325292</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.5696070921873826</v>
+        <v>-0.5712706131933203</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.512335721681545</v>
+        <v>-0.5141011270496705</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.4920137584650845</v>
+        <v>-0.493793620802677</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.5426436308789278</v>
+        <v>-0.5443751554267777</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.4427574423055631</v>
+        <v>-0.4446567748762291</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.5256261445546713</v>
+        <v>-0.5274359211622084</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.3817344389922255</v>
+        <v>-0.3837461353070282</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.4330795795070799</v>
+        <v>-0.4350061703002837</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.2774131497077192</v>
+        <v>-0.2795344446346135</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.304005580492408</v>
+        <v>-0.3061004488898362</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.2512820060194727</v>
+        <v>-0.253432994788696</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.3486921681282169</v>
+        <v>-0.3507191297210568</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.2388295681026165</v>
+        <v>-0.2410130322822894</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.3269845115392087</v>
+        <v>-0.3290659290932396</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.3368137122020158</v>
+        <v>-0.338873246895389</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.4553276925283285</v>
+        <v>-0.4572483601762301</v>
       </c>
     </row>
     <row r="7">
@@ -3266,79 +3266,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3288</v>
+        <v>3292</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1857493127275447</v>
+        <v>-0.1868501300232168</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2328618750779086</v>
+        <v>-0.2339220409308496</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2963833016767836</v>
+        <v>-0.2974340866805605</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.4493686904192771</v>
+        <v>-0.450268477840055</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3744469356769926</v>
+        <v>-0.3766127623769364</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.5635213990322754</v>
+        <v>-0.5654514781857642</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.5933384011405636</v>
+        <v>-0.5952696181690484</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.6429219741407763</v>
+        <v>-0.6448075138494431</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5842247420963034</v>
+        <v>-0.5861806966515459</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5231823285652695</v>
+        <v>-0.5252494538989296</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.4737241660653737</v>
+        <v>-0.4758398085794937</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.5233100233100245</v>
+        <v>-0.525380038165892</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4178509354600735</v>
+        <v>-0.4201024078943689</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.5000822125610114</v>
+        <v>-0.5022458635930178</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.352530243698304</v>
+        <v>-0.3549048549844045</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.4371481007352287</v>
+        <v>-0.4393939393939377</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.2498148019410351</v>
+        <v>-0.2522955252861436</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.2760418826566848</v>
+        <v>-0.2784972604653007</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.2240541205521041</v>
+        <v>-0.2265640361833761</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.3531287970838335</v>
+        <v>-0.3554749011566685</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2099050580408033</v>
+        <v>-0.2124519514539784</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.3285019691998343</v>
+        <v>-0.3309099918442158</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.3700339922903879</v>
+        <v>-0.3723802536235894</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.4583386690570705</v>
+        <v>-0.4605827210683486</v>
       </c>
     </row>
     <row r="8">
@@ -3348,243 +3348,243 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3259</v>
+        <v>3263</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.04828350203355569</v>
+        <v>-0.04985502578741574</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2147220956465716</v>
+        <v>-0.2161109741866483</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2965583600910193</v>
+        <v>-0.2979304151367614</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.5055781328680737</v>
+        <v>-0.506737096003306</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.4572856199772914</v>
+        <v>-0.4599499147162476</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.649714911498215</v>
+        <v>-0.652135683041891</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.6729805609642625</v>
+        <v>-0.6754187310835604</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.7205609220734246</v>
+        <v>-0.7229586445101646</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.6617352187718737</v>
+        <v>-0.6642040364969688</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.6544251772457059</v>
+        <v>-0.656948858039442</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.576438095088875</v>
+        <v>-0.5790430434014979</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.5934488928985999</v>
+        <v>-0.5960507957948593</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.5076844778271905</v>
+        <v>-0.5104573193232511</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.5887090229178185</v>
+        <v>-0.5913973615510031</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.4646272541105745</v>
+        <v>-0.4675068745250428</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.5247035611944852</v>
+        <v>-0.527477464958352</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.3345430035714756</v>
+        <v>-0.3375590608028816</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.3294686430851712</v>
+        <v>-0.3324988606638755</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.2483183054243554</v>
+        <v>-0.2514373585798637</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.3802099295127235</v>
+        <v>-0.383158697044351</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.230892009243199</v>
+        <v>-0.2340568065527648</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.3192091291606474</v>
+        <v>-0.3222720766966276</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.3635520772995378</v>
+        <v>-0.366546801202233</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.4519647794950217</v>
+        <v>-0.4548574215002006</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.03306</t>
+          <t>X &gt; -0.03305</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3231</v>
+        <v>3235</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1092781359290385</v>
+        <v>-0.1110742466425307</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3050239416063079</v>
+        <v>-0.3066033407041076</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.4674475689831041</v>
+        <v>-0.4689255160953252</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5798931276959465</v>
+        <v>-0.5812820801019072</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.4972912519292336</v>
+        <v>-0.5004943981008836</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.8161190152749356</v>
+        <v>-0.8189195759584038</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.8637620017457053</v>
+        <v>-0.8665581424776789</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.8170163700853337</v>
+        <v>-0.8198908385970682</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.7580710689945533</v>
+        <v>-0.7610172903572092</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.7440504768323208</v>
+        <v>-0.7470683690027897</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.6369598331706925</v>
+        <v>-0.6400931044515588</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.7133977647391134</v>
+        <v>-0.7164578891305737</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.5863726436628269</v>
+        <v>-0.5896676325850905</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.6662090939430385</v>
+        <v>-0.6694228744908344</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.5662486633615273</v>
+        <v>-0.569632596942057</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.6320197649489856</v>
+        <v>-0.6352843887533979</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.4390884220122473</v>
+        <v>-0.4426023855146681</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.4330943604675994</v>
+        <v>-0.4366251282987719</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.3531439192298222</v>
+        <v>-0.3567609604354942</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.487828438949002</v>
+        <v>-0.4912687156205635</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.3325479662026538</v>
+        <v>-0.3362193156730697</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.4210035933136211</v>
+        <v>-0.4245731410080609</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.4372020803366539</v>
+        <v>-0.4407351601057385</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.5257456547589996</v>
+        <v>-0.5291767178494524</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.03017</t>
+          <t>X &gt; -0.03016</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3195</v>
+        <v>3199</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2247739849925665</v>
+        <v>-0.2268185597386037</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.294655950547444</v>
+        <v>-0.2966422290745427</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4116839516454363</v>
+        <v>-0.4136429608127656</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5484827661036533</v>
+        <v>-0.5503310591620121</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4608545088341245</v>
+        <v>-0.4648734689618905</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.7853403141361213</v>
+        <v>-0.7889431815328862</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8248454388565349</v>
+        <v>-0.8284644779589456</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.6810117578217287</v>
+        <v>-0.6848348945712317</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6218286196248073</v>
+        <v>-0.6257245805778737</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.5989270494149324</v>
+        <v>-0.6029171412602281</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.4624961772672975</v>
+        <v>-0.4666364241455625</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.5989683842817612</v>
+        <v>-0.6029640543692736</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.6138119414323171</v>
+        <v>-0.6178835244664</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.6296648367392379</v>
+        <v>-0.6337374154990982</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.5211661276422817</v>
+        <v>-0.5254305250564215</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.5319090802780693</v>
+        <v>-0.5361141820449618</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.3665002195337976</v>
+        <v>-0.3709253980031946</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.2967548998206055</v>
+        <v>-0.3012785234441466</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.2495437956204327</v>
+        <v>-0.2541114944901466</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.356556736480151</v>
+        <v>-0.3609783127034873</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.19337239148701</v>
+        <v>-0.1980451742026546</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.2819252488132307</v>
+        <v>-0.2864965031177391</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.3013577699982406</v>
+        <v>-0.3058850364963561</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.3900008236553774</v>
+        <v>-0.3944263394226581</v>
       </c>
     </row>
     <row r="11">
@@ -3594,79 +3594,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.009090734622262175</v>
+        <v>0.006137414512465966</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1193538463913271</v>
+        <v>-0.1221810817122915</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1500413579073978</v>
+        <v>-0.1529794537037645</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3400058875478393</v>
+        <v>-0.3427790282959648</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1178040724420555</v>
+        <v>-0.1234687047787588</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.5460890299196706</v>
+        <v>-0.5511960927648616</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.5410664046598654</v>
+        <v>-0.546262706052886</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.4531531491654093</v>
+        <v>-0.4584927877538973</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.4886769689294326</v>
+        <v>-0.4939707566440106</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.4518395440573499</v>
+        <v>-0.4572632143597914</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3494838302407999</v>
+        <v>-0.3550123315659093</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.5151574314010858</v>
+        <v>-0.5205082692611356</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.6058136092033735</v>
+        <v>-0.6111691661072598</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.5228377065111687</v>
+        <v>-0.528324867997263</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.4644134736677614</v>
+        <v>-0.4700464669650444</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.4221902295024478</v>
+        <v>-0.4278187971081309</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.2515121093460664</v>
+        <v>-0.257374817559878</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.2104619363017761</v>
+        <v>-0.2163913184321302</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.1025843361609731</v>
+        <v>-0.1086320227754882</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.18288804071247</v>
+        <v>-0.1888180007976743</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.05634620251969835</v>
+        <v>0.05005206880183977</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.06417456075769223</v>
+        <v>-0.07032716792309657</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.05685244078816964</v>
+        <v>-0.0629895674979366</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.08194584124855453</v>
+        <v>-0.08806270956694817</v>
       </c>
     </row>
     <row r="12">
@@ -3676,79 +3676,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3083</v>
+        <v>3087</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.09278136308371643</v>
+        <v>0.08905642354552867</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1606656804595374</v>
+        <v>-0.1641089552041066</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2621417143781599</v>
+        <v>-0.2656378128076184</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4425199919058045</v>
+        <v>-0.4458760275680334</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2095562918538434</v>
+        <v>-0.216411921572913</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.5846881947481108</v>
+        <v>-0.5910412344992935</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.5653749049715131</v>
+        <v>-0.5718544866782338</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.5352659857605531</v>
+        <v>-0.5418237414654996</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.4431182065153578</v>
+        <v>-0.4497937621123995</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.4559243365693462</v>
+        <v>-0.4626854779904548</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.3890364158182038</v>
+        <v>-0.3958534731151531</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.5849441350249052</v>
+        <v>-0.5915479889302944</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.6888974005403767</v>
+        <v>-0.6955137511828653</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.6003399004052241</v>
+        <v>-0.607103009299955</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.367008888873805</v>
+        <v>-0.3741614110198128</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.2702448143384615</v>
+        <v>-0.2774514123464016</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.1262579761139193</v>
+        <v>-0.1336722837914408</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.05009962284490399</v>
+        <v>-0.05763036820658129</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.02344843235884042</v>
+        <v>0.01584536732391939</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.02935698088759864</v>
+        <v>-0.036872585633688</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.1595701678004886</v>
+        <v>0.1517362124306985</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.03825944621844002</v>
+        <v>0.0305681403061584</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.008246160985535766</v>
+        <v>0.0006240308611680234</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.04832196178629289</v>
+        <v>-0.05588517115791092</v>
       </c>
     </row>
     <row r="13">
@@ -3758,79 +3758,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3012</v>
+        <v>3016</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.09853098304656527</v>
+        <v>0.1116216159952828</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.05412223351311951</v>
+        <v>-0.05857322053753933</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2561190462023291</v>
+        <v>-0.2605313375002964</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3910228876480346</v>
+        <v>-0.3953716838128258</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.0450515747472906</v>
+        <v>-0.05382073122124353</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3342952096256724</v>
+        <v>-0.3426592363824028</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.4944156828285742</v>
+        <v>-0.5026947115585045</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4570458414518441</v>
+        <v>-0.4654230840031914</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3967206350992427</v>
+        <v>-0.4051763645393791</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.3586082335926903</v>
+        <v>-0.3672409125729246</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.2965577176312664</v>
+        <v>-0.3052348296791152</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.5235505235505187</v>
+        <v>-0.5319770615889325</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.6365942329057432</v>
+        <v>-0.64505332646646</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.5076475139549999</v>
+        <v>-0.5163173290230532</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.3195189810145038</v>
+        <v>-0.3285467015573147</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.1682289211557304</v>
+        <v>-0.1773689273689243</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.0154550796033206</v>
+        <v>0.00604517218761913</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.02965278962535933</v>
+        <v>0.02020170836605217</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.0004354884365795897</v>
+        <v>-0.008948732451138142</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.1574933687002655</v>
+        <v>-0.1666447719211561</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.0817995910020457</v>
+        <v>0.07223969040354206</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.1069623657686378</v>
+        <v>-0.1162900008007952</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.2105850774481794</v>
+        <v>-0.2197377875735782</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.2667691805875876</v>
+        <v>-0.2758651677037136</v>
       </c>
     </row>
     <row r="14">
@@ -3840,161 +3840,161 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2929</v>
+        <v>2933</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.273692894486409</v>
+        <v>0.3042934216171389</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1757251060365945</v>
+        <v>0.1726998267891631</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.008629734162809655</v>
+        <v>-0.01235613385713208</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3133502093733043</v>
+        <v>-0.3339140534262413</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.01517038771881118</v>
+        <v>-0.00694861850932682</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2838887438009436</v>
+        <v>-0.2943978848009721</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.3588400737076896</v>
+        <v>-0.369403848900852</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.3125203824085787</v>
+        <v>-0.3232077093535821</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.251615799632944</v>
+        <v>-0.2623845797841966</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2245340562118727</v>
+        <v>-0.2354964860094739</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.1344371609739028</v>
+        <v>-0.1454757055571676</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.4619105817677678</v>
+        <v>-0.472565525120018</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.5803924601026651</v>
+        <v>-0.5911117176128116</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.5436092679428199</v>
+        <v>-0.5544285315381643</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.2634895847912375</v>
+        <v>-0.274824884162058</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.1247214451756022</v>
+        <v>-0.1361369560961521</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.03390092620788465</v>
+        <v>0.02223623346161219</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.01666781034101206</v>
+        <v>-0.0282914896381854</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.05284134163269982</v>
+        <v>-0.06438099253930574</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.2887401977497461</v>
+        <v>-0.2999294003319122</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.1296601634317867</v>
+        <v>-0.1411793189044488</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.3558067781854319</v>
+        <v>-0.3670399023003768</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3678444619809653</v>
+        <v>-0.3790147229312453</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.5259464240435037</v>
+        <v>-0.5369231369749983</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.01571</t>
+          <t>X &gt; -0.0157</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2831</v>
+        <v>2835</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.339197907253066</v>
+        <v>0.3724721995718951</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3545306295522934</v>
+        <v>0.3882036381656349</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3013532466547844</v>
+        <v>0.3171667132145615</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2175083406067202</v>
+        <v>-0.2205331877563879</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.0684307453717139</v>
+        <v>0.07459116619475736</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2510397798355868</v>
+        <v>-0.2642050031232088</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.4424136871389663</v>
+        <v>-0.4555045929520034</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.595688617759528</v>
+        <v>-0.6086399712871042</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.4639418331200602</v>
+        <v>-0.4770766695744797</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.5499435501288161</v>
+        <v>-0.5631523956131304</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.466310481169991</v>
+        <v>-0.4795794607918467</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6196977486108608</v>
+        <v>-0.6328271533910481</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.668358681073812</v>
+        <v>-0.6816993845137205</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.5523041921550629</v>
+        <v>-0.5658702952896277</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.4510513063801298</v>
+        <v>-0.4649277734964983</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.2928763928659919</v>
+        <v>-0.3068408318144549</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.2299136340707832</v>
+        <v>-0.2440081953443922</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.2786956860813348</v>
+        <v>-0.2927561128539509</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.2884189719250827</v>
+        <v>-0.3024225845008743</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.4684744268077665</v>
+        <v>-0.4821882078385613</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.3910303313691657</v>
+        <v>-0.4049938791831167</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.5871664071043767</v>
+        <v>-0.6008809862008206</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.6092108066330155</v>
+        <v>-0.6228367290210315</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.7349189528631399</v>
+        <v>-0.7483949793139786</v>
       </c>
     </row>
     <row r="16">
@@ -4004,161 +4004,161 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2733</v>
+        <v>2737</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.4653121454474629</v>
+        <v>0.4985864377662921</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4932448370486</v>
+        <v>0.5269178456619414</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1791798123233903</v>
+        <v>0.2145342359918772</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2964630551026701</v>
+        <v>-0.2805548597035923</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.02370001758218621</v>
+        <v>0.0009386183664190639</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.5066537759075942</v>
+        <v>-0.5020007874025723</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.6410347290184291</v>
+        <v>-0.6566655206756451</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.7899157742195229</v>
+        <v>-0.8054215697040803</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.6186317321688506</v>
+        <v>-0.6343849111085547</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.7165544495090614</v>
+        <v>-0.7324006564644492</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6397887433756964</v>
+        <v>-0.6556775200359723</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.8251811940336538</v>
+        <v>-0.8408920843689174</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.9083807982950844</v>
+        <v>-0.9243085880640436</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.7439025816044804</v>
+        <v>-0.7601451808813877</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.6520200656901878</v>
+        <v>-0.6685995507805345</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.691953766586046</v>
+        <v>-0.7083126345421391</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.6220886519460223</v>
+        <v>-0.6385995294149609</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.7055127051751029</v>
+        <v>-0.7219436912830872</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.467814431120793</v>
+        <v>-0.4845400889440157</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.7341523565948052</v>
+        <v>-0.7504458209896328</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.5980249704014611</v>
+        <v>-0.614687145233539</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.835106104494308</v>
+        <v>-0.8514554956012574</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.8678806639228824</v>
+        <v>-0.8841127574605494</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.9588781687112089</v>
+        <v>-0.9750105852987261</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.009922</t>
+          <t>X &gt; -0.009921</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2622</v>
+        <v>2626</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4310620978436077</v>
+        <v>0.4643363901624369</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5877518877774079</v>
+        <v>0.6214248963907494</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2074536181672499</v>
+        <v>0.2428080418357368</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.2203228702709339</v>
+        <v>-0.2052954289880162</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.07928521968699442</v>
+        <v>0.1021225736822728</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5454413242371317</v>
+        <v>-0.5432986787371945</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.5771951203512344</v>
+        <v>-0.5963673020902718</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.682688140819991</v>
+        <v>-0.701811524039222</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5059010752260846</v>
+        <v>-0.5252907299051657</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.6511913799609914</v>
+        <v>-0.6706462531069874</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.5447738795959225</v>
+        <v>-0.5643068217687244</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.6882164911777622</v>
+        <v>-0.7076435476482743</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.6135276283363069</v>
+        <v>-0.6334775689590373</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.812604677129201</v>
+        <v>-0.8323442359410365</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.8030970663064707</v>
+        <v>-0.8230971743724069</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.8318655137072852</v>
+        <v>-0.8516255953613552</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.8295167489993815</v>
+        <v>-0.8493414139285278</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.9121091198916673</v>
+        <v>-0.931859065814777</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.7497103353996408</v>
+        <v>-0.7696443873820158</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.9591584158415856</v>
+        <v>-0.978721421884643</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.7943908851884345</v>
+        <v>-0.814410611456708</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.9240335134210511</v>
+        <v>-0.9438966591762679</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.8936082813837558</v>
+        <v>-0.9134340467742277</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.9852529875413225</v>
+        <v>-1.004979856360897</v>
       </c>
     </row>
     <row r="18">
@@ -4168,79 +4168,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2484</v>
+        <v>2488</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4176949615146697</v>
+        <v>0.4509692538334988</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5615613630380096</v>
+        <v>0.5952343716513511</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.04002457160656547</v>
+        <v>0.07537899527505232</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.09250315773831375</v>
+        <v>-0.0786927886387403</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.03585113391699934</v>
+        <v>-0.01528166437962852</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5855001862384412</v>
+        <v>-0.5867985122143935</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.496408942969218</v>
+        <v>-0.5204238428113328</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.7123166472642666</v>
+        <v>-0.7361245263392533</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.6481195098126591</v>
+        <v>-0.6720286920597758</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7187112532192259</v>
+        <v>-0.7428612084154622</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6616503742737763</v>
+        <v>-0.6857891117629151</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6774475524475534</v>
+        <v>-0.7016996507566944</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.7769079400421361</v>
+        <v>-0.8015083762762814</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.8946252346740025</v>
+        <v>-0.9191511625141615</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.8882614101636861</v>
+        <v>-0.9131027142270653</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.8312246797687166</v>
+        <v>-0.8559149184149177</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.9818949033562063</v>
+        <v>-1.00641971789689</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.063307520801246</v>
+        <v>-1.087765155323218</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.225362397468565</v>
+        <v>-1.249482803819191</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.336414790996784</v>
+        <v>-1.360292258447572</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.293351193075154</v>
+        <v>-1.317553229560467</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.265273726909264</v>
+        <v>-1.289571596367963</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.248555348460251</v>
+        <v>-1.272776860522058</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.341215357233658</v>
+        <v>-1.365338672356273</v>
       </c>
     </row>
     <row r="19">
@@ -4250,407 +4250,407 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2326</v>
+        <v>2330</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.6931559696220191</v>
+        <v>0.7264302619408483</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.167524553827292</v>
+        <v>1.201197562440633</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5373681885907473</v>
+        <v>0.5727226122592342</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1458197030075965</v>
+        <v>0.1580216818663445</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1457135045083575</v>
+        <v>0.1630918825188985</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.4961859720807524</v>
+        <v>-0.5020936143832913</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3489305890269634</v>
+        <v>-0.3792830311240962</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.6886445721148178</v>
+        <v>-0.7185907730129415</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.9219240337580814</v>
+        <v>-0.951471612154819</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.9451488135238861</v>
+        <v>-0.9750986266719863</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.6890967344463874</v>
+        <v>-0.7193565639966977</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.6015690895930348</v>
+        <v>-0.6321522553681334</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.5889067772544294</v>
+        <v>-0.620145784251001</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.8707666040976036</v>
+        <v>-0.9016670897858958</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.6908950799422726</v>
+        <v>-0.722484917719477</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.7130401482223547</v>
+        <v>-0.7442906395002211</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.8219190761046278</v>
+        <v>-0.8530792329046548</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.073192687540235</v>
+        <v>-1.104002755701103</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.346685580262218</v>
+        <v>-1.376931737922483</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.435085836909863</v>
+        <v>-1.46510065302229</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-1.352292293927114</v>
+        <v>-1.382768716844907</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.531956151925783</v>
+        <v>-1.562188651208253</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.532874066959472</v>
+        <v>-1.562976949838266</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.62679197276654</v>
+        <v>-1.656797761822624</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.001246</t>
+          <t>X &gt; -0.001247</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2161</v>
+        <v>2165</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.000489043378437</v>
+        <v>1.033763335697266</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.352756241841355</v>
+        <v>1.386429250454697</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.058793632933963</v>
+        <v>1.09414805660245</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5543115490014188</v>
+        <v>0.5645120939883057</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6737743796868614</v>
+        <v>0.6870167635125171</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1529086277842282</v>
+        <v>0.1407107222955091</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.3701682094572334</v>
+        <v>0.3311818367552917</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.02614913133012919</v>
+        <v>-0.01242229401916717</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.08977117047692218</v>
+        <v>-0.1281309106818398</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.1936015102524351</v>
+        <v>-0.2323196645968224</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.01540864668937303</v>
+        <v>-0.02353794244184115</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.08507943965836517</v>
+        <v>0.0457877171808363</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.04575871710270718</v>
+        <v>-0.08559701173046363</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1477198104351984</v>
+        <v>-0.1875497894617055</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.08806694862067133</v>
+        <v>-0.1284813157429952</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.2951986542093792</v>
+        <v>-0.3348603383117918</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.4942167527890717</v>
+        <v>-0.5336325228807013</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.8487714809334221</v>
+        <v>-0.8876349118314124</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.9747861778919074</v>
+        <v>-1.013300756760238</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.130196304849882</v>
+        <v>-1.168327117067534</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.8608991150977658</v>
+        <v>-0.8999243041744691</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.140711174303064</v>
+        <v>-1.179301257977016</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.116235062265737</v>
+        <v>-1.154713522184259</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.350157361628654</v>
+        <v>-1.388284841682676</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.001646</t>
+          <t>X &gt; 0.001645</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1953</v>
+        <v>1957</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.7883532392796297</v>
+        <v>0.8216275315984589</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.365956629300612</v>
+        <v>1.399629637913954</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.29542452221245</v>
+        <v>1.330778945880937</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.139440539648106</v>
+        <v>1.17563425706701</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.23056020695671</v>
+        <v>1.296233236852387</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.3308443636923926</v>
+        <v>0.3675807616921603</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8050197241426176</v>
+        <v>0.8126706173555647</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.5050932054528516</v>
+        <v>0.4837492334544109</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.169524621010396</v>
+        <v>0.1195569021845273</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1175185552886404</v>
+        <v>-0.1676136439099878</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.01711294156204701</v>
+        <v>-0.06721420669956757</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.1912400576522728</v>
+        <v>0.1404334117115624</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.2166065839141211</v>
+        <v>0.1647317783221496</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.127430347730396</v>
+        <v>0.07550322902143591</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.1614668197056446</v>
+        <v>0.1088560880141571</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.2326135606996758</v>
+        <v>-0.2839463335646499</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.2344080322528868</v>
+        <v>-0.2858951657375854</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.5132358712628218</v>
+        <v>-0.5642877193086662</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.6754247966418845</v>
+        <v>-0.7259986997038084</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.969276954522222</v>
+        <v>-1.019129144335551</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.6646216768916133</v>
+        <v>-0.7156107263448064</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.9148715771725406</v>
+        <v>-0.9654573753183797</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.7122155079844319</v>
+        <v>-0.7630160375178008</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.655536691190342</v>
+        <v>-0.7065608001948434</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.004538</t>
+          <t>X &gt; 0.004536</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1656</v>
+        <v>1660</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.6047535194437046</v>
+        <v>0.6380278117625338</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.22708847757017</v>
+        <v>1.260761486183512</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.881942172670144</v>
+        <v>1.91729659633863</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.347682073121511</v>
+        <v>1.383875790540415</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.999767165416444</v>
+        <v>2.065440195312121</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.109732496556077</v>
+        <v>1.175207099542348</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.29437683727285</v>
+        <v>1.360768888422797</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.25519980994698</v>
+        <v>1.321935061862412</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.9126724716505805</v>
+        <v>0.9445114119398994</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.832823563609665</v>
+        <v>0.8298841859333308</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.902720876022741</v>
+        <v>0.8645662099025486</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.138775741355225</v>
+        <v>1.064572042839949</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.31036384241834</v>
+        <v>1.234299959033891</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.185442001768536</v>
+        <v>1.109338015886678</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.284119332839801</v>
+        <v>1.206899321789294</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.8337303561417357</v>
+        <v>0.7582574394212074</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.8562990086862285</v>
+        <v>0.7805395547901455</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.510641705707684</v>
+        <v>0.4717253696845489</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.1008099069683723</v>
+        <v>0.06272503196716173</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.0225903614457863</v>
+        <v>-0.01527865387868133</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.1782432317494909</v>
+        <v>0.139702518086537</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.04240636934502362</v>
+        <v>-0.1166488584850214</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.6306498768566584</v>
+        <v>0.5550609297890219</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.6515382659547413</v>
+        <v>0.575737529557486</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.00743</t>
+          <t>X &gt; 0.007428</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1380</v>
+        <v>1385</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.745835521743821</v>
+        <v>1.811089758877934</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.482447516072938</v>
+        <v>1.548048972005873</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.837434776322766</v>
+        <v>1.90343020991893</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.123641463129609</v>
+        <v>1.19047619047619</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.265909366547767</v>
+        <v>2.361141958961923</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.806986398793605</v>
+        <v>1.902484041759443</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.46484532058021</v>
+        <v>1.560951426735663</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.047740782742906</v>
+        <v>2.143572119715728</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.802106811871795</v>
+        <v>1.898115255719382</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.501800788598132</v>
+        <v>1.555615648549463</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.60335375577214</v>
+        <v>1.614467256278104</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.94257181667254</v>
+        <v>1.909605944652206</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.157225265173189</v>
+        <v>2.0776920843958</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.340343300762051</v>
+        <v>2.259529614124382</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.519058465444765</v>
+        <v>2.364077027900272</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>2.077071767853568</v>
+        <v>1.924983116571902</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.843061944907653</v>
+        <v>1.691349922102532</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.2326633663575</v>
+        <v>1.126678378849221</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.232180031094366</v>
+        <v>1.170260777921499</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.390895953757223</v>
+        <v>1.328745249899256</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.614699084855992</v>
+        <v>1.623597684292164</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.438550758224842</v>
+        <v>1.331301506432851</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.975044032037076</v>
+        <v>1.822226435365117</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.87134502923977</v>
+        <v>1.718576031580014</v>
       </c>
     </row>
     <row r="24">
@@ -4660,79 +4660,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.853089478602946</v>
+        <v>1.886363770921776</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.198186072802152</v>
+        <v>2.231859081415493</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.544199894430307</v>
+        <v>2.579554318098793</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.405236513209935</v>
+        <v>1.441430230628839</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.975340877845753</v>
+        <v>2.04101390774143</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.737335422825325</v>
+        <v>1.802810025811596</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.729775413220281</v>
+        <v>1.796167464370228</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.301560903756148</v>
+        <v>2.36829615567158</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.74783887354068</v>
+        <v>1.814545242348181</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.739309585220234</v>
+        <v>1.806935688760674</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.319936040061719</v>
+        <v>2.336097371738916</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.517988825484572</v>
+        <v>2.48251803631814</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.809224256149044</v>
+        <v>2.719900187149094</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.323416153394568</v>
+        <v>3.179093419546042</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.888907318125227</v>
+        <v>2.744426746657915</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.512192202974006</v>
+        <v>2.370166744102015</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.260092762076823</v>
+        <v>2.118466029727948</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.727393349403272</v>
+        <v>1.63966805639857</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.943516512335087</v>
+        <v>1.907948953007697</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.183219178082197</v>
+        <v>2.147273833388184</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.37828630908259</v>
+        <v>2.341642114911458</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.527285358687045</v>
+        <v>2.43688255213366</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.19907463746388</v>
+        <v>3.053530061878334</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>3.005365647796467</v>
+        <v>2.860149148636538</v>
       </c>
     </row>
     <row r="25">
@@ -4742,243 +4742,243 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.941429350188727</v>
+        <v>1.974703642507556</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.470184721073565</v>
+        <v>2.503857729686906</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.758346028045743</v>
+        <v>2.79370045171423</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.504595911396855</v>
+        <v>1.540789628815759</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.003257011901965</v>
+        <v>2.068930041797643</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.326490739379594</v>
+        <v>1.391965342365864</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.065503657001599</v>
+        <v>2.131895708151546</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.082845339776767</v>
+        <v>3.1495805916922</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.800387322725975</v>
+        <v>2.867093691533476</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.538430961632571</v>
+        <v>3.606057065173012</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.230804355185356</v>
+        <v>3.23216854318806</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.801365301365308</v>
+        <v>2.737436418357774</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.717969138057718</v>
+        <v>2.586196597721958</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.455367024405056</v>
+        <v>2.25712636058423</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.73229961347122</v>
+        <v>2.530510702954636</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.526127542996306</v>
+        <v>2.326839826839823</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.609425153195204</v>
+        <v>2.476559241104539</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.743572171882533</v>
+        <v>1.679831523560772</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.285782291336091</v>
+        <v>2.288109751753353</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.798913043478258</v>
+        <v>2.868195423874987</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.867436152481922</v>
+        <v>2.869127516778526</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.295604883943312</v>
+        <v>3.228064164065074</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.857500835974612</v>
+        <v>3.719930180894949</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.741796266503229</v>
+        <v>3.535402275497766</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.01611</t>
+          <t>X &gt; 0.0161</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.769698818968301</v>
+        <v>3.80297311128713</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.294073866121728</v>
+        <v>3.32774687473507</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.2420138514738</v>
+        <v>4.277368275142287</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.68552390906715</v>
+        <v>2.721717626486054</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.865197944267827</v>
+        <v>3.930870974163504</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.350115366263381</v>
+        <v>3.415589969249652</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.858148110613847</v>
+        <v>2.924540161763794</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.984087847117756</v>
+        <v>4.050823099033188</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.885154473938151</v>
+        <v>3.951860842745653</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.375364006988939</v>
+        <v>4.442990110529379</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.612451825440417</v>
+        <v>3.593454247073325</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.926888161065378</v>
+        <v>1.910210461602858</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.349513679568396</v>
+        <v>2.331992214971457</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.496612327023364</v>
+        <v>2.391812214929359</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.246131792211422</v>
+        <v>3.227055348866372</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.57358620802998</v>
+        <v>2.55561948599923</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.143717865993743</v>
+        <v>3.124937229471833</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.334509097785777</v>
+        <v>2.4042212458424</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.973167471985207</v>
+        <v>3.042647838034341</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.160211267605639</v>
+        <v>3.229493648002368</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.128344019774964</v>
+        <v>3.109482691303946</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.423923631404634</v>
+        <v>3.315326870739909</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>3.416212922180549</v>
+        <v>3.308111442376898</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>3.288129564836183</v>
+        <v>3.091434118731087</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.019</t>
+          <t>X &gt; 0.01899</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.675206809220413</v>
+        <v>4.485347915248724</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.340031294576086</v>
+        <v>4.341775705809042</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.011655206689568</v>
+        <v>5.007007134789518</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.489800473150915</v>
+        <v>4.676462293167056</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.084223586399425</v>
+        <v>5.105490176260311</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.503633880788172</v>
+        <v>4.527638006717162</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.922706328388649</v>
+        <v>3.946893911736943</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.371598899760684</v>
+        <v>5.389523767175064</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.837299225819791</v>
+        <v>4.857397182359371</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.598972452286446</v>
+        <v>5.614118217603952</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.297515980438249</v>
+        <v>5.314564093035465</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.058729178690797</v>
+        <v>4.079791745036808</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.277808017785219</v>
+        <v>4.486266389461761</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.86451262709636</v>
+        <v>4.073982924105039</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>5.124967184604166</v>
+        <v>5.327885515625816</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>3.992580017334944</v>
+        <v>4.201431137377604</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.818179221458578</v>
+        <v>5.023536944950806</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.561564327436237</v>
+        <v>3.771468707668816</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.737380388640595</v>
+        <v>4.94338303314381</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>5.308301343570051</v>
+        <v>5.512638020932101</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>5.532855253190142</v>
+        <v>5.7349102086066</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>5.264961617893029</v>
+        <v>5.467859658287374</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>5.539736784375158</v>
+        <v>5.742334370769427</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>5.204678362573098</v>
+        <v>5.284092939725888</v>
       </c>
     </row>
     <row r="28">
@@ -4988,79 +4988,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.602987027984142</v>
+        <v>5.734152886568033</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.30395609165307</v>
+        <v>4.437837626679759</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.755821892627175</v>
+        <v>5.884433962264154</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.2829924348557</v>
+        <v>5.411864558206027</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.60446963778346</v>
+        <v>6.75876639335106</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>4.863923407416756</v>
+        <v>5.022655656371519</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.572984986206109</v>
+        <v>4.731476203250395</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.981177328639347</v>
+        <v>6.135957066189626</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.781729538240292</v>
+        <v>5.937059632719716</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>6.935604970844359</v>
+        <v>7.087220879760153</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.764181105429572</v>
+        <v>5.918972829614376</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.28026792484625</v>
+        <v>4.438300349243306</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.878668272624154</v>
+        <v>4.036292128541035</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.657311461589799</v>
+        <v>3.815213252094445</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>5.167054921347678</v>
+        <v>5.080146877590813</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>3.834404127595569</v>
+        <v>3.991841491841491</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.423201999711708</v>
+        <v>4.579078201017865</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.354363161929676</v>
+        <v>3.512699035658223</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>5.016269457391608</v>
+        <v>5.170898108890249</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>5.926204819277103</v>
+        <v>6.078897765012115</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>6.105895976544211</v>
+        <v>6.257505443199925</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>6.270904776323299</v>
+        <v>6.422044097175437</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>7.26857150907049</v>
+        <v>7.417672655811344</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>7.192630169802023</v>
+        <v>7.341840402588069</v>
       </c>
     </row>
     <row r="29">
@@ -5073,76 +5073,76 @@
         <v>344</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>6.20959952448176</v>
+        <v>6.242873816800589</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.165121684256036</v>
+        <v>6.198794692869377</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>6.469607266681528</v>
+        <v>6.504961690350015</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.883720930232556</v>
+        <v>4.91991464765146</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.425427889394562</v>
+        <v>7.49110091929024</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.449801804726924</v>
+        <v>6.515276407713195</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.258331021510109</v>
+        <v>6.324723072660056</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.433264748084582</v>
+        <v>7.500000000000014</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.184083138688607</v>
+        <v>7.250789507496108</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.735829123268012</v>
+        <v>8.803455226808452</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.428793041546129</v>
+        <v>8.496119520133156</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.114815417141003</v>
+        <v>6.182486395754935</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>4.990324198653859</v>
+        <v>5.059324328898818</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>5.931758085293929</v>
+        <v>6.001036150126652</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>5.854222195093818</v>
+        <v>5.924288201383284</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4.705096198203584</v>
+        <v>4.77448907681466</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>4.571002504054661</v>
+        <v>4.640571939837187</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>3.303228390284964</v>
+        <v>3.372940538341588</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.682142250891197</v>
+        <v>4.751622616940331</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>4.869186046511629</v>
+        <v>4.938468426908358</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>4.616683311932285</v>
+        <v>4.686619933360937</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>5.12212360512688</v>
+        <v>5.192169320789041</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>6.55968946928342</v>
+        <v>6.629434730945505</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>6.483748130014952</v>
+        <v>6.553602477722229</v>
       </c>
     </row>
     <row r="30">
@@ -5155,404 +5155,404 @@
         <v>287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.953056294597637</v>
+        <v>6.986330586916466</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.269448724204182</v>
+        <v>6.303121732817523</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.571908538863688</v>
+        <v>6.607262962532175</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.464387002674016</v>
+        <v>4.50058072009292</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.583437775141249</v>
+        <v>7.649110805036926</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.028442109402398</v>
+        <v>6.093916712388669</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.952440088846636</v>
+        <v>6.018832139996583</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.06761366632459</v>
+        <v>7.134348918240022</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.760697675598081</v>
+        <v>6.827404044405583</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.077454599323438</v>
+        <v>8.145080702863879</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.351813866438775</v>
+        <v>8.419140345025802</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.678991739967358</v>
+        <v>6.746662718581291</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.902932577229329</v>
+        <v>5.971932707474288</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.772168100689761</v>
+        <v>7.841446165522484</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>7.810100973150703</v>
+        <v>7.880166979440169</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>7.011432799775569</v>
+        <v>7.080825678386645</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>6.877339105626646</v>
+        <v>6.946908541409172</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>5.030195410785737</v>
+        <v>5.099907558842361</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>5.594750629466667</v>
+        <v>5.664230995515801</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>6.478658536585371</v>
+        <v>6.5479409169821</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>5.935458127587417</v>
+        <v>6.00539474901607</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>6.207935127693936</v>
+        <v>6.277980843356097</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>8.224870572921695</v>
+        <v>8.29461583458378</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>8.148929233653227</v>
+        <v>8.218783581360505</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.03057</t>
+          <t>X &gt; 0.03056</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>230</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.325878594249204</v>
+        <v>6.359152886568033</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.990703079604877</v>
+        <v>6.024376088218219</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.029263485083959</v>
+        <v>8.064617908752446</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.445904954499504</v>
+        <v>6.482098671918408</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.689330821649364</v>
+        <v>8.755003851545041</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6.702582391177891</v>
+        <v>6.768056994164162</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.234064085210811</v>
+        <v>7.300456136360758</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.564205091866171</v>
+        <v>9.630940343781603</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.301373330801837</v>
+        <v>8.368079699609339</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.266668354815032</v>
+        <v>9.334294458355473</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>9.97581023062601</v>
+        <v>10.04313670921304</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.827151109759811</v>
+        <v>8.894822088373743</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>8.137442499968323</v>
+        <v>8.206442630213282</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.52478134110788</v>
+        <v>10.5940594059406</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>10.30063271076623</v>
+        <v>10.3706987170557</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>9.156562325605002</v>
+        <v>9.225955204216078</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>8.152903414064767</v>
+        <v>8.222472849847293</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>7.613137389273845</v>
+        <v>7.682849537330469</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>7.394477943510005</v>
+        <v>7.463958309559139</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>9.320652173913047</v>
+        <v>9.389934554309775</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>9.212234373610748</v>
+        <v>9.282170995039401</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>8.701496709272483</v>
+        <v>8.771542424934644</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>10.28061970184157</v>
+        <v>10.35036496350365</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>9.769895753877442</v>
+        <v>9.83975010158472</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.03346</t>
+          <t>X &gt; 0.03345</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>173</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5.863450848584463</v>
+        <v>5.896725140903293</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.950240651859218</v>
+        <v>4.98391366047256</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.556782962339547</v>
+        <v>7.592137386008034</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.264954967065471</v>
+        <v>6.301148684484374</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>11.10199732076975</v>
+        <v>11.16767035066543</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.555057887533749</v>
+        <v>9.62053249052002</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.360226437560648</v>
+        <v>9.426618488710595</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.97184520244672</v>
+        <v>12.03858045436215</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>10.27925722122659</v>
+        <v>10.34596359003409</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>11.81756053878085</v>
+        <v>11.88518664232129</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.24798917005803</v>
+        <v>13.31531564864506</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>12.96889526658313</v>
+        <v>13.03656624519706</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.26636936601506</v>
+        <v>11.33536949626002</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>13.3571512833044</v>
+        <v>13.42642934813712</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>12.12018536218618</v>
+        <v>12.19025136847565</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>10.98114136556479</v>
+        <v>11.05053424417586</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>11.42508235349679</v>
+        <v>11.49465178927932</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>11.32009893740151</v>
+        <v>11.38981108545813</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>9.802118054090549</v>
+        <v>9.871598420139684</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>11.14523121387283</v>
+        <v>11.21451359426956</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>9.445961440713027</v>
+        <v>9.51589806214168</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>10.52607574923227</v>
+        <v>10.59612146489443</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>13.69102432611903</v>
+        <v>13.76076958778111</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>12.45901362268871</v>
+        <v>12.52886797039599</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.03635</t>
+          <t>X &gt; 0.03634</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>132</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.931939200309813</v>
+        <v>6.965213492628642</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.324036412938213</v>
+        <v>4.357709421551554</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.672214736730865</v>
+        <v>6.707569160399352</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.958421423537708</v>
+        <v>5.994615140956611</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>11.65375769911971</v>
+        <v>11.71943072901539</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>11.08334655455074</v>
+        <v>11.14882115753701</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.31048042249672</v>
+        <v>10.37687247364666</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14.5773803224327</v>
+        <v>14.64411557434813</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>12.34616911472807</v>
+        <v>12.41287548353557</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>14.60263673426167</v>
+        <v>14.67026283780211</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>15.63457175895276</v>
+        <v>15.70189823753979</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>15.35547785547786</v>
+        <v>15.42314883409179</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15.74613815214223</v>
+        <v>15.81513828238719</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>18.55508437141091</v>
+        <v>18.62436243624363</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>17.89615313237361</v>
+        <v>17.96621913866307</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>16.97606166684347</v>
+        <v>17.04545454545455</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>16.84196797269455</v>
+        <v>16.91153740847707</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>16.73698455659927</v>
+        <v>16.80669670465589</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>15.43795620437957</v>
+        <v>15.5074365704287</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>16.38257575757575</v>
+        <v>16.45185813797248</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>15.08179959100205</v>
+        <v>15.1517362124307</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>15.00584453535944</v>
+        <v>15.0758902510216</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>17.55334697456883</v>
+        <v>17.62309223623092</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>16.71982987772461</v>
+        <v>16.78968422543189</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.03924</t>
+          <t>X &gt; 0.03923</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.468735737106343</v>
+        <v>2.880892017002814</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.935758024659826</v>
+        <v>0.3722021751747349</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.5949586594747842</v>
+        <v>0.02113964788288314</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1188346537183733</v>
+        <v>-0.6918143715598575</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.208203253565266</v>
+        <v>6.581090808066783</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>5.197565668769862</v>
+        <v>4.594143950685904</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>6.622501734518025</v>
+        <v>5.996108310273812</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>10.73955148460387</v>
+        <v>10.06572295247726</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>8.583265351824295</v>
+        <v>9.020253612652823</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.30393543556037</v>
+        <v>13.68212054531199</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>14.6771958015768</v>
+        <v>15.04313670921304</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>13.2992007992008</v>
+        <v>13.67743078402592</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>13.27361067961476</v>
+        <v>13.64122523890892</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.25005606638261</v>
+        <v>15.5940594059406</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>15.6900259262464</v>
+        <v>16.02287263009918</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>15.18618487696668</v>
+        <v>15.53030303030303</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>17.24989338061997</v>
+        <v>17.57029893680382</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>18.24381106342578</v>
+        <v>18.55241475472177</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>16.26213202855539</v>
+        <v>16.59439309216784</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>16.44917582417582</v>
+        <v>16.78123890213587</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>18.10377761298007</v>
+        <v>18.41260577764809</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>18.02782255733747</v>
+        <v>18.33675981623899</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>20.50039992162178</v>
+        <v>20.78514757219931</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>21.52335968125441</v>
+        <v>21.79627184071516</v>
       </c>
     </row>
     <row r="35">
@@ -5565,76 +5565,76 @@
         <v>68</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>6.619996241308023</v>
+        <v>6.653270533626852</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3.343644256075464</v>
+        <v>3.377317264688806</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-2.507820913893021</v>
+        <v>-2.472466490224534</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-1.751025991792069</v>
+        <v>-1.714832274373165</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>6.707233634948594</v>
+        <v>6.772906664844271</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.953221777367141</v>
+        <v>4.018696380353411</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>4.650943880607237</v>
+        <v>4.717335931757184</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>8.784153940971024</v>
+        <v>8.850889192886456</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>5.884493535405426</v>
+        <v>5.951199904212928</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>15.40477577169482</v>
+        <v>15.47240187523526</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>17.14972327410428</v>
+        <v>17.2170497526913</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>13.92945290004114</v>
+        <v>13.99712387865507</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>15.74613815214223</v>
+        <v>15.81513828238719</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>14.05419310581376</v>
+        <v>14.12347117064648</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>11.92467363148234</v>
+        <v>11.99473963777181</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>9.578557210515477</v>
+        <v>9.647950089126553</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>12.3856399869548</v>
+        <v>12.45520942273733</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>13.75124480615364</v>
+        <v>13.82095695421026</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>12.49677973379134</v>
+        <v>12.56626009984047</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>11.21323529411765</v>
+        <v>11.28251767451438</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>13.61121135570793</v>
+        <v>13.68114797713658</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>15.00584453535944</v>
+        <v>15.0758902510216</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>18.2217961724298</v>
+        <v>18.29154143409188</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>21.08703130374958</v>
+        <v>21.15688565145685</v>
       </c>
     </row>
   </sheetData>
@@ -5831,76 +5831,76 @@
         <v>68</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.20353317045668</v>
+        <v>-2.170258878137851</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.4024677854872252</v>
+        <v>0.4361407941005666</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4333555566952114</v>
+        <v>0.4687099803636983</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.131326949384402</v>
+        <v>4.167520666803306</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8248806937721227</v>
+        <v>0.8905537236678001</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>5.423810012661264</v>
+        <v>5.489284615647534</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.121532115901353</v>
+        <v>6.1879241670513</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.784153940971024</v>
+        <v>8.850889192886456</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>11.76684647658189</v>
+        <v>11.83355284538939</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.051834595224229</v>
+        <v>8.119460698764669</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.326193862339565</v>
+        <v>8.393520340926592</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.45886466474703</v>
+        <v>12.52653564336096</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.33437344625988</v>
+        <v>11.40337357650484</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.52478134110788</v>
+        <v>15.5940594059406</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>10.45408539618823</v>
+        <v>10.52415140247769</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>12.51973368110372</v>
+        <v>12.5891265597148</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>3.56211057519009</v>
+        <v>3.631680010972616</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>3.45712715909481</v>
+        <v>3.526839307151434</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>5.143838557320741</v>
+        <v>5.213318923369876</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>6.80147058823529</v>
+        <v>6.870752968632019</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>4.78768194394322</v>
+        <v>4.857618565371872</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>6.182315123594726</v>
+        <v>6.252360839256887</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>10.86885499595922</v>
+        <v>10.9386002576213</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>15.2046783625731</v>
+        <v>15.27453271028038</v>
       </c>
     </row>
     <row r="7">
@@ -5913,76 +5913,76 @@
         <v>83</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.6620732129797062</v>
+        <v>-0.6287989206608771</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2075705494843945</v>
+        <v>0.2412435580977359</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.177508639615134</v>
+        <v>1.212863063283621</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.487811711964142</v>
+        <v>6.524005429383045</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.508084095614791</v>
+        <v>2.573757125510468</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.514525817055301</v>
+        <v>7.580000420041571</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7.946478962109715</v>
+        <v>8.012871013259662</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>10.07756287080802</v>
+        <v>10.14429812272346</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.11907893583066</v>
+        <v>10.18578530463816</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.935604970844359</v>
+        <v>7.0032310743848</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.005144960851254</v>
+        <v>6.072471439438281</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>9.340508888701663</v>
+        <v>9.408179867315596</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.216017670214519</v>
+        <v>8.285017800459478</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.60911869050546</v>
+        <v>11.67839675533818</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>7.335729620142864</v>
+        <v>7.405795626432329</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>10.34042822398111</v>
+        <v>10.40982110259219</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>1.772599590073149</v>
+        <v>1.842169025855675</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>1.667616173977869</v>
+        <v>1.737328322034493</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>3.088558614018126</v>
+        <v>3.158038980067261</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>5.685240963855421</v>
+        <v>5.754523344252149</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>2.732402000640604</v>
+        <v>2.802338622069257</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>5.066085499214857</v>
+        <v>5.136131214877018</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>10.16013777413072</v>
+        <v>10.22988303579281</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>12.49383498907913</v>
+        <v>12.5636893367864</v>
       </c>
     </row>
     <row r="8">
@@ -5995,240 +5995,240 @@
         <v>112</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.566978548607942</v>
+        <v>-4.533704256289113</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.4378683489665534</v>
+        <v>-0.4041953403532119</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.8010026155187404</v>
+        <v>0.8363570391872273</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.337209302325583</v>
+        <v>6.373403019744487</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.186225231587244</v>
+        <v>4.251898261482921</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>7.944818416022613</v>
+        <v>8.010293019008884</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8.064809426825725</v>
+        <v>8.131201477975672</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>9.571969067021442</v>
+        <v>9.638704318936874</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>9.613485132044076</v>
+        <v>9.680191500851578</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.839649721274647</v>
+        <v>8.907275824815088</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>7.328294702675706</v>
+        <v>7.395621181262733</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.834915084915082</v>
+        <v>8.902586063529014</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.603281009285091</v>
+        <v>8.67228113953005</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>11.06049562682217</v>
+        <v>11.12977369165489</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>8.615850102070574</v>
+        <v>8.68591610836004</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>10.10376729454909</v>
+        <v>10.17316017316017</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>3.719673600400171</v>
+        <v>3.789243036182697</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>2.721833041447752</v>
+        <v>2.791545189504376</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>2.937956204379567</v>
+        <v>3.007436570428702</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>4.910714285714292</v>
+        <v>4.97999666611102</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>2.581799591002046</v>
+        <v>2.651736212430698</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>3.398701678216575</v>
+        <v>3.468747393878736</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>7.244905416127274</v>
+        <v>7.314650677789359</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>8.954678362573098</v>
+        <v>9.024532710280376</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.03306</t>
+          <t>X &lt; -0.03305</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>140</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.245549977179373</v>
+        <v>-2.212275684860543</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.704988793890593</v>
+        <v>1.738661802503934</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.55100261551874</v>
+        <v>4.586357039187227</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.694352159468437</v>
+        <v>6.730545876887341</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.186225231587244</v>
+        <v>4.251898261482921</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>10.08767555887975</v>
+        <v>10.15315016186602</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10.74338085539716</v>
+        <v>10.8097729065471</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>9.750540495592873</v>
+        <v>9.817275747508305</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.792056560615507</v>
+        <v>9.858762929423008</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>9.018221149846077</v>
+        <v>9.085847253386518</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.149723274104275</v>
+        <v>7.217049752691302</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9.727772227772235</v>
+        <v>9.795443206386167</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.603281009285091</v>
+        <v>8.67228113953005</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>10.52478134110788</v>
+        <v>10.5940594059406</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>9.151564387784852</v>
+        <v>9.221630394074317</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>10.46091015169196</v>
+        <v>10.53030303030303</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>5.326816457543032</v>
+        <v>5.396385893325558</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>4.507547327162044</v>
+        <v>4.577259475218668</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>4.723670490093859</v>
+        <v>4.793150856142994</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>6.339285714285708</v>
+        <v>6.408568094682437</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>4.367513876716338</v>
+        <v>4.43745049814499</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>5.005844535359437</v>
+        <v>5.075890251021598</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>7.423476844698705</v>
+        <v>7.49322210636079</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>8.776106934001668</v>
+        <v>8.845961281708945</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.03017</t>
+          <t>X &lt; -0.03016</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>176</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.3031513215219306</v>
+        <v>0.3364256138407598</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.104339443241244</v>
+        <v>1.138012451854586</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.505548070064201</v>
+        <v>2.540902493732688</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.632663847780123</v>
+        <v>4.668857565199026</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.562848608210629</v>
+        <v>2.628521638106307</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.295467766671955</v>
+        <v>7.360942369658225</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.658965270981561</v>
+        <v>7.725357322131508</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.107683352735734</v>
+        <v>5.174418604651166</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.149199417758368</v>
+        <v>5.21590578656587</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.375364006988939</v>
+        <v>4.442990110529379</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.376996001377002</v>
+        <v>2.444322479964029</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.506993006993007</v>
+        <v>5.574663985606939</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>7.223410879414963</v>
+        <v>7.292411009659922</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>7.570235886562422</v>
+        <v>7.639513951395145</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>6.343122829343308</v>
+        <v>6.413188835632774</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>6.370001060782862</v>
+        <v>6.439393939393938</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>2.826816457543032</v>
+        <v>2.896385893325558</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>1.017287586902292</v>
+        <v>1.086999734958916</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.801592568015934</v>
+        <v>1.871072934065069</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.55681818181818</v>
+        <v>2.626100562214909</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.8772541364565853</v>
+        <v>0.9471907578852381</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>1.369480898995803</v>
+        <v>1.439526614657964</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>3.348801520023386</v>
+        <v>3.418546781685471</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.409223817118551</v>
+        <v>4.479078164825829</v>
       </c>
     </row>
     <row r="11">
@@ -6241,76 +6241,76 @@
         <v>231</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.024770756400152</v>
+        <v>-2.991496464081322</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.628344539442736</v>
+        <v>-1.594671530829395</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.769343704827577</v>
+        <v>-1.73398928115909</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5471660122822968</v>
+        <v>0.5833597297012005</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.848406803044782</v>
+        <v>-2.782733773149104</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.100662571866764</v>
+        <v>2.166137174853034</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.760696872713176</v>
+        <v>1.827088923863123</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.6163413613937436</v>
+        <v>0.6830766133091757</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.956558725117674</v>
+        <v>2.023265093925176</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.182723314348245</v>
+        <v>1.250349417888685</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.158381282762285</v>
+        <v>0.2257077613493124</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.909590409590407</v>
+        <v>2.97726138820434</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.248302654306734</v>
+        <v>5.317302784551693</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.161144977471508</v>
+        <v>4.230423042304231</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>3.935114171334639</v>
+        <v>4.005180177624105</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>3.231472922254717</v>
+        <v>3.300865800865793</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.499976630703209</v>
+        <v>0.569546066485735</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.470807651192942</v>
+        <v>-0.4010955031363181</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.6875849211615517</v>
+        <v>-0.6181045551124171</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.500541125541119</v>
+        <v>-0.4312587451443903</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-2.775343266140816</v>
+        <v>-2.705406644712163</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.985497455982554</v>
+        <v>-1.915451740320393</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.844921423699553</v>
+        <v>-0.775176162037468</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.9208627629680208</v>
+        <v>-0.8510084152607433</v>
       </c>
     </row>
     <row r="12">
@@ -6323,76 +6323,76 @@
         <v>288</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.326899183528575</v>
+        <v>-3.293624891209745</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.8842969203951228</v>
+        <v>-0.8506239117817813</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2406640511479239</v>
+        <v>-0.205309627479437</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.476098191214469</v>
+        <v>1.512291908633372</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.319727149365129</v>
+        <v>-1.254054119469451</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.992437463641657</v>
+        <v>2.057912066627928</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.566793553809852</v>
+        <v>1.633185604959799</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.288238908291291</v>
+        <v>1.354974160206723</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.9825327510917035</v>
+        <v>1.049239119899205</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.9031417847667171</v>
+        <v>0.970767888307158</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.4830566074376108</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.981740481740488</v>
+        <v>3.04941146035442</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.982249263253344</v>
+        <v>5.051249393498303</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.06644800777454</v>
+        <v>4.135726072607262</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2.018627879848353</v>
+        <v>2.088693886137818</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.8775768183586194</v>
+        <v>0.9469696969696955</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.992627986901411</v>
+        <v>-0.9230585511188849</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.139278069663362</v>
+        <v>-2.069565921606738</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.923154906731547</v>
+        <v>-1.853674540682412</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-2.083333333333336</v>
+        <v>-2.014050952936607</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.320978186775733</v>
+        <v>-3.25104156534708</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-2.702488797973899</v>
+        <v>-2.632443082311738</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.386046964825098</v>
+        <v>-1.316301703163013</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.114766081871345</v>
+        <v>-1.044911734164067</v>
       </c>
     </row>
     <row r="13">
@@ -6405,76 +6405,76 @@
         <v>359</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.69919104363381</v>
+        <v>-2.807513780098638</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.641608898111002</v>
+        <v>-1.607935889497661</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2957940418628766</v>
+        <v>-0.2604396181943898</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.661721837144519</v>
+        <v>0.6979155545634228</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.489063268213791</v>
+        <v>-2.423390238318113</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.6305894630064373</v>
+        <v>-0.5651148600201665</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.5464051291735075</v>
+        <v>0.6127971803234544</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2678504836549465</v>
+        <v>0.3345857355703785</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3093665486775805</v>
+        <v>0.3760729174850823</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.185917330058416</v>
+        <v>-0.1182912265179752</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.4686611270099306</v>
+        <v>-0.4013346484229032</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.759208757815998</v>
+        <v>1.82687973642993</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.420232859663116</v>
+        <v>3.489232989908075</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.363221452528485</v>
+        <v>2.432499517361208</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.147187149424333</v>
+        <v>1.217253155713799</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.2076135251882647</v>
+        <v>-0.1382206465771887</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.013016411537755</v>
+        <v>-1.943446975755229</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-2.396551359666454</v>
+        <v>-2.32683921160983</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.344773600634362</v>
+        <v>-1.275293234585227</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.600626740947078</v>
+        <v>-0.5313443605503494</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.979481746045309</v>
+        <v>-1.909545124616656</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.941230673554216</v>
+        <v>-0.871184957892055</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.7263021530950482</v>
+        <v>0.7960474147571333</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.928912345860013</v>
+        <v>0.9987666935672905</v>
       </c>
     </row>
     <row r="14">
@@ -6487,158 +6487,158 @@
         <v>442</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.335520954283531</v>
+        <v>-3.528487562870161</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.878075200938113</v>
+        <v>-2.849497785655657</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.055332226110217</v>
+        <v>-1.914771628984326</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.0541934126065442</v>
+        <v>0.08107796331107409</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.229417948761814</v>
+        <v>-2.286315218039803</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.9110316162980112</v>
+        <v>-0.8455570133117405</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.5526760288950285</v>
+        <v>-0.4862839777450816</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.8312306744135896</v>
+        <v>-0.7644954224981575</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.7897146093909555</v>
+        <v>-0.7230082405834537</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.111061332377581</v>
+        <v>-1.04343522883714</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.51543509693645</v>
+        <v>-1.448108618349423</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.9204031262854855</v>
+        <v>0.9880741048994182</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.28459969060377</v>
+        <v>2.353599820848729</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.063242879569415</v>
+        <v>2.132520944402138</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.4993342649664996</v>
+        <v>0.5694002712559652</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.4893160926519329</v>
+        <v>-0.4199232140408569</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.754631506257866</v>
+        <v>-1.68506207047534</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.633370578461744</v>
+        <v>-1.56365843040512</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.7385143838557227</v>
+        <v>-0.6690340178065881</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.3535067873303177</v>
+        <v>0.4227891677270463</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.1896936216676366</v>
+        <v>-0.1197570002389838</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.8655730421467638</v>
+        <v>0.9356187578089248</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>1.592836896411704</v>
+        <v>1.662582158073789</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.421872932708844</v>
+        <v>2.491727280416121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.01571</t>
+          <t>X &lt; -0.0157</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>540</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.027171313329355</v>
+        <v>-3.182131517101695</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.268556179654382</v>
+        <v>-3.424153323546491</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.226775162259031</v>
+        <v>-3.295779240739108</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.60723514211886</v>
+        <v>-0.5915416297020073</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.268801223439205</v>
+        <v>-2.303422572950666</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.9705254993213117</v>
+        <v>-0.905050896335041</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.07672496470866719</v>
+        <v>-0.01033291355872024</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.7558315008838861</v>
+        <v>0.8225667527993181</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.4269771955361392</v>
+        <v>0.493683564343641</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.7642528958778314</v>
+        <v>0.8318789994182723</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.4830566074376108</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.500259000259007</v>
+        <v>1.56792997887294</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.227619633623711</v>
+        <v>2.296619763868669</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.635892452218989</v>
+        <v>1.705170517051712</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.347331583552055</v>
+        <v>1.417397589841521</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.4609101516919551</v>
+        <v>0.5303030303030312</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.04355391282733478</v>
+        <v>0.02601552295519127</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.03664785626256162</v>
+        <v>0.1063600043191855</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.6231413895647506</v>
+        <v>0.6926217556138852</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.18055555555555</v>
+        <v>1.249837935952279</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>1.19291070211316</v>
+        <v>1.262847323541813</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.857696387211284</v>
+        <v>1.927742102873445</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>2.502841924063787</v>
+        <v>2.572587185725872</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>2.982456140350877</v>
+        <v>3.052310488058154</v>
       </c>
     </row>
     <row r="16">
@@ -6651,158 +6651,158 @@
         <v>638</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-3.049121405750796</v>
+        <v>-3.175008604115192</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.30507156828245</v>
+        <v>-3.431300428111484</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.157461334324516</v>
+        <v>-2.298378163304982</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2066778450098425</v>
+        <v>-0.2763629708951356</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.512386501507237</v>
+        <v>-1.618637452802787</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2421762306218014</v>
+        <v>0.2191014250003889</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7232285938655778</v>
+        <v>0.7896206450155248</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.385112819820378</v>
+        <v>1.45184807173581</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.9564094491063315</v>
+        <v>1.023115817913833</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.279752721722488</v>
+        <v>1.347378825262929</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.083892553101137</v>
+        <v>1.151219031688164</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.058717144924046</v>
+        <v>2.126388123537978</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.81510366938361</v>
+        <v>2.884103799628569</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.123527422612582</v>
+        <v>2.192805487445305</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1.934815619311955</v>
+        <v>2.004881625601421</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>2.059656233196662</v>
+        <v>2.129049111807738</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.612082915223283</v>
+        <v>1.681652351005809</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.820579122952459</v>
+        <v>1.890291271009083</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.253003226323138</v>
+        <v>1.322483592372272</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>2.067006269592476</v>
+        <v>2.136288649989204</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.837285484418977</v>
+        <v>1.90722210584763</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.545029488337491</v>
+        <v>2.615075203999652</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.133284278644076</v>
+        <v>3.203029540306161</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.370822563200058</v>
+        <v>3.440676910907335</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.009922</t>
+          <t>X &lt; -0.009921</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>749</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.409141379119639</v>
+        <v>-2.515019298862434</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.075963587061793</v>
+        <v>-3.179867943612017</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.910946650168846</v>
+        <v>-2.027188777545845</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.4885583879280873</v>
+        <v>-0.5414905972767912</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.65489626373985</v>
+        <v>-1.735356826970559</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2679158793069902</v>
+        <v>0.2579120666279309</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.2961178380406793</v>
+        <v>0.3625098891906262</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.6851199348452113</v>
+        <v>0.7518551867606433</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3261019544739909</v>
+        <v>0.3928083232814927</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.753868679886132</v>
+        <v>0.8214947834265729</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4941825531429913</v>
+        <v>0.5615090317300186</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.149668088920428</v>
+        <v>1.217339067534361</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.226779006614862</v>
+        <v>1.295779136859821</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.940001634832846</v>
+        <v>2.009279699665569</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.082138486583261</v>
+        <v>2.152204492872727</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>2.143153142346158</v>
+        <v>2.212546020957234</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>2.009059448197235</v>
+        <v>2.078628883979761</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>2.171098729031193</v>
+        <v>2.240810877087817</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.986687846569161</v>
+        <v>2.056168212618296</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>2.440754339118826</v>
+        <v>2.510036719515554</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.16457662705011</v>
+        <v>2.234513248478763</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>2.355644268336746</v>
+        <v>2.425689983998907</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.630419434818876</v>
+        <v>2.700164696480961</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.821500792479632</v>
+        <v>2.89135514018691</v>
       </c>
     </row>
     <row r="18">
@@ -6815,76 +6815,76 @@
         <v>887</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.930589347258106</v>
+        <v>-2.017106911864218</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.432720343818552</v>
+        <v>-2.518224808642771</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.108523878280579</v>
+        <v>-1.204888752058565</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.8076610471670875</v>
+        <v>-0.8456981038510207</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.060191260601506</v>
+        <v>-1.119305338067136</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.254369068301564</v>
+        <v>0.2561102648261269</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.0675387773939633</v>
+        <v>-0.001146726244016349</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5558231498045103</v>
+        <v>0.6225584017199424</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.5973392148271444</v>
+        <v>0.6640455836346462</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7254203767747356</v>
+        <v>0.7930464803151764</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.6615609291211797</v>
+        <v>0.728887407708207</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.833425312004799</v>
+        <v>0.9010962906187316</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.400027667362068</v>
+        <v>1.469027797607026</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.742368714275855</v>
+        <v>1.811646779108578</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.872614476365946</v>
+        <v>1.942680482655412</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.678497524859935</v>
+        <v>1.747890403471011</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>1.995362117069526</v>
+        <v>2.064931552852052</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>2.115857844153503</v>
+        <v>2.185569992210127</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>2.89567886503346</v>
+        <v>2.965159231082595</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>2.969983089064264</v>
+        <v>3.039265469460993</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>3.103220109604081</v>
+        <v>3.173156731032734</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.801785910782208</v>
+        <v>2.871831626444369</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>3.076561077264337</v>
+        <v>3.146306338926422</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>3.226098881175133</v>
+        <v>3.295953228882411</v>
       </c>
     </row>
     <row r="19">
@@ -6897,404 +6897,404 @@
         <v>1045</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.193701157422232</v>
+        <v>-2.261208673850611</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.34008085920965</v>
+        <v>-3.404195340353212</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.051868197878385</v>
+        <v>-2.124796440317056</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.234561032602649</v>
+        <v>-1.26018476651506</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.312749477913783</v>
+        <v>-1.352549821475179</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.07295328595962047</v>
+        <v>-0.06127212712605967</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.4630442983964187</v>
+        <v>-0.3966522472464717</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.311032635032376</v>
+        <v>0.3777678869478081</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.022405159385166</v>
+        <v>1.089111528192667</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.014119987850187</v>
+        <v>1.081746091390627</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5229290157310729</v>
+        <v>0.5902554943181002</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.435222672064782</v>
+        <v>0.5028936506787147</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.6504443722379207</v>
+        <v>0.7194445024828795</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.290331580342318</v>
+        <v>1.359609645175041</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.014175460922246</v>
+        <v>1.084241467211712</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.035072831117795</v>
+        <v>1.104465709728871</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.188060476681791</v>
+        <v>1.257629912464317</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.657239740012351</v>
+        <v>1.726951888068974</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.543219362274307</v>
+        <v>2.612699728323442</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.538875598086122</v>
+        <v>2.608157978482851</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>2.569837868514007</v>
+        <v>2.63977448994266</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.780964152584318</v>
+        <v>2.851009868246479</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>3.055739319066447</v>
+        <v>3.125484580728532</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>3.17118553960659</v>
+        <v>3.241039887313867</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.001246</t>
+          <t>X &lt; -0.001247</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1210</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.353989392549472</v>
+        <v>-2.407294481853015</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-3.059668514119316</v>
+        <v>-3.111426380917585</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.639080029109351</v>
+        <v>-2.695356305129081</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.78262540841822</v>
+        <v>-1.798484861541581</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.065250565343092</v>
+        <v>-2.089450159073415</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.299573555642091</v>
+        <v>-1.279550085863129</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.74186117529942</v>
+        <v>-1.675469124149473</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.111324911727074</v>
+        <v>-1.044589659811642</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.7392303343077486</v>
+        <v>-0.6725239655002468</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6039748359862713</v>
+        <v>-0.5363487324458305</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.9081279655651429</v>
+        <v>-0.8408014869781155</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.9392879847425206</v>
+        <v>-0.8716170061285879</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.4935312693453753</v>
+        <v>-0.4245311391004165</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.3016649398838567</v>
+        <v>-0.2323868750511338</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.2994391541277679</v>
+        <v>-0.2293731478383023</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.0476870111960892</v>
+        <v>0.1170798898071652</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.3268164575430319</v>
+        <v>0.396385893325558</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.8829900662411418</v>
+        <v>0.9527022142977657</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.347047113470481</v>
+        <v>1.416527479519615</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.451446280991732</v>
+        <v>1.520728661388461</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.156179756291301</v>
+        <v>1.226116377719954</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.493447841144558</v>
+        <v>1.563493556806719</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.685578379527513</v>
+        <v>1.755323641189598</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>2.022860180754911</v>
+        <v>2.092714528462189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.001646</t>
+          <t>X &lt; 0.001645</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1418</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.56441676440059</v>
+        <v>-1.607186524371663</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.425904942914471</v>
+        <v>-2.46685198195722</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.420828370396755</v>
+        <v>-2.464204758565586</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.251585623678643</v>
+        <v>-2.296660226917496</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.437792499623704</v>
+        <v>-2.52427212228239</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.333843683513962</v>
+        <v>-1.384499380709627</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.036187953790837</v>
+        <v>-2.047369950595751</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.60952398153789</v>
+        <v>-1.582100070472158</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.003833022298046</v>
+        <v>-0.9371266534905445</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6493186446330625</v>
+        <v>-0.5816925410926217</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7275686864034796</v>
+        <v>-0.6602422078164523</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.9361407281012362</v>
+        <v>-0.8684697494873035</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.7912384345996628</v>
+        <v>-0.722238304354704</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.6599859367482637</v>
+        <v>-0.5907078719155407</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.6136985580140575</v>
+        <v>-0.5436325517245919</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.0891603701698287</v>
+        <v>-0.01976749155875268</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.1527322025415998</v>
+        <v>-0.08316276675907375</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.1654155520260261</v>
+        <v>0.2351277000826499</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.5931043002892977</v>
+        <v>0.6625846663384323</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.8506699576868755</v>
+        <v>0.9199523380836041</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.5895569957975297</v>
+        <v>0.6594936172261825</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.7956893872635291</v>
+        <v>0.8657351029256901</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.7178552448598978</v>
+        <v>0.7876005065219829</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.5713920438142779</v>
+        <v>0.6412463915215554</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.004538</t>
+          <t>X &lt; 0.004536</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1715</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.9753402101617112</v>
+        <v>-1.006220593455133</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.628344539442736</v>
+        <v>-1.658126808653165</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.340339627363306</v>
+        <v>-2.370164699943203</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.860465116279066</v>
+        <v>-1.892258233155751</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.543185555415164</v>
+        <v>-2.602840151583983</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.800732889482127</v>
+        <v>-1.861948560549777</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.017664156667074</v>
+        <v>-2.079328114453979</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.972736227683853</v>
+        <v>-2.034883720930225</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.523294754735801</v>
+        <v>-1.554018588070548</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.481279349654415</v>
+        <v>-1.47959428993628</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.498295373914374</v>
+        <v>-1.463788919411208</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.66083916083916</v>
+        <v>-1.593168182225227</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.678104272100192</v>
+        <v>-1.609104141855234</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.5498107334842</v>
+        <v>-1.480532668651477</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.567716331495866</v>
+        <v>-1.497650325206401</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.147481456699651</v>
+        <v>-1.078088578088575</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.22330009257351</v>
+        <v>-1.153730656790984</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.9443477165697374</v>
+        <v>-0.9089210109618264</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.3783703262326767</v>
+        <v>-0.3433792803871469</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.4245626822157433</v>
+        <v>-0.3896337035193511</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.4429817501058295</v>
+        <v>-0.4077043470098616</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.3440096920458089</v>
+        <v>-0.2739639763836479</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.827252018275054</v>
+        <v>-0.757506756612969</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.9031933575435218</v>
+        <v>-0.8333390098362443</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.00743</t>
+          <t>X &lt; 0.007428</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.550183374766291</v>
+        <v>-1.594938929799227</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.409296920395121</v>
+        <v>-1.454405739040894</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.722133952765404</v>
+        <v>-1.76728931445912</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.257885792769514</v>
+        <v>-1.304008274608336</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.096413011491649</v>
+        <v>-2.162387452802783</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.881978034020342</v>
+        <v>-1.948257684914516</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.675165510517637</v>
+        <v>-1.742064645290448</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.076368803733679</v>
+        <v>-2.142807234106968</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.806395163275255</v>
+        <v>-1.873272570147549</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.626893895670364</v>
+        <v>-1.666032445861596</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.653588316462709</v>
+        <v>-1.664595182113104</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.832330990635043</v>
+        <v>-1.814835626672398</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.852958686794047</v>
+        <v>-1.805343645323653</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.97396426852584</v>
+        <v>-1.926020915344537</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-2.030788131747791</v>
+        <v>-1.931553771158029</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.736781770034092</v>
+        <v>-1.638371668492155</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.619997390926613</v>
+        <v>-1.521284789405364</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.244030412367515</v>
+        <v>-1.174318264310891</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.098959918171914</v>
+        <v>-1.058828489812257</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.31372425916625</v>
+        <v>-1.273589105547046</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.354664497395753</v>
+        <v>-1.364328044597421</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.330167518884664</v>
+        <v>-1.260121803222503</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.557652523170987</v>
+        <v>-1.458680262626999</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.533141828285764</v>
+        <v>-1.434010003287469</v>
       </c>
     </row>
     <row r="24">
@@ -7307,76 +7307,76 @@
         <v>2207</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.284581279510945</v>
+        <v>-1.300613090029621</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.505913970462778</v>
+        <v>-1.521774294492275</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.748636373650939</v>
+        <v>-1.764994312164127</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.174077379389999</v>
+        <v>-1.191941730142851</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.51451034719711</v>
+        <v>-1.548050212045347</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.483236583654623</v>
+        <v>-1.516738361879071</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.507975383300867</v>
+        <v>-1.541954788140885</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.806608822750469</v>
+        <v>-1.840254081579083</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.423198772286881</v>
+        <v>-1.457535947851468</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.447406477393137</v>
+        <v>-1.482224530229765</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.71627944205688</v>
+        <v>-1.725084062860226</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.7690265822905</v>
+        <v>-1.752337371245162</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.807053337219465</v>
+        <v>-1.764047237974808</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.073679500902081</v>
+        <v>-2.004401436069358</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.781954334325988</v>
+        <v>-1.711888328036522</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.594318458538922</v>
+        <v>-1.524925579927846</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.502065389446557</v>
+        <v>-1.432495953664031</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.263674204929053</v>
+        <v>-1.220451188947415</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.247589785652146</v>
+        <v>-1.230906571264363</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.468339374716813</v>
+        <v>-1.451484935130651</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.467815270801303</v>
+        <v>-1.450798871317609</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.634391078596167</v>
+        <v>-1.590776415645067</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.85803004895137</v>
+        <v>-1.788284787289285</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.798040259991474</v>
+        <v>-1.728185912284196</v>
       </c>
     </row>
     <row r="25">
@@ -7389,240 +7389,240 @@
         <v>2455</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.9998912598836966</v>
+        <v>-1.011397275244263</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.232645116584827</v>
+        <v>-1.243936335901566</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.393847343929757</v>
+        <v>-1.405545794820874</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9498089532525071</v>
+        <v>-0.9625629583843107</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.170917625555603</v>
+        <v>-1.194964438216076</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.001878411307594</v>
+        <v>-1.026130630304927</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.305476055360657</v>
+        <v>-1.329608393418141</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.683255290092383</v>
+        <v>-1.706920137742337</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.497142045656261</v>
+        <v>-1.521107200447119</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.800927168285568</v>
+        <v>-1.824772780254222</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.648568714508983</v>
+        <v>-1.649725226999998</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.439659364628866</v>
+        <v>-1.418058854332472</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.303475511948861</v>
+        <v>-1.258032449320133</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.199496820746539</v>
+        <v>-1.130218755913816</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.248423993090057</v>
+        <v>-1.178357986800592</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.182034134603292</v>
+        <v>-1.112641255992216</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.251702663693749</v>
+        <v>-1.205891455190098</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.966608146993444</v>
+        <v>-0.9447297189950206</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.052271808649749</v>
+        <v>-1.054173840307371</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.330193482688394</v>
+        <v>-1.355331283694362</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.262395928346223</v>
+        <v>-1.264048978781673</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.501283774212872</v>
+        <v>-1.478851303719964</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.593107385734804</v>
+        <v>-1.547029173304168</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.587582329891255</v>
+        <v>-1.517727982183978</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.01611</t>
+          <t>X &lt; 0.0161</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2664</v>
+        <v>2665</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.250556901649382</v>
+        <v>-1.258121871436437</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.155884014762897</v>
+        <v>-1.163705848467067</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.456460071048426</v>
+        <v>-1.464313601647355</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.067605927237686</v>
+        <v>-1.076280170713957</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.412302454319075</v>
+        <v>-1.428830405822922</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.353970206636014</v>
+        <v>-1.370535030226485</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.246796381416857</v>
+        <v>-1.263787861043518</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.541849357544635</v>
+        <v>-1.558504127711657</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.442049647312693</v>
+        <v>-1.458851494987528</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.596390575876761</v>
+        <v>-1.613229538331282</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.359442457283677</v>
+        <v>-1.355446510387914</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.8688915874544563</v>
+        <v>-0.865437968513703</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.8862092832752211</v>
+        <v>-0.882692682459485</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.9203702874956434</v>
+        <v>-0.8949043052453334</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.070479485944411</v>
+        <v>-1.06670267203652</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.9028965174725272</v>
+        <v>-0.8993376882598483</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.089975146654865</v>
+        <v>-1.086204896640744</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.9105254137453471</v>
+        <v>-0.9289714709224342</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.9723963837674674</v>
+        <v>-0.9906907703952612</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.101078799249535</v>
+        <v>-1.119130882997801</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.006380521568317</v>
+        <v>-1.002686576174995</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.157382481526113</v>
+        <v>-1.131458830343234</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.048209126987267</v>
+        <v>-1.022478247299048</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.049075391180658</v>
+        <v>-1.001264663077968</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.019</t>
+          <t>X &lt; 0.01899</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2851</v>
+        <v>2852</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.081013156533949</v>
+        <v>-1.049542765605885</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.049686892539967</v>
+        <v>-1.052868170654435</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.217022462851162</v>
+        <v>-1.219420893287541</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.145369094886966</v>
+        <v>-1.182307286662194</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.282330263109756</v>
+        <v>-1.289973659699342</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.250240360626123</v>
+        <v>-1.257999663917957</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.166779092781631</v>
+        <v>-1.174243425674177</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.42581280916238</v>
+        <v>-1.432973306088023</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.260050145941456</v>
+        <v>-1.267351974159624</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.420725378485919</v>
+        <v>-1.427561180468523</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.336130725197151</v>
+        <v>-1.34315967139247</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.071369231746587</v>
+        <v>-1.078459427293012</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.022474221153821</v>
+        <v>-1.064009464731221</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9437501274235913</v>
+        <v>-0.9852557582802248</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.127504217621627</v>
+        <v>-1.168592804607457</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.931672073640442</v>
+        <v>-0.9731934731934757</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.115255646062145</v>
+        <v>-1.156604662812953</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.9196235411853024</v>
+        <v>-0.9610790232318038</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.033147123116052</v>
+        <v>-1.074642533526493</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.211019621583745</v>
+        <v>-1.252496331087862</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.173019897255934</v>
+        <v>-1.214288305958092</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.193313949914057</v>
+        <v>-1.234551234612603</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.14344203088379</v>
+        <v>-1.184861114309172</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.114157133743987</v>
+        <v>-1.135004456620045</v>
       </c>
     </row>
     <row r="28">
@@ -7632,79 +7632,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2956</v>
+        <v>2959</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.005440640393296</v>
+        <v>-1.025152948442035</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.8528160607577746</v>
+        <v>-0.872638336471482</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.098980589049617</v>
+        <v>-1.118340947389953</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.055263815953992</v>
+        <v>-1.074566097408919</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.267556281017789</v>
+        <v>-1.291131576375662</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.095435210646627</v>
+        <v>-1.119223752429292</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.076089616949204</v>
+        <v>-1.09978930543447</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.268494305406932</v>
+        <v>-1.291967949970683</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.174428990185078</v>
+        <v>-1.198014859029293</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.356959225334293</v>
+        <v>-1.380252405447742</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.164523947182353</v>
+        <v>-1.188064648385414</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.9191280417695467</v>
+        <v>-0.9428844370239418</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.7772861822022321</v>
+        <v>-0.801023333774431</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.7429192657700767</v>
+        <v>-0.7666681117421206</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.9098665927017748</v>
+        <v>-0.8996634064647537</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.7334218321137129</v>
+        <v>-0.7571927566871963</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.8476688613904884</v>
+        <v>-0.871314713552394</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.7302263778635165</v>
+        <v>-0.7539860077974794</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.8656574396596071</v>
+        <v>-0.8893245631745401</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-1.064189189189193</v>
+        <v>-1.087695344881702</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-1.013164924036822</v>
+        <v>-1.036650013092604</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-1.103012800678428</v>
+        <v>-1.126406270423864</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.146502381350857</v>
+        <v>-1.169905306766616</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.16879930995735</v>
+        <v>-1.192179016654407</v>
       </c>
     </row>
     <row r="29">
@@ -7714,79 +7714,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3027</v>
+        <v>3031</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.9200230450950642</v>
+        <v>-0.9230998966670683</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.9427177140979737</v>
+        <v>-0.9458171643202675</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.019863526213541</v>
+        <v>-1.02307939593728</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.862495325176873</v>
+        <v>-0.8660266754374248</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.176780115003119</v>
+        <v>-1.183698928212621</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.135641354092336</v>
+        <v>-1.142590830496815</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.134786968894197</v>
+        <v>-1.141858139572136</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.263496404083192</v>
+        <v>-1.2704451958083</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.170655940558525</v>
+        <v>-1.177725204898344</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.366990481666107</v>
+        <v>-1.373922861556004</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.30422409431678</v>
+        <v>-1.31120254691448</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.005316664250522</v>
+        <v>-1.012734813425112</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.7943490104647495</v>
+        <v>-0.8022187195851984</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.8976750303112837</v>
+        <v>-0.9054473352629557</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.8456123485223088</v>
+        <v>-0.8535575758504947</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.7252512980609254</v>
+        <v>-0.7332705136258895</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.7410807079151098</v>
+        <v>-0.7491045609206566</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.6288098863465166</v>
+        <v>-0.6370027196164614</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.6900121333513027</v>
+        <v>-0.6980970264092363</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.7804767403497195</v>
+        <v>-0.7884194317943738</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.6772763165887099</v>
+        <v>-0.6854424296259936</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.7997018495860857</v>
+        <v>-0.8077233328887203</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.8686537459787758</v>
+        <v>-0.8765479652562433</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.8921171445296494</v>
+        <v>-0.8999971478522468</v>
       </c>
     </row>
     <row r="30">
@@ -7796,407 +7796,407 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3084</v>
+        <v>3088</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.8578999702824959</v>
+        <v>-0.860390668558928</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.8219176544582254</v>
+        <v>-0.8244985098525248</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.8918315229675713</v>
+        <v>-0.8945049743219471</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7182030688084353</v>
+        <v>-0.7211915748501099</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.03337791743904</v>
+        <v>-1.039149602786694</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.957272400961827</v>
+        <v>-0.9631224901439097</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.9705823822681126</v>
+        <v>-0.9765164884379445</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.069736002102978</v>
+        <v>-1.075581395348834</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.9777770262558292</v>
+        <v>-0.9837397177847578</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.120116948466197</v>
+        <v>-1.125997639309439</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.117955124345841</v>
+        <v>-1.123808035119083</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.926528252109641</v>
+        <v>-0.9326673926921814</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.7724402000387087</v>
+        <v>-0.7789243184517858</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.9425748321306457</v>
+        <v>-0.948871517235645</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.9036293676998781</v>
+        <v>-0.9100638722663703</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.839219214414122</v>
+        <v>-0.8456659619450235</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.8572663635504583</v>
+        <v>-0.8637110372075583</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.7166782854130886</v>
+        <v>-0.7233222959513412</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.6756728017712845</v>
+        <v>-0.6823468114012314</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.825777202072544</v>
+        <v>-0.8322376713497093</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.7021330296652692</v>
+        <v>-0.7088267121891576</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.791303876824621</v>
+        <v>-0.7978961567453879</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.8863170890822616</v>
+        <v>-0.8927557875484666</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.9107561380754063</v>
+        <v>-0.9171771342792141</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.03057</t>
+          <t>X &lt; 0.03056</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3141</v>
+        <v>3145</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.6715929607444693</v>
+        <v>-0.6736753962602577</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.6738558834049257</v>
+        <v>-0.6759712436415839</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.86329213463938</v>
+        <v>-0.8653169974520623</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.7689279959977284</v>
+        <v>-0.771146743288682</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9584402295339132</v>
+        <v>-0.9630195640543704</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.8803070757695508</v>
+        <v>-0.8849691642710127</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.9389678282181535</v>
+        <v>-0.9436381352889924</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.104701823064076</v>
+        <v>-1.109194176114414</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.9502936113924605</v>
+        <v>-0.9549802893834993</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.040642332155279</v>
+        <v>-1.045297322202494</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.065241849548229</v>
+        <v>-1.069840684294135</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.9457359956884162</v>
+        <v>-0.9505181493312946</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.8147755534415282</v>
+        <v>-0.8198427062059608</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.9858502044332269</v>
+        <v>-0.9907266479421324</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.9278006915802166</v>
+        <v>-0.9328220019760352</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.8537929286510106</v>
+        <v>-0.8588501571374962</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.8104135297504911</v>
+        <v>-0.8155430406845952</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.8013636538175746</v>
+        <v>-0.8065189171284359</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.693639472670661</v>
+        <v>-0.6989126359205002</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.9012321144674118</v>
+        <v>-0.9062257174120987</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.8215082970386618</v>
+        <v>-0.8266627710508772</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.846843978799015</v>
+        <v>-0.8519775595916883</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.8715126979038246</v>
+        <v>-0.8765898998148458</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.865044655573989</v>
+        <v>-0.8701413755701779</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.03346</t>
+          <t>X &lt; 0.03345</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3198</v>
+        <v>3202</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.5229261247821526</v>
+        <v>-0.524568043664523</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.4999801502087919</v>
+        <v>-0.5016785023525046</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.6804357193678712</v>
+        <v>-0.6820264544522345</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.631404743665712</v>
+        <v>-0.6331146711307483</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.9172429508364885</v>
+        <v>-0.9206302345475805</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.8993535811344699</v>
+        <v>-0.9027504592519904</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.9084742879043404</v>
+        <v>-0.9119241599775592</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.0450857822985</v>
+        <v>-1.04839059360863</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.8926617711616487</v>
+        <v>-0.8961551397630103</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.9951216717159213</v>
+        <v>-0.998552178027829</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.045542998085075</v>
+        <v>-1.048891149330466</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9954142430777893</v>
+        <v>-0.9988496196428187</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.8244445839126229</v>
+        <v>-0.8281857138779785</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.9340715267225477</v>
+        <v>-0.9376965093769627</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.8263856322605747</v>
+        <v>-0.8302003662584596</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.774273878251897</v>
+        <v>-0.778108184650236</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.8276297203040812</v>
+        <v>-0.8314109281141384</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.851824886142758</v>
+        <v>-0.8555869800716849</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.6797459498508402</v>
+        <v>-0.6837078012582367</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.8178482198625829</v>
+        <v>-0.8216252927161918</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.655470012246937</v>
+        <v>-0.6594962368672768</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.7754054646405635</v>
+        <v>-0.7792907726987579</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.8572358780271472</v>
+        <v>-0.8609993824220439</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.8209626630679239</v>
+        <v>-0.824780219138745</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.03635</t>
+          <t>X &lt; 0.03634</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3239</v>
+        <v>3243</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.4858933248188535</v>
+        <v>-0.487142275709985</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4061077146300249</v>
+        <v>-0.4074768979992385</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.541021924358553</v>
+        <v>-0.5423194314010118</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5322291757351678</v>
+        <v>-0.5335844151313935</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.7883428645278059</v>
+        <v>-0.7910201934526953</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.8296892378218672</v>
+        <v>-0.8323056579964287</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.8176932056769033</v>
+        <v>-0.820376085565087</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.9867866933472129</v>
+        <v>-0.9892819169812341</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.8357421925673876</v>
+        <v>-0.8384220219055933</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.9466464449016172</v>
+        <v>-0.9492420049142822</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.9622078452069189</v>
+        <v>-0.9647684291268774</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.9162054494259877</v>
+        <v>-0.918842507899555</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.8538618478577717</v>
+        <v>-0.8566502855292271</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.9649077940106281</v>
+        <v>-0.9675760075238955</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.8976966959589845</v>
+        <v>-0.9004922557236057</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.8695487334327794</v>
+        <v>-0.8723423095923835</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.8931465738802586</v>
+        <v>-0.8959217989821369</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.9183826750391546</v>
+        <v>-0.9211356353648128</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.7765937339681557</v>
+        <v>-0.7795092423791843</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.8797795251310561</v>
+        <v>-0.8825577797511031</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.7571886878381804</v>
+        <v>-0.7601553464109543</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.8148898058932588</v>
+        <v>-0.8177923375762504</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.8304914092695412</v>
+        <v>-0.833358834276865</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.8265041011502703</v>
+        <v>-0.8293834167624823</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.03924</t>
+          <t>X &lt; 0.03923</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3280</v>
+        <v>3283</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2984023624568195</v>
+        <v>-0.2833153529963965</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2539971021031775</v>
+        <v>-0.2388614306925163</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2838959000825909</v>
+        <v>-0.2683645104495724</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2840028188865347</v>
+        <v>-0.2682863535525115</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.511085641837596</v>
+        <v>-0.496306289871228</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.5191857423417687</v>
+        <v>-0.5044427753391574</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.5775169304687893</v>
+        <v>-0.5625214657472739</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.6872195598856266</v>
+        <v>-0.6720500222054611</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.5677960298895854</v>
+        <v>-0.5830632855990814</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.7172285856036567</v>
+        <v>-0.7321691251394142</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.7291106159655669</v>
+        <v>-0.7441152958523887</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.6567096330158293</v>
+        <v>-0.6717148252635283</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.5786871289273563</v>
+        <v>-0.5934834541034064</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.6302338564605137</v>
+        <v>-0.6449323948489507</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.6023773226785849</v>
+        <v>-0.6169392986873419</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.597484008891989</v>
+        <v>-0.6122068451147769</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.6832230921983751</v>
+        <v>-0.6978390306866018</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.7398224667689277</v>
+        <v>-0.7543654216236249</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.5970514059705039</v>
+        <v>-0.6117848407635194</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.6661084043849002</v>
+        <v>-0.6808317053957893</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.6431471040939059</v>
+        <v>-0.6577586141061218</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.7010415097350204</v>
+        <v>-0.715586156893167</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.6825012978536478</v>
+        <v>-0.6971380815633381</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.7404435886464142</v>
+        <v>-0.7550134365365579</v>
       </c>
     </row>
     <row r="35">
@@ -8206,79 +8206,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3303</v>
+        <v>3307</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.3367792530147753</v>
+        <v>-0.3375438101286576</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2950112061094075</v>
+        <v>-0.2958401929472956</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.214340344770072</v>
+        <v>-0.215325653120459</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2494593705603592</v>
+        <v>-0.2504322673009014</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.4473861901036429</v>
+        <v>-0.4491583487739277</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4541147796585534</v>
+        <v>-0.4558723945249596</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4872559776493119</v>
+        <v>-0.4890065330265685</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.5679719651310933</v>
+        <v>-0.5696379707325292</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4490525412530886</v>
+        <v>-0.4508612212607446</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.6630743409157915</v>
+        <v>-0.6646581881758351</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.6729546511068207</v>
+        <v>-0.6745165123689389</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.5728095433977813</v>
+        <v>-0.574504712522284</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.533282487568087</v>
+        <v>-0.5350726880769443</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.4954420214034485</v>
+        <v>-0.4972881973153562</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.4119276757072043</v>
+        <v>-0.4139029507473211</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.3726748679395797</v>
+        <v>-0.3746743452625765</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.4586820318829581</v>
+        <v>-0.4605845351596614</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.5155498536867285</v>
+        <v>-0.5173893109483885</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.4024307363701283</v>
+        <v>-0.404399178363569</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.4394088297550596</v>
+        <v>-0.4413261970723141</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4203177713694046</v>
+        <v>-0.4222819144575212</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.5085276280293627</v>
+        <v>-0.5103895918312276</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.488145431330345</v>
+        <v>-0.4900219772460446</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.5764297209873064</v>
+        <v>-0.5782039090120321</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/ma/ma_ratio_50.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/ma/ma_ratio_50.xlsx
@@ -618,1477 +618,1477 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.04029</t>
+          <t>X ≈ -0.04022</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>6.313940253120144</v>
+        <v>3.575064799132754</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.6395918377378464</v>
+        <v>3.332118559901176</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.555539847585351</v>
+        <v>9.184894218345256</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>17.10059265105738</v>
+        <v>15.69804658799956</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.14383515266485</v>
+        <v>8.327335462330126</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>16.96250739179469</v>
+        <v>15.5893618536603</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>16.19962735355249</v>
+        <v>14.80302010197671</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>15.92757109199231</v>
+        <v>14.50364636105192</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.700995703106216</v>
+        <v>7.524943394807359</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.932585005466386</v>
+        <v>-0.3780683643882696</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-4.434056943383752</v>
+        <v>-0.1068036305316156</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-4.71317022361567</v>
+        <v>-0.3823904544205874</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-5.833521848495913</v>
+        <v>-1.493491316656268</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.055813889011262</v>
+        <v>-1.741610403298345</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-6.713445790112878</v>
+        <v>-2.42198561892949</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.527962886786888</v>
+        <v>5.262725483184738</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-6.257569277647391</v>
+        <v>-1.967021585586458</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-6.364080201795126</v>
+        <v>-2.100328002164119</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-6.150273776703706</v>
+        <v>-1.886822269510532</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.6930141746817853</v>
+        <v>5.461013978300869</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-6.50921823806835</v>
+        <v>-2.240624931516933</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.07564437598959728</v>
+        <v>4.821983021732613</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>7.014797829722355</v>
+        <v>12.20759822129981</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.2745327102803756</v>
+        <v>4.906183987077007</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.03739</t>
+          <t>X ≈ -0.03734</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>29</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-15.60116134110639</v>
+        <v>-15.5036289573971</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-2.237974137010902</v>
+        <v>-2.05087345951867</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2415885779711999</v>
+        <v>0.1286813162661673</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.903424662391267</v>
+        <v>6.393794858728214</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9.000253723250253</v>
+        <v>9.551173345162866</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.188016123384955</v>
+        <v>9.709111921855104</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.422887465970582</v>
+        <v>8.921104687952536</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.148542118769072</v>
+        <v>8.620022893997785</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.19279026595521</v>
+        <v>8.750429327912819</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>14.2932041912909</v>
+        <v>14.82813998132515</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.136303475013</v>
+        <v>11.66930276176481</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>7.426298656431513</v>
+        <v>7.961560744698701</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>9.746382971155391</v>
+        <v>10.28981666017692</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>9.52883475147263</v>
+        <v>10.04527193735021</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>12.31476375746855</v>
+        <v>12.80735787458458</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>9.471521368078015</v>
+        <v>9.931009410780888</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>9.341322281304485</v>
+        <v>9.830583483290219</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>5.797613823946719</v>
+        <v>6.258858248012473</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>2.572113583808047</v>
+        <v>3.031849866634175</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>2.759429443033476</v>
+        <v>3.246876658430324</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>2.218466744660837</v>
+        <v>2.681024028156742</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-1.302824375520395</v>
+        <v>-0.8396331851386876</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-1.028744227792707</v>
+        <v>-0.596436224659648</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-1.10477763454643</v>
+        <v>-0.7588406434656534</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.0345</t>
+          <t>X ≈ -0.03445</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.023151383723324</v>
+        <v>9.722539737867031</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10.23898922881294</v>
+        <v>6.169723012708047</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>19.45811071346846</v>
+        <v>14.86129677165346</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.105870888245505</v>
+        <v>7.64973672510515</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.224385933472675</v>
+        <v>4.064932778933162</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>18.61736051641967</v>
+        <v>20.79630635339546</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>21.40800969248702</v>
+        <v>23.32784251074884</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>10.47617163660216</v>
+        <v>13.08010012367994</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>10.52118440057036</v>
+        <v>13.2119139059456</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>9.755073212190936</v>
+        <v>12.4235339060492</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>6.474419367204185</v>
+        <v>9.378757575084265</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>13.31526873781361</v>
+        <v>15.74844737624882</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.641162802179061</v>
+        <v>11.32020331805985</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>8.423336008461447</v>
+        <v>11.07604049781789</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>11.33166141186911</v>
+        <v>13.72374318218986</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>11.92807248064696</v>
+        <v>14.28769659325157</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>11.7986964907202</v>
+        <v>14.18866745037273</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>11.69780384643988</v>
+        <v>14.06038507409589</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>11.91720021295441</v>
+        <v>14.27888260611211</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>12.10740952059979</v>
+        <v>14.49736525725865</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>11.56936165788215</v>
+        <v>13.93499143992148</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>11.49715446071408</v>
+        <v>13.86399705334487</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>8.204858236399474</v>
+        <v>10.77938726828037</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>8.131675567422427</v>
+        <v>10.62046970136272</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.03161</t>
+          <t>X ≈ -0.03155</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>36</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>10.17409401986665</v>
+        <v>7.514681798498934</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.191758788009302</v>
+        <v>4.513509983748243</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-5.381394803564568</v>
+        <v>0.5084440466645148</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.331624190843804</v>
+        <v>-2.841677773685518</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-3.665809740201766</v>
+        <v>-3.115436251703315</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.482655291715091</v>
+        <v>-8.486922964616184</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.251603497905982</v>
+        <v>-6.517204167601435</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-12.82111208689307</v>
+        <v>-12.35051520660465</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-12.7832778065819</v>
+        <v>-14.99138422129062</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-13.55650663423818</v>
+        <v>-15.78832323831806</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-16.0536464460872</v>
+        <v>-21.05477950929637</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-10.80164615028099</v>
+        <v>-15.80190467449624</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>1.917627870978436</v>
+        <v>-0.3075479223349049</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.840472411007134</v>
+        <v>-3.324408468233322</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-4.497477818113389</v>
+        <v>-4.005282039695011</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-9.447659145983074</v>
+        <v>-8.988559020376343</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-6.811899136882182</v>
+        <v>-6.322941545686142</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-12.46367482079778</v>
+        <v>-12.00271335656527</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-9.478306559301984</v>
+        <v>-9.018736050239816</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-12.06901868594593</v>
+        <v>-11.58172905596263</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-12.6145270535576</v>
+        <v>-12.15208564203277</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-12.6942166024288</v>
+        <v>-12.23108622592435</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-12.4236669775057</v>
+        <v>-11.9913892176664</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-12.5032450674974</v>
+        <v>-12.1573080764138</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.02871</t>
+          <t>X ≈ -0.02867</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-13.54342916056335</v>
+        <v>-11.52404102026652</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-10.26947581647264</v>
+        <v>-10.17017842182486</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-15.31411689446194</v>
+        <v>-16.22634234975845</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-12.41475987812306</v>
+        <v>-13.61528269910918</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-19.98081126153997</v>
+        <v>-18.70216474386986</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-14.37943131038118</v>
+        <v>-13.74232651628892</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-16.96014394837066</v>
+        <v>-17.74612150943322</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-13.62337278245678</v>
+        <v>-14.84500648061859</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-8.15725226145198</v>
+        <v>-9.905879938523981</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-8.929025253532586</v>
+        <v>-10.70124412028191</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-6.847475461789976</v>
+        <v>-7.220192127716743</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-5.316436570368978</v>
+        <v>-4.284697576702456</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.00170066412327</v>
+        <v>-0.5754098321204069</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-6.659501949058118</v>
+        <v>-5.646502503582788</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-3.691384682134668</v>
+        <v>-3.111424098872469</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-6.726672186434342</v>
+        <v>-4.161383299743093</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-6.86188948734474</v>
+        <v>-4.266135901280101</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-5.153739842676714</v>
+        <v>-1.180269620692329</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-8.570247113960292</v>
+        <v>-4.187228638412506</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-10.20228777873785</v>
+        <v>-5.585286584815549</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-14.380185756132</v>
+        <v>-9.37658446994417</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-12.64352177315323</v>
+        <v>-7.842943192783771</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-14.19067330069758</v>
+        <v>-9.214373018837527</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-17.90728547153781</v>
+        <v>-12.60533675025056</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.02583</t>
+          <t>X ≈ -0.02579</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.484581548383886</v>
+        <v>-2.702029186751631</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.148544277396546</v>
+        <v>3.563762579935883</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5.948360099868154</v>
+        <v>7.204540748026879</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.240737405964715</v>
+        <v>3.359445402133552</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.910140246862696</v>
+        <v>1.458957391888752</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.606732899062713</v>
+        <v>-1.646671152348311</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.8397342551833162</v>
+        <v>-0.8073017633818438</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4.054536231679542</v>
+        <v>3.782004726841912</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2.886503776276939</v>
+        <v>-2.615166013035278</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1636048314145881</v>
+        <v>-0.1442176373923587</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.856857913390606</v>
+        <v>1.759720279506581</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.326853390716025</v>
+        <v>3.117215731946033</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.956755994040243</v>
+        <v>3.640259529437344</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.738133416237481</v>
+        <v>3.394296044522513</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-5.662979233682506</v>
+        <v>-3.822909795042861</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-8.571399792887433</v>
+        <v>-6.534529248850752</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-6.95684362007124</v>
+        <v>-5.004430773904389</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-8.814550149068111</v>
+        <v>-5.138654794291327</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-6.850065412896264</v>
+        <v>-3.289401486734256</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-8.417861800994316</v>
+        <v>-4.713566783540003</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-5.456947078256157</v>
+        <v>-2.006301845199729</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-5.534604650443995</v>
+        <v>-2.082309405070085</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-3.508168131262067</v>
+        <v>1.438047109116361</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-1.830730447614357</v>
+        <v>2.91555166857583</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.02293</t>
+          <t>X ≈ -0.02289</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.8694875261508486</v>
+        <v>-4.142670883662966</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.647148050335915</v>
+        <v>-5.646076724765166</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.4825551300874267</v>
+        <v>-1.865110489445385</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.591243643986004</v>
+        <v>-3.712368915683712</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-7.123102486370605</v>
+        <v>-7.759151285147986</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-11.14202864746451</v>
+        <v>-10.12445418496799</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.509683807257424</v>
+        <v>-3.365846598752213</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.787237585216388</v>
+        <v>-3.670594911125939</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.34509053789008</v>
+        <v>-2.284197369302568</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.517063073755253</v>
+        <v>-3.077238705967552</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.245231340764271</v>
+        <v>-2.806938271297781</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.122053860219431</v>
+        <v>-1.823235325555004</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.839015736319048</v>
+        <v>-1.674052459009076</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-4.463576413738068</v>
+        <v>-3.183310083000414</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-2.311822872131458</v>
+        <v>-1.33963897127515</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-4.528842605192857</v>
+        <v>-3.305102512893619</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-6.068712385662622</v>
+        <v>-4.672634103394657</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.363849282897725</v>
+        <v>-2.280184683994648</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.069070788754587</v>
+        <v>1.724359791460309</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>5.475703665675852</v>
+        <v>5.731500981640934</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>3.528658894598365</v>
+        <v>3.902035467284101</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>6.268936500567385</v>
+        <v>6.357913960443462</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>9.361345782962786</v>
+        <v>9.134177521952758</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>9.288617217322631</v>
+        <v>8.974900081109546</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.02005</t>
+          <t>X ≈ -0.02001</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-6.696889298328827</v>
+        <v>-5.263842824552903</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-8.231149700166675</v>
+        <v>-6.678478755331156</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-9.030385220457198</v>
+        <v>-9.094827988111319</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.56712144193159</v>
+        <v>-0.3386048295473003</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.710156955125356</v>
+        <v>0.5591587039409802</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.048087479615162</v>
+        <v>-0.455890228110988</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-5.212840496798272</v>
+        <v>-3.586888859917124</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-5.49093746770567</v>
+        <v>-3.891702510403029</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-5.451059553538755</v>
+        <v>-4.935663693503955</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.022739745230638</v>
+        <v>-4.55855129122385</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-5.950698818229085</v>
+        <v>-5.460143583882086</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.631423284038945</v>
+        <v>-2.223277340682074</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.551206805596181</v>
+        <v>-2.163346130040786</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.8304315502154935</v>
+        <v>1.106449278771557</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-2.226933333126922</v>
+        <v>-1.918400952193089</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.634397502586111</v>
+        <v>-1.359025561307192</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.5661040171692093</v>
+        <v>-0.2892922740969865</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>1.733822789648563</v>
+        <v>1.925955775886791</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>1.949880410182473</v>
+        <v>2.140508822362875</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>4.543280711557827</v>
+        <v>4.704956256094121</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>7.613901790407716</v>
+        <v>7.665691677299634</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>8.744546879901399</v>
+        <v>8.768565723373094</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>5.408686928137755</v>
+        <v>5.486712347075802</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>8.949231505461093</v>
+        <v>10.03223440724533</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.01715</t>
+          <t>X ≈ -0.01711</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.668021226359876</v>
+        <v>-2.538004121799496</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-6.061517573744617</v>
+        <v>-6.675123151412691</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-9.544981352716924</v>
+        <v>-9.869043140390282</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.613860524589825</v>
+        <v>-4.621899828560807</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.365778104591634</v>
+        <v>-3.920616778283375</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.16783481905081</v>
+        <v>-1.819495023854167</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.121367675436225</v>
+        <v>0.3126836360811538</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>7.933939868008849</v>
+        <v>5.858563360506935</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.948350874863173</v>
+        <v>4.038143622001037</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>9.243120898953691</v>
+        <v>7.149789990296838</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>9.519668642302882</v>
+        <v>7.423582030489158</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>4.163574435577878</v>
+        <v>2.268117907152977</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.029460074877875</v>
+        <v>0.1809996103192475</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2234346515851087</v>
+        <v>-2.020013856535329</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>5.224580128727261</v>
+        <v>3.163924669847077</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>4.80208230575478</v>
+        <v>2.747330575272343</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>7.724307209635285</v>
+        <v>5.578677905632325</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>7.62229225338929</v>
+        <v>5.447707685185861</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>6.821822203491699</v>
+        <v>4.684842745310945</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>4.972557531110482</v>
+        <v>2.942340593239173</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>7.490599032014082</v>
+        <v>5.314760232225197</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>6.397648596248125</v>
+        <v>5.241267692868696</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>6.674407596094838</v>
+        <v>4.50654876289223</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>5.580655159259969</v>
+        <v>4.34595989744092</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.01426</t>
+          <t>X ≈ -0.01423</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.149718309999983</v>
+        <v>-2.516783952684278</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.485886014052355</v>
+        <v>-2.761416492798986</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.183545184219824</v>
+        <v>3.932496502338459</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.455786364483075</v>
+        <v>2.349158103466038</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.131601609114583</v>
+        <v>3.072186065806207</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>6.377091543536402</v>
+        <v>7.200504057254911</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.162632745615383</v>
+        <v>5.418127703984396</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.887188955930199</v>
+        <v>5.115430198733279</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.916317790412933</v>
+        <v>4.251194012151352</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.163709746734213</v>
+        <v>4.4552190106808</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.438587765240598</v>
+        <v>4.728144316783734</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.178129133204834</v>
+        <v>5.449556428834526</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>6.094029086070073</v>
+        <v>6.332643208777959</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>4.859949723737401</v>
+        <v>5.091743545965819</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>5.223334006364915</v>
+        <v>5.410750140371512</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>10.90569308722286</v>
+        <v>10.95809708445242</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>10.77636406334081</v>
+        <v>10.85833997292745</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>11.69383982755977</v>
+        <v>11.72724790756695</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>4.783859146732944</v>
+        <v>4.958287435506136</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>7.00986370230936</v>
+        <v>7.171153755796567</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>5.451439479796655</v>
+        <v>5.60816711859087</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>6.39730709776871</v>
+        <v>6.53417393695657</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>6.674229493825266</v>
+        <v>6.780112101623835</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>5.580655159259969</v>
+        <v>5.620469701362488</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.01137</t>
+          <t>X ≈ -0.01134</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.308862338736773</v>
+        <v>1.318901594249965</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.708897606714899</v>
+        <v>-0.6793498069875596</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4543577833412016</v>
+        <v>0.7085759070984423</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-2.061016707082793</v>
+        <v>-0.7610796895035961</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.39283675694373</v>
+        <v>-1.032144716164204</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.4750105877750883</v>
+        <v>1.75635248518239</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.083180133335091</v>
+        <v>-0.7920102115877796</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.25659255993753</v>
+        <v>-1.976468233866505</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.215297702460802</v>
+        <v>-1.848455108849024</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.193365189948146</v>
+        <v>-1.761172435740143</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.817294219583722</v>
+        <v>-1.490552241432653</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.993240349489611</v>
+        <v>-2.648026919345781</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-7.804689274277777</v>
+        <v>-6.403587152169997</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.9479153469262229</v>
+        <v>2.163371247568769</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>2.986452337077417</v>
+        <v>4.130560089232759</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>2.682136330424207</v>
+        <v>3.809247551667902</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4.347059828536615</v>
+        <v>5.472298797585232</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>4.244162376466456</v>
+        <v>5.341585888090066</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>6.260359800228649</v>
+        <v>7.324744823511452</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>4.650020196580371</v>
+        <v>5.774208677802605</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>4.110302244874759</v>
+        <v>5.209907736362879</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>1.335485905731929</v>
+        <v>2.483778245696236</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.1904397327963281</v>
+        <v>0.959122036622432</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.2660078302603708</v>
+        <v>0.7974608518053969</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.008476</t>
+          <t>X ≈ -0.008454</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.7053322973103135</v>
+        <v>1.196725467161322</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.093613487344385</v>
+        <v>0.9545458519848182</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.261383895770209</v>
+        <v>3.328326371535653</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-2.487812597024153</v>
+        <v>-2.330290807988916</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.218801880189503</v>
+        <v>2.469153909998141</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2409591885906934</v>
+        <v>0.4469408785184612</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.965550828800509</v>
+        <v>-1.79233340201003</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.08318290286185714</v>
+        <v>0.07840090474748251</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.120245863143111</v>
+        <v>2.383876880182669</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.6313161295560832</v>
+        <v>1.592698120882979</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.625895623923746</v>
+        <v>1.864500272514945</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.8148059785631148</v>
+        <v>-0.5897721348260347</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.39594742093432</v>
+        <v>2.660319594288289</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.7326965851745086</v>
+        <v>0.9594094805204563</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.7996113992391471</v>
+        <v>1.007572796844791</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.7742934521927864</v>
+        <v>-0.6153934271776791</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.982621051820033</v>
+        <v>2.192145838152008</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>1.878969562424359</v>
+        <v>2.060333148004389</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>7.881355468383923</v>
+        <v>8.103377475600453</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>5.900613660496418</v>
+        <v>6.134441590921611</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>8.256740358414142</v>
+        <v>8.486786329044435</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>5.288271773670964</v>
+        <v>5.497740263854091</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>5.565152334418514</v>
+        <v>5.743659509700912</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>5.491924014628204</v>
+        <v>5.583973350997745</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.005584</t>
+          <t>X ≈ -0.005566</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-3.611208903699016</v>
+        <v>-3.190573669797715</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-8.34080508745641</v>
+        <v>-7.79538354189706</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-7.258865483035777</v>
+        <v>-6.551762662672694</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3.569482132163131</v>
+        <v>-2.77828592947408</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.645727007883295</v>
+        <v>-1.803782749149903</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.835927701748979</v>
+        <v>-1.029428250251883</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.601804167059591</v>
+        <v>-1.818100122534176</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.9946919013412412</v>
+        <v>-0.250080592557147</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.448870066303904</v>
+        <v>4.252251181712289</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.681905782329366</v>
+        <v>3.462488463530427</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.1907754174293714</v>
+        <v>0.6078745100163374</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.727303646043701</v>
+        <v>-0.9182716827231445</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.476032676395889</v>
+        <v>-2.655066915422452</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.176985905912076</v>
+        <v>-0.3988001222710835</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-3.724111991838981</v>
+        <v>-2.95779436721287</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-2.502019791017567</v>
+        <v>-1.772719365483248</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-3.267706616833031</v>
+        <v>-2.5047113563324</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.8483119345608259</v>
+        <v>-0.1291587408345691</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.629985654792641</v>
+        <v>1.339850025190827</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.1852998893946491</v>
+        <v>0.9269729550280772</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.3558311702393055</v>
+        <v>0.3611462749135512</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.730667250327436</v>
+        <v>3.428495724887782</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>3.006756102178926</v>
+        <v>3.673815850128214</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>2.932760558381787</v>
+        <v>3.513551462369001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.002693</t>
+          <t>X ≈ -0.002678</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-3.306152190681146</v>
+        <v>-3.226255643415421</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.229266707562118</v>
+        <v>-0.4882757748835971</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-6.26901124836558</v>
+        <v>-5.32227320933773</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-5.175625240824921</v>
+        <v>-4.125583004775351</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-6.711437616579047</v>
+        <v>-4.999798320699099</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-8.936465668380919</v>
+        <v>-7.237827727237317</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-9.701443267238574</v>
+        <v>-8.034874597180746</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-9.984377179204039</v>
+        <v>-8.343749107670057</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-11.75469960420938</v>
+        <v>-10.01528207884974</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-10.72125894723403</v>
+        <v>-9.019385427815948</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-9.849340295307378</v>
+        <v>-8.15206484385822</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-9.527546440631895</v>
+        <v>-7.833390330599244</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-7.634073617626576</v>
+        <v>-5.955220273384541</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-10.27175166676689</v>
+        <v>-8.605795013905826</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-8.516532180017009</v>
+        <v>-6.893092382392737</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-6.116512470245489</v>
+        <v>-4.531838720751821</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-5.044607276552263</v>
+        <v>-3.435937959678803</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.943011131324432</v>
+        <v>-2.367676812298356</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-6.148210975596889</v>
+        <v>-4.557162867956642</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-5.35912917024676</v>
+        <v>-4.342994540201502</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-7.718272677035834</v>
+        <v>-6.721190107187816</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-6.586135356333301</v>
+        <v>-6.196381836839159</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-6.919887985419521</v>
+        <v>-5.953756118442996</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-5.180012744265085</v>
+        <v>-3.957843551649333</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.000199</t>
+          <t>X ≈ 0.000209</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.029675684838381</v>
+        <v>2.294174109888601</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.262231374215411</v>
+        <v>0.8418823088167073</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.132230069926365</v>
+        <v>-1.123457407387029</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-5.185324796132001</v>
+        <v>-5.362590363415954</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-5.044890151516903</v>
+        <v>-5.148766326076725</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.993830946450764</v>
+        <v>-2.051110047669184</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-4.198979430719419</v>
+        <v>-3.827184194114245</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.680728444335458</v>
+        <v>-4.626382241556982</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.458539803852418</v>
+        <v>-2.534168011273294</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.8411162150013212</v>
+        <v>-0.8707165737830422</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.3873969092523097</v>
+        <v>0.3854256818337021</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.8447008606875741</v>
+        <v>-0.8762329828523221</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-2.440853945061967</v>
+        <v>-2.485001377692519</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.662524583555566</v>
+        <v>-2.734869355238445</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-2.36150679243886</v>
+        <v>-1.939796213347243</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.8138925848990652</v>
+        <v>-0.3911285248188179</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-2.864507561001332</v>
+        <v>-2.469975085576571</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-3.929896718403626</v>
+        <v>-4.085458965010389</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-3.716426360892001</v>
+        <v>-3.871664249694092</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-2.572079197050684</v>
+        <v>-2.668488459396308</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-2.634066957119906</v>
+        <v>-2.7461660199696</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-3.191284327029649</v>
+        <v>-2.326718102257189</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-4.84005956782012</v>
+        <v>-3.771846749892262</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-7.802390366642697</v>
+        <v>-6.409233268934308</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.00309</t>
+          <t>X ≈ 0.003097</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.847807783880071</v>
+        <v>2.534339092326036</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.175795065094206</v>
+        <v>2.964343473042071</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.947400514589653</v>
+        <v>-0.3077396350188053</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.01172534943790282</v>
+        <v>1.796275952433177</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.003037978781201</v>
+        <v>-1.315474223510222</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.146425032352731</v>
+        <v>-2.514838837190148</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.250774264703722</v>
+        <v>-0.6071329873385025</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-4.201060447209855</v>
+        <v>-2.9387623285429</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-4.491299953687275</v>
+        <v>-3.152291162493327</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-5.742854039667208</v>
+        <v>-4.286836027903071</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-5.275145154711424</v>
+        <v>-3.679787510313673</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-5.024785873383088</v>
+        <v>-3.619521150376002</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-5.81332606673336</v>
+        <v>-4.397089950215367</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.702832616757327</v>
+        <v>-4.309549408739265</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-6.028355252277834</v>
+        <v>-4.655639993439507</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-6.109058330724658</v>
+        <v>-4.775388841067929</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-6.246439394949832</v>
+        <v>-5.221593819572597</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-6.354798587082165</v>
+        <v>-5.357502921708232</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-5.134353563588746</v>
+        <v>-4.126179386131575</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-6.629875993353743</v>
+        <v>-5.612362085397891</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-5.496149398924025</v>
+        <v>-4.145300000974338</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-5.709639657955996</v>
+        <v>-4.699121027721432</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-8.130045551757966</v>
+        <v>-7.176574977817253</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-7.873615437867777</v>
+        <v>-6.998577917684869</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.005982</t>
+          <t>X ≈ 0.005985</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>275</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-5.269938721891442</v>
+        <v>-5.310461140785769</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.186122760594543</v>
+        <v>-0.1546789199910705</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.98713276067059</v>
+        <v>2.202474455731256</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.357906503591167</v>
+        <v>3.04947874231015</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.5761785856576864</v>
+        <v>0.9828093791217185</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.487624045805561</v>
+        <v>-1.539662368875682</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.3525768318288911</v>
+        <v>0.9135931613554362</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.816127938598825</v>
+        <v>-2.272012233206247</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.85818431036769</v>
+        <v>-3.231727812420452</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.825163362151578</v>
+        <v>-2.221768425711097</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.912208150934319</v>
+        <v>-2.31497233735768</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-3.191325971741811</v>
+        <v>-2.229155339175477</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.013329472334327</v>
+        <v>-2.61696243289424</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.683445124328642</v>
+        <v>-3.952910931314328</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-4.621068398078727</v>
+        <v>-4.273701905020154</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-5.117797334592332</v>
+        <v>-4.807382770591531</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-3.806632658764968</v>
+        <v>-3.827675314783072</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-2.826856149199394</v>
+        <v>-2.875853181988603</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-5.515227724930149</v>
+        <v>-5.206735683540728</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-6.78427176926936</v>
+        <v>-6.449835233841817</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-7.333733137167265</v>
+        <v>-6.294954176761827</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-7.409053423616825</v>
+        <v>-6.733753062353479</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-5.826845343748751</v>
+        <v>-5.399209486165958</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-5.180012744265085</v>
+        <v>-4.834075753182773</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.008874</t>
+          <t>X ≈ 0.008875</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.405928256264133</v>
+        <v>1.141515209887665</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.132551063894788</v>
+        <v>-2.335919982832856</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.73580001291095</v>
+        <v>-1.262051955910309</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1602810394699006</v>
+        <v>-0.01159753514116346</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.084227506545005</v>
+        <v>4.808843445649742</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.43897828428058</v>
+        <v>3.111212770576643</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.294903814029837</v>
+        <v>1.400654925819275</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.933997585169891</v>
+        <v>2.028711330416499</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.347929889901714</v>
+        <v>3.541507144407184</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.2028884275047815</v>
+        <v>1.362025526924995</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.269698526478741</v>
+        <v>-1.148369636918815</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.174086788369948</v>
+        <v>-0.03175011965965524</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.378985629962905</v>
+        <v>-0.2118718693138177</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.690011974504671</v>
+        <v>-1.85357365874809</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.3168490485964384</v>
+        <v>1.648892346003947</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.4712126297653256</v>
+        <v>0.8089070419864157</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.6075976064987927</v>
+        <v>0.2374411815874709</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.634482650540754</v>
+        <v>-0.3640830150018246</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.800337325768218</v>
+        <v>-1.551143279094809</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-3.076975420677108</v>
+        <v>-1.806022348129687</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-2.241268191114941</v>
+        <v>-1.441938034026059</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-4.619475734942952</v>
+        <v>-3.386259434486014</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-4.805251148816666</v>
+        <v>-3.609914668833802</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-4.425928119212706</v>
+        <v>-3.3047639434971</v>
       </c>
     </row>
     <row r="24">
@@ -2098,79 +2098,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.558651344071301</v>
+        <v>2.45857218353602</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.222831837827997</v>
+        <v>1.407363819014115</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.785141241783499</v>
+        <v>1.752672641297288</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.072838914774124</v>
+        <v>1.162829095393548</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.937454055597442</v>
+        <v>2.891569492173709</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.326911270852214</v>
+        <v>3.854170148833411</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.5507239793750003</v>
+        <v>1.281754984690693</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5300170747274393</v>
+        <v>0.8133026927560678</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.090069972371438</v>
+        <v>-0.6706579259484897</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-4.867224255994749</v>
+        <v>-3.481371968906544</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.98803761912081</v>
+        <v>0.009203665194448263</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.536853070687201</v>
+        <v>2.553780416234922</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>3.215897373733604</v>
+        <v>3.859793455704107</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.599293799565672</v>
+        <v>7.249402658116288</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>3.537986263621733</v>
+        <v>4.141903203978472</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.530895630719868</v>
+        <v>3.088348798959814</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.7900557294599722</v>
+        <v>1.36315836330958</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.4906745491839</v>
+        <v>2.043917807781874</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.4976750221770132</v>
+        <v>0.6327965530514774</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.5271127119660974</v>
+        <v>0.2822169589767896</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.384841430565892</v>
+        <v>1.183242423385998</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.4981460082570948</v>
+        <v>0.2950717713494058</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.5814005881070514</v>
+        <v>1.351714386709048</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.355177871570703</v>
+        <v>0.783071327378984</v>
       </c>
     </row>
     <row r="25">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-4.206588370985294</v>
+        <v>-3.164484770559206</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2816722369044626</v>
+        <v>0.2684706736439466</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.222509808447327</v>
+        <v>-1.470968287779158</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.4518716966409</v>
+        <v>-2.513626171948829</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-4.226203586677414</v>
+        <v>-4.183846680712726</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-5.449813158050709</v>
+        <v>-5.398060097354239</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.5479974445375078</v>
+        <v>-0.2206737800273046</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.1025225906821845</v>
+        <v>-0.5412711207859076</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.8004523911362398</v>
+        <v>-1.057361458488892</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.7764262927776713</v>
+        <v>0.7188591428340629</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.010678782433125</v>
+        <v>1.91480397298843</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.534247986433911</v>
+        <v>5.337689495821785</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.445649510830819</v>
+        <v>3.289951167055364</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>1.801759900655469</v>
+        <v>1.936884333669539</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.1755264239196634</v>
+        <v>0.3203465738050966</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>1.553346693491335</v>
+        <v>1.348995698698943</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.2844241375769982</v>
+        <v>-0.1544611714688742</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.7692956327247273</v>
+        <v>-0.9269983125927723</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.2629475875775995</v>
+        <v>-0.4283540485584396</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.646663332777656</v>
+        <v>1.181581233709849</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.056498117192575</v>
+        <v>1.544369290468616</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>2.933033108164452</v>
+        <v>2.399439326652875</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>5.112269725408325</v>
+        <v>4.503538928210375</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>5.036437472185106</v>
+        <v>4.341399933920833</v>
       </c>
     </row>
     <row r="26">
@@ -2262,735 +2262,735 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.89451309806833</v>
+        <v>1.853387755440231</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.4917197161698894</v>
+        <v>0.5491092749840476</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.236720555380252</v>
+        <v>1.894014984569253</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.74529553219935</v>
+        <v>-2.92501019318815</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.6457060399569272</v>
+        <v>-0.04947599924016544</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.3054235329100194</v>
+        <v>-0.4062851154835201</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.0652299412506494</v>
+        <v>-0.6773290053850332</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.3067565244973451</v>
+        <v>-0.4856657267017255</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.419264556018497</v>
+        <v>0.1765967054034192</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.167589041010665</v>
+        <v>-0.119439267694105</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.220131044040052</v>
+        <v>-2.152774007243998</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.15765590864288</v>
+        <v>-4.741897911245694</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-3.693063363950621</v>
+        <v>-4.300002666132308</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.312868431588718</v>
+        <v>-2.956955668199214</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-2.648528486508937</v>
+        <v>-3.32759428174748</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-2.047372458764869</v>
+        <v>-2.424805753514292</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-2.185050210076298</v>
+        <v>-2.199689716312022</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.419684757019688</v>
+        <v>-1.800658927856631</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-2.273312092672874</v>
+        <v>-2.650026487944942</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-3.155984999282381</v>
+        <v>-3.499269830119999</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-4.233290525537186</v>
+        <v>-4.598629225117726</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-2.704858412080014</v>
+        <v>-3.078047066221949</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-3.499902416175459</v>
+        <v>-3.898242368177605</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-3.040975311109975</v>
+        <v>-3.52846646885002</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.02044</t>
+          <t>X ≈ 0.02042</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3698190760487918</v>
+        <v>-1.301004153154693</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.968301321863073</v>
+        <v>3.080954972340777</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.595702833579701</v>
+        <v>0.8809345917895612</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1.817328253389398</v>
+        <v>1.210930982046584</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.322200536914941</v>
+        <v>-1.849459609551893</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>2.603083406191843</v>
+        <v>2.018232373871264</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.8965552830491532</v>
+        <v>0.295460767282286</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.487502716800691</v>
+        <v>1.826519159852502</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.6598310202107243</v>
+        <v>1.032049480471365</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1130846558257659</v>
+        <v>0.221888637809343</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.964713304093166</v>
+        <v>3.277192435482434</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.68596390064517</v>
+        <v>3.009428823162828</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.235699030050732</v>
+        <v>7.099122243630923</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.08004071435181</v>
+        <v>5.924962256271876</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>6.291056295275929</v>
+        <v>7.094659726238667</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>5.016284338714243</v>
+        <v>5.804111893206482</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>6.751526080241504</v>
+        <v>7.552083333333321</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>4.777526497915588</v>
+        <v>5.567347376319873</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.058838439587532</v>
+        <v>4.85588367753968</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>3.311104810303263</v>
+        <v>4.144544196672783</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>3.703138081589572</v>
+        <v>4.503025621217972</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>1.758133241675857</v>
+        <v>2.576011247410889</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.7711303635991555</v>
+        <v>0.04186795491143158</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-2.716121495327108</v>
+        <v>-1.97212289122988</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.02334</t>
+          <t>X ≈ 0.02332</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.303597331012476</v>
+        <v>2.79540144090349</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-4.492758915927141</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.919690372520563</v>
+        <v>2.703251207533341</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.762291908633372</v>
+        <v>7.744651825626576</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.259834769419435</v>
+        <v>3.243741572851178</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-2.108754600038743</v>
+        <v>-2.233127638052146</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.880703283929094</v>
+        <v>-3.028209650284865</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.3811369509044269</v>
+        <v>-0.5162286852427371</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3396497689897231</v>
+        <v>-0.388299775558707</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.112565445026178</v>
+        <v>-1.184351270778002</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.394061358419769</v>
+        <v>-6.545919073075126</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-3.89503298409003</v>
+        <v>-4.005599619095634</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.8515283842794759</v>
+        <v>-0.8951396238703424</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-6.628162816281666</v>
+        <v>-6.77717650220491</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>1.04702721947119</v>
+        <v>0.9913733412621468</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.2525252525252526</v>
+        <v>0.1442266558565066</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.285274782214444</v>
+        <v>4.265698356807547</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>4.180434078393262</v>
+        <v>4.132814251645911</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>7.174103237095444</v>
+        <v>7.164177887242502</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>11.52761571373007</v>
+        <v>11.60411644497746</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>13.76284732354177</v>
+        <v>13.85357335204735</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>12.29811247324374</v>
+        <v>12.36996012586668</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>11.18369829683702</v>
+        <v>11.20514390691975</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>11.10786604361375</v>
+        <v>11.04300491263029</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.02622</t>
+          <t>X ≈ 0.0262</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.499503763761012</v>
+        <v>3.353924996027338</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.67349889523576</v>
+        <v>6.556294022392429</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.989865811117056</v>
+        <v>7.025737851535375</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7.031297756586589</v>
+        <v>8.157473583761593</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.695507284039373</v>
+        <v>7.881915443662308</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>8.636859435048976</v>
+        <v>9.762986980694826</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.864910751158568</v>
+        <v>8.967904968462051</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.34108527131788</v>
+        <v>10.38712245608791</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.382572453232626</v>
+        <v>10.51505136577217</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>12.1184287070206</v>
+        <v>13.1672757326217</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.883716419357917</v>
+        <v>9.991234885157112</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.341809121173135</v>
+        <v>4.542239137582271</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.4642610894047863</v>
+        <v>1.703209089097072</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.265589716866366</v>
+        <v>-1.993300834404998</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-3.923733014446981</v>
+        <v>-2.675455216290011</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-6.838118022328494</v>
+        <v>-5.562427059539367</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-6.972035159305968</v>
+        <v>-5.666307471264375</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-5.322489898214918</v>
+        <v>-4.075053645391492</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.1565593774462997</v>
+        <v>1.311822374857734</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-3.165366742410292</v>
+        <v>-1.9218670421523</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-1.953526945463992</v>
+        <v>-0.765173612498451</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.2749869419608615</v>
+        <v>0.8838017965806984</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-1.754898194391082</v>
+        <v>-0.5967016491753085</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.830730447614357</v>
+        <v>-0.7588406434647723</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.02912</t>
+          <t>X ≈ 0.02908</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>9.517047623410136</v>
+        <v>8.957373271889402</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.427884860148048</v>
+        <v>6.92575215047124</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7267079163802066</v>
+        <v>0.3139151914368128</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.495018032887138</v>
+        <v>-3.849915578799937</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.186735354214711</v>
+        <v>3.017383423957767</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.373701540312091</v>
+        <v>3.174317029955851</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.8473668915096084</v>
+        <v>0.5935207320089546</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.939616483068129</v>
+        <v>-3.282828282828333</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.6106426286711368</v>
+        <v>0.4165291982842874</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>3.346498882459152</v>
+        <v>3.191906274493618</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.8661725597089</v>
+        <v>1.678427003383717</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.921348773563714</v>
+        <v>-2.169583522516248</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.044510840419932</v>
+        <v>-3.28447563996702</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.265589716866423</v>
+        <v>-3.532709701400073</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-2.16934704953475</v>
+        <v>-2.429149797570894</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-1.574960127591758</v>
+        <v>-1.867845778751288</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.799894665255387</v>
+        <v>1.599702380952372</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-5.322489898214975</v>
+        <v>-5.676038867066367</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-1.597826587466088</v>
+        <v>-1.890148068492124</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-4.919752707322566</v>
+        <v>-5.246990194861652</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-7.216684840200926</v>
+        <v>-7.600148981956622</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-3.783758871785423</v>
+        <v>-4.103882932483394</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.0005122294788506565</v>
+        <v>-0.2888198757764471</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>1.678041482210148</v>
+        <v>1.334755415648324</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.032</t>
+          <t>X ≈ 0.03198</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7.762661658497862</v>
+        <v>8.526338789130783</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>9.1822708250603</v>
+        <v>10.00456988446137</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>9.498637740941611</v>
+        <v>10.4740137136043</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.031297756586646</v>
+        <v>8.157473583761544</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.432349389302459</v>
+        <v>2.709501650558778</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.889456354424624</v>
+        <v>-0.5818406055119993</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.8473668915094521</v>
+        <v>2.071353244324165</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.323541411668707</v>
+        <v>3.490570731950093</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.365028593583347</v>
+        <v>3.618499641634166</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.592112917546977</v>
+        <v>2.822448146414807</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1117865947965129</v>
+        <v>1.370545229984607</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-3.675734738475988</v>
+        <v>-2.354312586555558</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.290124875507502</v>
+        <v>-0.02092884193741895</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.997568177870448</v>
+        <v>3.179112958698468</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4.848196810114423</v>
+        <v>5.945234438882359</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>3.688197767145134</v>
+        <v>4.782400526667587</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-1.708877264569232</v>
+        <v>-0.4938936781609726</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-3.568103933302588</v>
+        <v>-2.350915714357001</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.1565593774462428</v>
+        <v>1.31182237485779</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>3.852177117238831</v>
+        <v>4.974684681985735</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>8.572788844009686</v>
+        <v>9.579653973708403</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>3.2337849878637</v>
+        <v>4.332077658649716</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.0005122294788080239</v>
+        <v>1.127436281859076</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>1.678041482210205</v>
+        <v>2.689435218604139</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.03489</t>
+          <t>X ≈ 0.03487</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>41</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.456713862177793</v>
+        <v>2.554934247499162</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.999985844315809</v>
+        <v>7.187076192283122</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.4400155757726</v>
+        <v>10.81043087087932</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.28803716608595</v>
+        <v>7.779004281827191</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.391271083782655</v>
+        <v>9.942470531971836</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.700188489392119</v>
+        <v>5.221355357482004</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.367264195745705</v>
+        <v>6.865297735493222</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.650028360748728</v>
+        <v>4.121352901840702</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.69151554266346</v>
+        <v>4.249281811524838</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.918599866626941</v>
+        <v>3.453230316305472</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.631683899032765</v>
+        <v>6.164489721153707</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5.352934495584769</v>
+        <v>5.88790776668241</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-3.087300742003052</v>
+        <v>-2.544057521500065</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.308379618449685</v>
+        <v>-2.792291582933217</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-6.405547306274102</v>
+        <v>-5.913470355062131</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-8.250184774575018</v>
+        <v>-7.791190726486377</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-5.945077521308583</v>
+        <v>-5.456046747967477</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-6.049918225129765</v>
+        <v>-5.588930853129078</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-8.273051234449348</v>
+        <v>-7.813493016227213</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-5.647181034237413</v>
+        <v>-5.15988218092432</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-8.628751592447351</v>
+        <v>-8.166351072548963</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-3.826548773368643</v>
+        <v>-3.363464814016439</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>1.325974719601213</v>
+        <v>1.758218451749741</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-1.188881923865971</v>
+        <v>-0.8429449327836309</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.03778</t>
+          <t>X ≈ 0.03775</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>40</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>16.35915288656803</v>
+        <v>16.4573732718894</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>13.52437608821823</v>
+        <v>13.71146643618555</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>22.08635703918723</v>
+        <v>22.45677233429395</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>21.37340301974449</v>
+        <v>21.86437013548573</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>23.53761254719717</v>
+        <v>24.08881199538635</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>26.22457873329458</v>
+        <v>26.74574560138446</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>20.45263004940424</v>
+        <v>20.95066358915176</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>25.17441860465115</v>
+        <v>25.64574314574313</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>20.21590578656587</v>
+        <v>20.77367205542725</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>16.94299011052938</v>
+        <v>17.47762056020791</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>17.2170497526913</v>
+        <v>17.74985557481224</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>19.43830034924331</v>
+        <v>19.97327362034095</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>20.81513828238719</v>
+        <v>21.35838150289018</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>25.5940594059406</v>
+        <v>26.11014744145707</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>22.43591610836</v>
+        <v>22.92799305957197</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>20.53030303030303</v>
+        <v>20.98929707839167</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>15.39638589332556</v>
+        <v>15.88541666666666</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>12.79154518950438</v>
+        <v>13.25253256150506</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>13.00743657042867</v>
+        <v>13.46699478865081</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>15.6942823803967</v>
+        <v>16.18158123370979</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>7.651736212430698</v>
+        <v>8.114136732329086</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>7.575890251021598</v>
+        <v>8.038974210373802</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>10.35036496350365</v>
+        <v>10.78260869565218</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>5.274532710280376</v>
+        <v>5.620469701362715</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.04068</t>
+          <t>X ≈ 0.04064</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-7.807513780098638</v>
+        <v>-10.06436585854541</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-8.142290578448481</v>
+        <v>-5.962446607292762</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.086357039187192</v>
+        <v>10.17416363864178</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2.206736353077844</v>
+        <v>5.233935352877005</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.037612547197213</v>
+        <v>9.306203299734221</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>6.224578733294628</v>
+        <v>9.463136905732334</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.619296716070899</v>
+        <v>8.668054893499587</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.50775193798452</v>
+        <v>12.71096053704755</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>17.71590578656587</v>
+        <v>17.18671553368815</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>8.609656777196037</v>
+        <v>7.695011864555767</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.88371641935796</v>
+        <v>7.967246879160044</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>12.77163368257665</v>
+        <v>16.38631709860181</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.481804949053846</v>
+        <v>10.92359889419455</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>19.76072607260726</v>
+        <v>19.37101700667449</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>27.4359161083601</v>
+        <v>27.3845147987025</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>32.19696969696973</v>
+        <v>32.29364490447863</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>32.06305255999222</v>
+        <v>32.18976449275362</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>31.95821185617103</v>
+        <v>32.05688038759205</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>28.00743657042876</v>
+        <v>32.27134261473786</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>32.36094904706346</v>
+        <v>32.48592905979685</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>31.81840287909736</v>
+        <v>31.91848455841607</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>27.5758902510216</v>
+        <v>27.4954959495042</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>27.85036496350365</v>
+        <v>32.08695652173913</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>23.60786604361368</v>
+        <v>27.57699144049315</v>
       </c>
     </row>
   </sheetData>
@@ -3180,1477 +3180,1477 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.04173</t>
+          <t>X &gt; -0.04167</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3307</v>
+        <v>3331</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1573636299484846</v>
+        <v>-0.05425463508734651</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.2357620914153102</v>
+        <v>-0.0157927347062099</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2754218069666194</v>
+        <v>0.08803725076173663</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.3706607013255478</v>
+        <v>-0.04028519128240049</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3288937666933478</v>
+        <v>0.08881199538640061</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.4859475824948873</v>
+        <v>-0.06598924483827062</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.5190907688869757</v>
+        <v>-0.06785492936676718</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.5696379707325292</v>
+        <v>-0.1467576011944161</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.5712706131933203</v>
+        <v>-0.09154013823682305</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.5141011270496705</v>
+        <v>-0.03359020212393204</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.493793620802677</v>
+        <v>0.01660198629549114</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.5443751554267777</v>
+        <v>0.02636964187848889</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.4446567748762291</v>
+        <v>0.09566456692368064</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.5274359211622084</v>
+        <v>0.04459820470160736</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.3837461353070282</v>
+        <v>0.2184122212486557</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.4350061703002837</v>
+        <v>0.1686921068433023</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.2795344446346135</v>
+        <v>0.2622890453365301</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.3061004488898362</v>
+        <v>0.267066574091217</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-0.253432994788696</v>
+        <v>0.3195127742623427</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.3507191297210568</v>
+        <v>0.2520460013260148</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.2410130322822894</v>
+        <v>0.392181123450861</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.3290659290932396</v>
+        <v>0.3349538083335943</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.338873246895389</v>
+        <v>0.326426222662981</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.4572483601762301</v>
+        <v>0.212183901302673</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.03884</t>
+          <t>X &gt; -0.03878</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3292</v>
+        <v>3317</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1868501300232168</v>
+        <v>-0.06957283589502339</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2339220409308496</v>
+        <v>-0.0299232014305133</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2974340866805605</v>
+        <v>0.04964231631911531</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.450268477840055</v>
+        <v>-0.1067116745232681</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.3766127623769364</v>
+        <v>0.05403981313219219</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.5654514781857642</v>
+        <v>-0.1320654930682892</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.5952696181690484</v>
+        <v>-0.1306201540995957</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.6448075138494431</v>
+        <v>-0.2085922878002151</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.5861806966515459</v>
+        <v>-0.1236868881501891</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5252494538989296</v>
+        <v>-0.03213626957293059</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.4758398085794937</v>
+        <v>0.01712284207950887</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.525380038165892</v>
+        <v>0.02809488798888538</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.4201024078943689</v>
+        <v>0.1023718875055621</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.5022458635930178</v>
+        <v>0.05213722204017301</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.3549048549844045</v>
+        <v>0.2295564991390648</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.4393939393939377</v>
+        <v>0.1471918152337821</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.2522955252861436</v>
+        <v>0.2716982551143161</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.2784972604653007</v>
+        <v>0.2770585922002198</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.2265640361833761</v>
+        <v>0.3288250114082061</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.3554749011566685</v>
+        <v>0.2300606073924456</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.2124519514539784</v>
+        <v>0.4032933588351071</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.3309099918442158</v>
+        <v>0.3160154878670269</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.3723802536235894</v>
+        <v>0.2762795817281258</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.4605827210683486</v>
+        <v>0.1923720227374517</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.03595</t>
+          <t>X &gt; -0.03589</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3263</v>
+        <v>3288</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.04985502578741574</v>
+        <v>0.06655478804766091</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.2161109741866483</v>
+        <v>-0.01209851849725396</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2979304151367614</v>
+        <v>0.04894519618576254</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.506737096003306</v>
+        <v>-0.164045825820196</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.4599499147162476</v>
+        <v>-0.02972444247269834</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.652135683041891</v>
+        <v>-0.2188641989785012</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.6754187310835604</v>
+        <v>-0.2104559267332675</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.7229586445101646</v>
+        <v>-0.2864602440873654</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.6642040364969688</v>
+        <v>-0.201956161345386</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.656948858039442</v>
+        <v>-0.1632031829780445</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.5790430434014979</v>
+        <v>-0.08564881779605571</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.5960507957948593</v>
+        <v>-0.04187789481056825</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.5104573193232511</v>
+        <v>0.01251912035000657</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.5913973615510031</v>
+        <v>-0.03600173986494326</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.4675068745250428</v>
+        <v>0.1186209030660947</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.527477464958352</v>
+        <v>0.06089902013924586</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.3375590608028816</v>
+        <v>0.1873893525543693</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.3324988606638755</v>
+        <v>0.2242994103210947</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.2514373585798637</v>
+        <v>0.3049844637191654</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.383158697044351</v>
+        <v>0.2034524366259873</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.2340568065527648</v>
+        <v>0.3832038851701682</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.3222720766966276</v>
+        <v>0.3262082529269961</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.366546801202233</v>
+        <v>0.2839768926725483</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.4548574215002006</v>
+        <v>0.2007616721656404</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.03305</t>
+          <t>X &gt; -0.033</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3235</v>
+        <v>3258</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.1110742466425307</v>
+        <v>-0.02235851719929371</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3066033407041076</v>
+        <v>-0.06902136869251052</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.4689255160953252</v>
+        <v>-0.08744846473014434</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.5812820801019072</v>
+        <v>-0.2359959413904136</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.5004943981008836</v>
+        <v>-0.06742846845249062</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.8189195759584038</v>
+        <v>-0.4123740567351746</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.8665581424776789</v>
+        <v>-0.4271990062680899</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.8198908385970682</v>
+        <v>-0.4095409104572312</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.7610172903572092</v>
+        <v>-0.3254724603075516</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.7470683690027897</v>
+        <v>-0.2791031561735053</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.6400931044515588</v>
+        <v>-0.1727980479330853</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.7164578891305737</v>
+        <v>-0.1872768383746504</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.5896676325850905</v>
+        <v>-0.09160320191251259</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.6694228744908344</v>
+        <v>-0.1383225707828331</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.569632596942057</v>
+        <v>-0.00665646598660885</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.6352843887533979</v>
+        <v>-0.07010279913435369</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.4426023855146681</v>
+        <v>0.05846413986727583</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.4366251282987719</v>
+        <v>0.09689530660309487</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.3567609604354942</v>
+        <v>0.1763113684853437</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.4912687156205635</v>
+        <v>0.07183261323158519</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.3362193156730697</v>
+        <v>0.2584176277599326</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.4245731410080609</v>
+        <v>0.2015508974903639</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.4407351601057385</v>
+        <v>0.1873340715343517</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.5291767178494524</v>
+        <v>0.1048159260404375</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.03016</t>
+          <t>X &gt; -0.03011</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3199</v>
+        <v>3222</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2268185597386037</v>
+        <v>-0.1065712581568192</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2966422290745427</v>
+        <v>-0.1202228363175522</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4136429608127656</v>
+        <v>-0.09410648161723856</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5503310591620121</v>
+        <v>-0.2068821779010719</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4648734689618905</v>
+        <v>-0.03337251556701659</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.7889431815328862</v>
+        <v>-0.3221556331834208</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.8284644779589456</v>
+        <v>-0.359154255862137</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.6848348945712317</v>
+        <v>-0.2761222032377049</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.6257245805778737</v>
+        <v>-0.161607524430643</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.6029171412602281</v>
+        <v>-0.1058157809540177</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.4666364241455625</v>
+        <v>0.0605201806855078</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.6029640543692736</v>
+        <v>-0.01281172288724974</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.6178835244664</v>
+        <v>-0.08919041174019782</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.6337374154990982</v>
+        <v>-0.1027238456716475</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.5254305250564215</v>
+        <v>0.03802091472521596</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.5361141820449618</v>
+        <v>0.02954475641024601</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.3709253980031946</v>
+        <v>0.1297647620522326</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.3012785234441466</v>
+        <v>0.2320864648507879</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.2541114944901466</v>
+        <v>0.2790493284711033</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.3609783127034873</v>
+        <v>0.2020400061834735</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.1980451742026546</v>
+        <v>0.3970824687632017</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.2864965031177391</v>
+        <v>0.3404630441206962</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.3058850364963561</v>
+        <v>0.3234091920840783</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.3944263394226581</v>
+        <v>0.2418228981348989</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.02727</t>
+          <t>X &gt; -0.02723</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3144</v>
+        <v>3160</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.006137414512465966</v>
+        <v>0.1174423890744549</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1221810817122915</v>
+        <v>0.07695983656265071</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.1529794537037645</v>
+        <v>0.2224120702260421</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3427790282959648</v>
+        <v>0.05619403485680152</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1234687047787588</v>
+        <v>0.3329139142287971</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.5511960927648616</v>
+        <v>-0.05884848294528666</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.546262706052886</v>
+        <v>-0.01801755658321014</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.4584927877538973</v>
+        <v>0.009722994609639102</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.4939707566440106</v>
+        <v>0.02957756723827032</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.4572632143597914</v>
+        <v>0.1020692054505119</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3550123315659093</v>
+        <v>0.2033695993946623</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.5205082692611356</v>
+        <v>0.07100375905469036</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.6111691661072598</v>
+        <v>-0.07965066361881412</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.528324867997263</v>
+        <v>0.006046495084831349</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.4700464669650444</v>
+        <v>0.09981382321985421</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.4278187971081309</v>
+        <v>0.1117718258664269</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.257374817559878</v>
+        <v>0.2160134459530596</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.2163913184321302</v>
+        <v>0.2597972488076508</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.1086320227754882</v>
+        <v>0.366678832884638</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.1888180007976743</v>
+        <v>0.3155888190448479</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.05005206880183977</v>
+        <v>0.5888442884467011</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.07032716792309657</v>
+        <v>0.5010235462371782</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.0629895674979366</v>
+        <v>0.5105428936907686</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.08806270956694817</v>
+        <v>0.4938874228816985</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.02438</t>
+          <t>X &gt; -0.02434</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3087</v>
+        <v>3099</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.08905642354552867</v>
+        <v>0.1729402161558937</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1641089552041066</v>
+        <v>0.008326416960926508</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2656378128076184</v>
+        <v>0.08497746249908289</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4458760275680334</v>
+        <v>-0.008826401865981381</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.216411921572913</v>
+        <v>0.3107491345781881</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.5910412344992935</v>
+        <v>-0.02759414837490937</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.5718544866782338</v>
+        <v>-0.00248146861460441</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.5418237414654996</v>
+        <v>-0.06452972745108099</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.4497937621123995</v>
+        <v>0.08163608882480844</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.4626854779904548</v>
+        <v>0.1069170587623631</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.3958534731151531</v>
+        <v>0.1727347521901379</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.5915479889302944</v>
+        <v>0.01104282638402765</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.6955137511828653</v>
+        <v>-0.1528725164024323</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.607103009299955</v>
+        <v>-0.06064702621743123</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.3741614110198128</v>
+        <v>0.1770278086067592</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.2774514123464016</v>
+        <v>0.2425960806446525</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.1336722837914408</v>
+        <v>0.3187714638334356</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.05763036820658129</v>
+        <v>0.3660591315533779</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.01584536732391939</v>
+        <v>0.4386442731869167</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.036872585633688</v>
+        <v>0.414581555978593</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.1517362124306985</v>
+        <v>0.6399265453529424</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.0305681403061584</v>
+        <v>0.5518732751916033</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.0006240308611680234</v>
+        <v>0.4922861150070119</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.05588517115791092</v>
+        <v>0.4462199433762706</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.02149</t>
+          <t>X &gt; -0.02145</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3016</v>
+        <v>3020</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1116216159952828</v>
+        <v>0.2858320296941983</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.05857322053753933</v>
+        <v>0.1562396117279334</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2605313375002964</v>
+        <v>0.1359896970035805</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3953716838128258</v>
+        <v>0.08805434601204354</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.05382073122124353</v>
+        <v>0.5218491786703652</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3426592363824028</v>
+        <v>0.2365290115227197</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.5026947115585045</v>
+        <v>0.08550059935920018</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.4654230840031914</v>
+        <v>0.02980111675763197</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.4051763645393791</v>
+        <v>0.1435237852460247</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.3672409125729246</v>
+        <v>0.1902111996278109</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.3052348296791152</v>
+        <v>0.2506798412151525</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.5319770615889325</v>
+        <v>0.0590255992327684</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.64505332646646</v>
+        <v>-0.1130800609501392</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.5163173290230532</v>
+        <v>0.02103853056597416</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.3285467015573147</v>
+        <v>0.2167022045043296</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.1773689273689243</v>
+        <v>0.3354001167007894</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.00604517218761913</v>
+        <v>0.4493413445655676</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.02020170836605217</v>
+        <v>0.4352820658011609</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.008948732451138142</v>
+        <v>0.4050113175764523</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.1666447719211561</v>
+        <v>0.2754965776251694</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.07223969040354206</v>
+        <v>0.5545932324944829</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.1162900008007952</v>
+        <v>0.3999934029614991</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.2197377875735782</v>
+        <v>0.2662233927723392</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.2758651677037136</v>
+        <v>0.2231187079852361</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.0186</t>
+          <t>X &gt; -0.01856</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2933</v>
+        <v>2935</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.3042934216171389</v>
+        <v>0.4465551515378081</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1726998267891631</v>
+        <v>0.3541786445047777</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.01235613385713208</v>
+        <v>0.4033217253629644</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3339140534262413</v>
+        <v>0.100410744622792</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.00694861850932682</v>
+        <v>0.5207686643098839</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2943978848009721</v>
+        <v>0.2565820389056412</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.369403848900852</v>
+        <v>0.1918560010758839</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.3232077093535821</v>
+        <v>0.1433710684812013</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.2623845797841966</v>
+        <v>0.2906212079696218</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2354964860094739</v>
+        <v>0.3277392445076757</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.1454757055571676</v>
+        <v>0.4160699574445417</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.472565525120018</v>
+        <v>0.1251229586510902</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.5911117176128116</v>
+        <v>-0.05370267905143322</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.5544285315381643</v>
+        <v>-0.01039585226110518</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.274824884162058</v>
+        <v>0.2785365378328777</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.1361369560961521</v>
+        <v>0.3844720698969368</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.02223623346161219</v>
+        <v>0.4707327781554511</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.0282914896381854</v>
+        <v>0.3921109362075441</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.06438099253930574</v>
+        <v>0.3547498906916573</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.2999294003319122</v>
+        <v>0.1472158032913171</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.1411793189044488</v>
+        <v>0.3486500066653733</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.3670399023003768</v>
+        <v>0.1576327054367965</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.3790147229312453</v>
+        <v>0.1150337637720682</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.5369231369749983</v>
+        <v>-0.060961303748023</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.0157</t>
+          <t>X &gt; -0.01567</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2835</v>
+        <v>2833</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.3724721995718951</v>
+        <v>0.5540119273515813</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3882036381656349</v>
+        <v>0.6072632838212542</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3171667132145615</v>
+        <v>0.7731703721355814</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2205331877563879</v>
+        <v>0.270433927984854</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.07459116619475736</v>
+        <v>0.6806773530301484</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2642050031232088</v>
+        <v>0.3313296069965403</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.4555045929520034</v>
+        <v>0.1875056944149236</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.6086399712871042</v>
+        <v>-0.0624000624000729</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.4770766695744797</v>
+        <v>0.15569452733736</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.5631523956131304</v>
+        <v>0.08211652086824728</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.4795794607918467</v>
+        <v>0.1637698404482251</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6328271533910481</v>
+        <v>0.04796606322319263</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.6816993845137205</v>
+        <v>-0.06215295561896284</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.5658702952896277</v>
+        <v>0.0619589082175267</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.4649277734964983</v>
+        <v>0.1746503431751094</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.3068408318144549</v>
+        <v>0.2993991551252151</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.2440081953443922</v>
+        <v>0.2868251173708956</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.2927561128539509</v>
+        <v>0.2100880387857984</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.3024225845008743</v>
+        <v>0.198848206550764</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.4821882078385613</v>
+        <v>0.04657947128472983</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.4049938791831167</v>
+        <v>0.169849003133038</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.6008809862008206</v>
+        <v>-0.0253996873334259</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.6228367290210315</v>
+        <v>-0.04307937774231618</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.7483949793139786</v>
+        <v>-0.2196291337943634</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.01281</t>
+          <t>X &gt; -0.01279</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2737</v>
+        <v>2733</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.4985864377662921</v>
+        <v>0.6663718205105909</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.5269178456619414</v>
+        <v>0.7305226975285422</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2145342359918772</v>
+        <v>0.6575711723476942</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2805548597035923</v>
+        <v>0.194373767886745</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.0009386183664190639</v>
+        <v>0.5931724605026716</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.5020007874025723</v>
+        <v>0.07998769516856186</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.6566655206756451</v>
+        <v>-0.003881865393694284</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.8054215697040803</v>
+        <v>-0.2518559812121168</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.6343849111085547</v>
+        <v>0.005840905500029692</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.7324006564644492</v>
+        <v>-0.07789454718197675</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6556775200359723</v>
+        <v>-0.003239836695399845</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.8408920843689174</v>
+        <v>-0.1496771993311867</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.9243085880640436</v>
+        <v>-0.2961374475471388</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.7601451808813877</v>
+        <v>-0.1220800466945988</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.6685995507805345</v>
+        <v>-0.01693764794075037</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.7083126345421391</v>
+        <v>-0.09060076910923698</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.6385995294149609</v>
+        <v>-0.0999847931873461</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.7219436912830872</v>
+        <v>-0.2113228601816814</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.4845400889440157</v>
+        <v>0.02470114365448239</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.7504458209896328</v>
+        <v>-0.2141074765568973</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.614687145233539</v>
+        <v>-0.02913812147208716</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.8514554956012574</v>
+        <v>-0.2654133581819522</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.8841127574605494</v>
+        <v>-0.2927387805731314</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.9750105852987261</v>
+        <v>-0.4333173458381552</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.009921</t>
+          <t>X &gt; -0.009898</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2626</v>
+        <v>2620</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.4643363901624369</v>
+        <v>0.6382283608035166</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6214248963907494</v>
+        <v>0.7913301757767499</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.2428080418357368</v>
+        <v>0.655371349818374</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.2052954289880162</v>
+        <v>0.2355822566978532</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1021225736822728</v>
+        <v>0.663272018122278</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5432986787371945</v>
+        <v>0.007686465675604381</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.5963673020902718</v>
+        <v>0.03010992969024784</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.701811524039222</v>
+        <v>-0.177473849704505</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.5252907299051657</v>
+        <v>0.08581626795096753</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.6706462531069874</v>
+        <v>-0.005295157331950406</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.5643068217687244</v>
+        <v>0.06090760671501982</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.7076435476482743</v>
+        <v>-0.04192394804811528</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.6334775689590373</v>
+        <v>-0.03272454043935369</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.8323442359410365</v>
+        <v>-0.2206510376303825</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.8230971743724069</v>
+        <v>-0.1958182755363964</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.8516255953613552</v>
+        <v>-0.2588003340893081</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.8493414139285278</v>
+        <v>-0.3403161083618826</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.931859065814777</v>
+        <v>-0.4508185428361386</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.7696443873820158</v>
+        <v>-0.290148068492023</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.978721421884643</v>
+        <v>-0.4723821809243205</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.814410611456708</v>
+        <v>-0.2550969695390037</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.9438966591762679</v>
+        <v>-0.3839853624713498</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.9134340467742277</v>
+        <v>-0.3467312509330966</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-1.004979856360897</v>
+        <v>-0.4864005276449177</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.00703</t>
+          <t>X &gt; -0.00701</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2488</v>
+        <v>2483</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.4509692538334988</v>
+        <v>0.6074131761192518</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.5952343716513511</v>
+        <v>0.7823247196186642</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.07537899527505232</v>
+        <v>0.5078905451565703</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.0786927886387403</v>
+        <v>0.3771547938956346</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.01528166437962852</v>
+        <v>0.5636321392712915</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.5867985122143935</v>
+        <v>-0.01654948058273931</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.5204238428113328</v>
+        <v>0.1306635891517587</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.7361245263392533</v>
+        <v>-0.1915917882304541</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.6720286920597758</v>
+        <v>-0.04097966594985536</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.7428612084154622</v>
+        <v>-0.09346474215492151</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.6857891117629151</v>
+        <v>-0.03860596364929592</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.7016996507566944</v>
+        <v>-0.01169631953881378</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.8015083762762814</v>
+        <v>-0.1813137657545738</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.9191511625141615</v>
+        <v>-0.2857611024659192</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.9131027142270653</v>
+        <v>-0.2622156081647518</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.8559149184149177</v>
+        <v>-0.2391252419616023</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-1.00641971789689</v>
+        <v>-0.4800451807228967</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-1.087765155323218</v>
+        <v>-0.5893718177637126</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.249482803819191</v>
+        <v>-0.7532624460758512</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.360292258447572</v>
+        <v>-0.8369149464268872</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.317553229560467</v>
+        <v>-0.7374320528680158</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.289571596367963</v>
+        <v>-0.7085106990829431</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-1.272776860522058</v>
+        <v>-0.6827697262479759</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.365338672356273</v>
+        <v>-0.821334567666689</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.004138</t>
+          <t>X &gt; -0.004122</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2330</v>
+        <v>2324</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7264302619408483</v>
+        <v>0.8672582314121939</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.201197562440633</v>
+        <v>1.369181696202581</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5727226122592342</v>
+        <v>0.9908874728867048</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.1580216818663445</v>
+        <v>0.5930390774652494</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1630918825188985</v>
+        <v>0.7256024349937391</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.5020936143832913</v>
+        <v>0.0527481632973803</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3792830311240962</v>
+        <v>0.2639912269134044</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.7185907730129415</v>
+        <v>-0.187590187590196</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.951471612154819</v>
+        <v>-0.3347075939955886</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.9750986266719863</v>
+        <v>-0.3367506972771181</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.7193565639966977</v>
+        <v>-0.08283590999733548</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.6321522553681334</v>
+        <v>0.05032841486148953</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.620145784251001</v>
+        <v>-0.01206817591068443</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.9016670897858958</v>
+        <v>-0.2780273657408756</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.722484917719477</v>
+        <v>-0.07779348136240571</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.7442906395002211</v>
+        <v>-0.1342020639754011</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.8530792329046548</v>
+        <v>-0.3415245602745642</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.104002755701103</v>
+        <v>-0.6208579964348502</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.376931737922483</v>
+        <v>-0.8964659241014203</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.46510065302229</v>
+        <v>-0.9575940240221357</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-1.382768716844907</v>
+        <v>-0.8125929625570336</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-1.562188651208253</v>
+        <v>-0.9915502952151911</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-1.562976949838266</v>
+        <v>-0.9808321645628695</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-1.656797761822624</v>
+        <v>-1.117912398465172</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.001247</t>
+          <t>X &gt; -0.001235</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2165</v>
+        <v>2158</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.033763335697266</v>
+        <v>1.182143914091242</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.386429250454697</v>
+        <v>1.51206304013229</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.09414805660245</v>
+        <v>1.476515217673196</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.5645120939883057</v>
+        <v>0.9560100068683681</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6870167635125171</v>
+        <v>1.166017877739336</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.1407107222955091</v>
+        <v>0.6135616933385037</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.3311818367552917</v>
+        <v>0.9023655210744863</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.01242229401916717</v>
+        <v>0.439806652415939</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1281309106818398</v>
+        <v>0.4099519817624255</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2323196645968224</v>
+        <v>0.3311442819951012</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.02353794244184115</v>
+        <v>0.5378740079919666</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.0457877171808363</v>
+        <v>0.6567683183584734</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.08559701173046363</v>
+        <v>0.4450973700488419</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1875497894617055</v>
+        <v>0.3625701456564272</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.1284813157429952</v>
+        <v>0.4464602802553017</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.3348603383117918</v>
+        <v>0.2040776788535652</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.5336325228807013</v>
+        <v>-0.1034927603203997</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.8876349118314124</v>
+        <v>-0.4864873182915161</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.013300756760238</v>
+        <v>-0.6148738514971726</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-1.168327117067534</v>
+        <v>-0.6971785997006421</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.8999243041744691</v>
+        <v>-0.3580854898931349</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.179301257977016</v>
+        <v>-0.591178638167186</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.154713522184259</v>
+        <v>-0.5982995527259405</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.388284841682676</v>
+        <v>-0.8994561559125387</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.001645</t>
+          <t>X &gt; 0.001653</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.8216275315984589</v>
+        <v>1.067302349903585</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1.399629637913954</v>
+        <v>1.581273933652604</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.330778945880937</v>
+        <v>1.745019548073081</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.17563425706701</v>
+        <v>1.608544400936594</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.296233236852387</v>
+        <v>1.818158168726484</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.3675807616921603</v>
+        <v>0.8887476297820456</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.8126706173555647</v>
+        <v>1.390795501886409</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.4837492334544109</v>
+        <v>0.9630020289918733</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.1195569021845273</v>
+        <v>0.7139970935176478</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1676136439099878</v>
+        <v>0.4552628366306806</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.06721420669956757</v>
+        <v>0.5536176490369513</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.1404334117115624</v>
+        <v>0.8150844036573304</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.1647317783221496</v>
+        <v>0.7476944799894127</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.07550322902143591</v>
+        <v>0.6824488671189783</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.1088560880141571</v>
+        <v>0.6928937218236655</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.2839463335646499</v>
+        <v>0.2655458041816843</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.2858951657375854</v>
+        <v>0.1408985636579985</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.5642877193086662</v>
+        <v>-0.1148143772704415</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.7259986997038084</v>
+        <v>-0.2785386467754023</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-1.019129144335551</v>
+        <v>-0.4935975201206233</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.7156107263448064</v>
+        <v>-0.1114636764598771</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.9654573753183797</v>
+        <v>-0.4119460350249682</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.7630160375178008</v>
+        <v>-0.270561038499153</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.7065608001948434</v>
+        <v>-0.3304505440360543</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.004536</t>
+          <t>X &gt; 0.004541</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.6380278117625338</v>
+        <v>0.8077904351790366</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.260761486183512</v>
+        <v>1.336615423074683</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.91729659633863</v>
+        <v>2.108143013674173</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.383875790540415</v>
+        <v>1.575335570527443</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.065440195312121</v>
+        <v>2.37248303233514</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.175207099542348</v>
+        <v>1.49082610227893</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.360768888422797</v>
+        <v>1.74421967507061</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.321935061862412</v>
+        <v>1.653205832310306</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.9445114119398994</v>
+        <v>1.397925340970851</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.8298841859333308</v>
+        <v>1.294117870429069</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.8645662099025486</v>
+        <v>1.302487153759614</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.064572042839949</v>
+        <v>1.59954531393759</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.234299959033891</v>
+        <v>1.657782700494963</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.109338015886678</v>
+        <v>1.565509933967554</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.206899321789294</v>
+        <v>1.639024234631961</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.7582574394212074</v>
+        <v>1.157263485110327</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.7805395547901455</v>
+        <v>1.089498299319729</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.4717253696845489</v>
+        <v>0.8125926215651234</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.06272503196716173</v>
+        <v>0.4020909424969901</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.01527865387868133</v>
+        <v>0.411887908394128</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.139702518086537</v>
+        <v>0.602103037984925</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.1166488584850214</v>
+        <v>0.3464351008671827</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.5550609297890219</v>
+        <v>0.9510804164704751</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.575737529557486</v>
+        <v>0.8491098939018187</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.007428</t>
+          <t>X &gt; 0.007429</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.811089758877934</v>
+        <v>2.020854013686836</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.548048972005873</v>
+        <v>1.632293825629183</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.90343020991893</v>
+        <v>2.089439951982968</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.19047619047619</v>
+        <v>1.283057724644074</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.361141958961923</v>
+        <v>2.648013136613216</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.902484041759443</v>
+        <v>2.0916799808424</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.560951426735663</v>
+        <v>1.908907700500791</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.143572119715728</v>
+        <v>2.431457431457424</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.898115255719382</v>
+        <v>2.315845036127747</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>1.555615648549463</v>
+        <v>1.991211404270857</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.614467256278104</v>
+        <v>2.019719569085687</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>1.909605944652206</v>
+        <v>2.358660439825194</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.0776920843958</v>
+        <v>2.5053349079081</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.259529614124382</v>
+        <v>2.659645289376719</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>2.364077027900272</v>
+        <v>2.811338357490165</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.924983116571902</v>
+        <v>2.33987179103535</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.691349922102532</v>
+        <v>2.06442457464653</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.126678378849221</v>
+        <v>1.543899467979884</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.170260777921499</v>
+        <v>1.514151016152631</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.328745249899256</v>
+        <v>1.772359331692535</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.623597684292164</v>
+        <v>1.969580135357205</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.331301506432851</v>
+        <v>1.750221506696803</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.822226435365117</v>
+        <v>2.210150152032853</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.718576031580014</v>
+        <v>1.975913104390834</v>
       </c>
     </row>
     <row r="24">
@@ -4660,79 +4660,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1168</v>
+        <v>1173</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.886363770921776</v>
+        <v>2.181278995795125</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.231859081415493</v>
+        <v>2.356247580966674</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.579554318098793</v>
+        <v>2.700880078401696</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.441430230628839</v>
+        <v>1.519252290367888</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.04101390774143</v>
+        <v>2.253795160369556</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.802810025811596</v>
+        <v>1.905678261317135</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.796167464370228</v>
+        <v>2.001632418132381</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.36829615567158</v>
+        <v>2.504933702235554</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.814545242348181</v>
+        <v>2.092237456271128</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.806935688760674</v>
+        <v>2.105998938586289</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.336097371738916</v>
+        <v>2.597700038041324</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2.48251803631814</v>
+        <v>2.794762622032998</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.719900187149094</v>
+        <v>3.00105720145072</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>3.179093419546042</v>
+        <v>3.483028797389274</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2.744426746657915</v>
+        <v>3.023412906900262</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>2.370166744102015</v>
+        <v>2.619178232890825</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>2.118466029727948</v>
+        <v>2.397736122911354</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.63966805639857</v>
+        <v>1.891988343817985</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.907948953007697</v>
+        <v>2.07337776737424</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.147273833388184</v>
+        <v>2.425192818036905</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.341642114911458</v>
+        <v>2.591971344434796</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.43688255213366</v>
+        <v>2.687311806281734</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>3.053530061878334</v>
+        <v>3.271952259164536</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.860149148636538</v>
+        <v>2.939310281072856</v>
       </c>
     </row>
     <row r="25">
@@ -4742,899 +4742,899 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.974703642507556</v>
+        <v>2.107693101313714</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>2.503857729686906</v>
+        <v>2.608054922326254</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.79370045171423</v>
+        <v>2.952507941969856</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.540789628815759</v>
+        <v>1.613837086445223</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.068930041797643</v>
+        <v>2.084547603062298</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.391965342365864</v>
+        <v>1.388602744241616</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.131895708151546</v>
+        <v>2.19266785354408</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.1495805916922</v>
+        <v>2.953845491158923</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.867093691533476</v>
+        <v>2.825432994594799</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>3.606057065173012</v>
+        <v>3.588731671319024</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>3.23216854318806</v>
+        <v>3.284614933101011</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.737436418357774</v>
+        <v>2.858712592503686</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>2.586196597721958</v>
+        <v>2.773172499674736</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.25712636058423</v>
+        <v>2.48353799939698</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.530510702954636</v>
+        <v>2.726596711559118</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.326839826839823</v>
+        <v>2.494673422477696</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>2.476559241104539</v>
+        <v>2.67228426623609</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>1.679831523560772</v>
+        <v>1.851670492539547</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.288109751753353</v>
+        <v>2.455667927809415</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.868195423874987</v>
+        <v>2.993878968337654</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.869127516778526</v>
+        <v>2.965808792739011</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.228064164065074</v>
+        <v>3.3221457314094</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>3.719930180894949</v>
+        <v>3.781529947000621</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.535402275497766</v>
+        <v>3.511516087554732</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.0161</t>
+          <t>X &gt; 0.01609</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.80297311128713</v>
+        <v>3.699713104758487</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.32774687473507</v>
+        <v>3.314530503037901</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.277368275142287</v>
+        <v>4.288248657413732</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.721717626486054</v>
+        <v>2.860191862505232</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>3.930870974163504</v>
+        <v>3.977391382573018</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.415589969249652</v>
+        <v>3.437946158487549</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.924540161763794</v>
+        <v>2.921415678288248</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.050823099033188</v>
+        <v>4.009252895046764</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.951860842745653</v>
+        <v>3.997906038714163</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>4.442990110529379</v>
+        <v>4.455336437645229</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.593454247073325</v>
+        <v>3.698251669651853</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.910210461602858</v>
+        <v>2.110145128720831</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.331992214971457</v>
+        <v>2.617122761631428</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>2.391812214929359</v>
+        <v>2.648608979918606</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3.227055348866372</v>
+        <v>3.45320314360562</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>2.55561948599923</v>
+        <v>2.840629476708642</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.124937229471833</v>
+        <v>3.525866104868918</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>2.4042212458424</v>
+        <v>2.690734808696071</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>3.042647838034341</v>
+        <v>3.326545350448583</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>3.229493648002368</v>
+        <v>3.541131795507567</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>3.109482691303946</v>
+        <v>3.395035608733579</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>3.315326870739909</v>
+        <v>3.600771963182794</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>3.308111442376898</v>
+        <v>3.563507572056672</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>3.091434118731087</v>
+        <v>3.260919139564969</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.01899</t>
+          <t>X &gt; 0.01898</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.485347915248724</v>
+        <v>4.362135176651307</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.341775705809042</v>
+        <v>4.306704531423634</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.007007134789518</v>
+        <v>5.147248524770148</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.676462293167056</v>
+        <v>4.935798706914305</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.105490176260311</v>
+        <v>5.422145328719722</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>4.527638006717162</v>
+        <v>4.817174172813054</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>3.946893911736943</v>
+        <v>4.212568351056518</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.389523767175064</v>
+        <v>5.621933621933614</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.857397182359371</v>
+        <v>5.368910150665343</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>5.614118217603952</v>
+        <v>6.096668179255531</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>5.314564093035465</v>
+        <v>5.797474622431295</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4.079791745036808</v>
+        <v>4.568511715579042</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.486266389461761</v>
+        <v>5.098839518157355</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>4.073982924105039</v>
+        <v>4.659765762067757</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>5.327885515625816</v>
+        <v>5.886008326747579</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>4.201431137377604</v>
+        <v>4.729755093658852</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>5.023536944950806</v>
+        <v>5.580073155216276</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>3.771468707668816</v>
+        <v>4.302150882115754</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>4.94338303314381</v>
+        <v>5.470811582543973</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>5.512638020932101</v>
+        <v>6.067077416915922</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>5.7349102086066</v>
+        <v>6.262991694161144</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>5.467859658287374</v>
+        <v>5.99698947754937</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>5.742334370769427</v>
+        <v>6.240623962827748</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>5.284092939725888</v>
+        <v>5.696805579225305</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.02189</t>
+          <t>X &gt; 0.02187</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>416</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.734152886568033</v>
+        <v>5.832373271889402</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>4.437837626679759</v>
+        <v>4.624927974647072</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.884433962264154</v>
+        <v>6.254849257370878</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5.411864558206027</v>
+        <v>5.902831673947269</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.75876639335106</v>
+        <v>7.30996584154024</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.022655656371519</v>
+        <v>5.543822524461405</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.731476203250395</v>
+        <v>5.229509742997912</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>6.135957066189626</v>
+        <v>6.6072816072816</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.937059632719716</v>
+        <v>6.494825901581095</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.087220879760153</v>
+        <v>7.621851329438684</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.918972829614376</v>
+        <v>6.451778651735317</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4.438300349243306</v>
+        <v>4.973273620340947</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>4.036292128541035</v>
+        <v>4.579535349044022</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.815213252094445</v>
+        <v>4.331301287610913</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>5.080146877590813</v>
+        <v>5.572223828802784</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>3.991841491841491</v>
+        <v>4.450835539930132</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>4.579078201017865</v>
+        <v>5.068108974358971</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>3.512699035658223</v>
+        <v>3.97368640765891</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>5.170898108890249</v>
+        <v>5.630456327112384</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>6.078897765012115</v>
+        <v>6.566196618325208</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>6.257505443199925</v>
+        <v>6.719905963098313</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>6.422044097175437</v>
+        <v>6.885128056527641</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>7.417672655811344</v>
+        <v>7.849916387959873</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>7.341840402588069</v>
+        <v>7.687777393670409</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.02478</t>
+          <t>X &gt; 0.02476</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>6.242873816800589</v>
+        <v>6.457373271889402</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.198794692869377</v>
+        <v>6.501321508649305</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>6.504961690350015</v>
+        <v>6.985757841540334</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.91991464765146</v>
+        <v>5.523790425340799</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.49110091929024</v>
+        <v>8.146783009879144</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.515276407713195</v>
+        <v>7.144296326022157</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.324723072660056</v>
+        <v>6.928924458716978</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.500000000000014</v>
+        <v>8.073279377627188</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>7.250789507496108</v>
+        <v>7.911353214847544</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.803455226808452</v>
+        <v>9.434142299338347</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.496119520133156</v>
+        <v>9.12666716901515</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.182486395754935</v>
+        <v>6.821099707297464</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.059324328898818</v>
+        <v>5.706207589846692</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.001036150126652</v>
+        <v>6.61739381826866</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>5.924288201383284</v>
+        <v>6.514949581311136</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>4.77448907681466</v>
+        <v>5.337123165348189</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>4.640571939837187</v>
+        <v>5.23324275362318</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>3.372940538341588</v>
+        <v>3.940938358606516</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>4.751622616940331</v>
+        <v>5.314820875607353</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>4.938468426908358</v>
+        <v>5.529407320666337</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>4.686619933360937</v>
+        <v>5.251817891749383</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>5.192169320789041</v>
+        <v>5.756365514721629</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>6.629434730945505</v>
+        <v>7.159420289855085</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>6.553602477722229</v>
+        <v>6.997281295565621</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.02767</t>
+          <t>X &gt; 0.02764</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>287</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.986330586916466</v>
+        <v>7.084550972237835</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.303121732817523</v>
+        <v>6.490212080784836</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.607262962532175</v>
+        <v>6.9776782576389</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4.50058072009292</v>
+        <v>4.991547835834162</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>7.649110805036926</v>
+        <v>8.200310253226107</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.093916712388669</v>
+        <v>6.615083580478554</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.018832139996583</v>
+        <v>6.5168656797441</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.134348918240022</v>
+        <v>7.605673459331996</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6.827404044405583</v>
+        <v>7.385170313266961</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.145080702863879</v>
+        <v>8.67971115254241</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.419140345025802</v>
+        <v>8.951946167146744</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.746662718581291</v>
+        <v>7.281635989678932</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.971932707474288</v>
+        <v>6.515175927977275</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.841446165522484</v>
+        <v>8.357534201038952</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>7.880166979440169</v>
+        <v>8.372243930652139</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>7.080825678386645</v>
+        <v>7.539819726475287</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>6.946908541409172</v>
+        <v>7.435939314750279</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>5.099907558842361</v>
+        <v>5.560894930843048</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>5.664230995515801</v>
+        <v>6.123789213737936</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>6.5479409169821</v>
+        <v>7.035239770295192</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>6.00539474901607</v>
+        <v>6.467795268914458</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>6.277980843356097</v>
+        <v>6.741064802708301</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>8.29461583458378</v>
+        <v>8.726859566732308</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>8.218783581360505</v>
+        <v>8.564720572442845</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.03056</t>
+          <t>X &gt; 0.03053</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.359152886568033</v>
+        <v>6.630533445049579</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6.024376088218219</v>
+        <v>6.384626609345709</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>8.064617908752446</v>
+        <v>8.593135970657585</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>6.482098671918408</v>
+        <v>7.134932906048491</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.755003851545041</v>
+        <v>9.456777363351762</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>6.768056994164162</v>
+        <v>7.449208804847686</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.300456136360758</v>
+        <v>7.952828091316263</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.630940343781603</v>
+        <v>10.24531024531025</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8.368079699609339</v>
+        <v>9.074537856293055</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.334294458355473</v>
+        <v>10.01008809267545</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>10.04313670921304</v>
+        <v>10.7152235401802</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>8.894822088373743</v>
+        <v>9.572840719908058</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>8.206442630213282</v>
+        <v>8.890849035357711</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.5940594059406</v>
+        <v>11.24001757132719</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>10.3706987170557</v>
+        <v>10.99076362234258</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>9.225955204216078</v>
+        <v>9.820465909560511</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>8.222472849847293</v>
+        <v>8.850784632034625</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>7.682849537330469</v>
+        <v>8.285000093972599</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>7.463958309559139</v>
+        <v>8.066561888217947</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>9.389934554309775</v>
+        <v>10.01275006487866</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>9.282170995039401</v>
+        <v>9.87820599639835</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>8.771542424934644</v>
+        <v>9.37014304154264</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>10.35036496350365</v>
+        <v>10.91247882552231</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>9.83975010158472</v>
+        <v>10.31743939833242</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.03345</t>
+          <t>X &gt; 0.03342</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>173</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>5.896725140903293</v>
+        <v>5.994945526224662</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.98391366047256</v>
+        <v>5.171004008439873</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.592137386008034</v>
+        <v>7.962552681114758</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6.301148684484374</v>
+        <v>6.792115800225616</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>11.16767035066543</v>
+        <v>11.71886979885461</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.62053249052002</v>
+        <v>10.14169935860991</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.426618488710595</v>
+        <v>9.924652028458112</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>12.03858045436215</v>
+        <v>12.50990499545412</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>10.34596359003409</v>
+        <v>10.90372985889547</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>11.88518664232129</v>
+        <v>12.41981709199982</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.31531564864506</v>
+        <v>13.848121470766</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>13.03656624519706</v>
+        <v>13.57153951629471</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>11.33536949626002</v>
+        <v>11.87861271676301</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>13.42642934813712</v>
+        <v>13.94251738365359</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>12.19025136847565</v>
+        <v>12.68232831968762</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>11.05053424417586</v>
+        <v>11.50952829226451</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>11.49465178927932</v>
+        <v>11.98368256262042</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>11.38981108545813</v>
+        <v>11.85079845745882</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>9.871598420139684</v>
+        <v>10.33115663836182</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>11.21451359426956</v>
+        <v>11.70181244758265</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>9.51589806214168</v>
+        <v>9.978298582040068</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>10.59612146489443</v>
+        <v>11.05920542424663</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>13.76076958778111</v>
+        <v>14.19301331992964</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>12.52886797039599</v>
+        <v>12.87480496147833</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.03634</t>
+          <t>X &gt; 0.03631</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>132</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.965213492628642</v>
+        <v>7.063433877950011</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>4.357709421551554</v>
+        <v>4.544799769518868</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.707569160399352</v>
+        <v>7.077984455506076</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.994615140956611</v>
+        <v>6.485582256697853</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>11.71943072901539</v>
+        <v>12.27063017720457</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>11.14882115753701</v>
+        <v>11.6699880256269</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.37687247364666</v>
+        <v>10.87490601339418</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14.64411557434813</v>
+        <v>15.11544011544011</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>12.41287548353557</v>
+        <v>12.97064175239695</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>14.67026283780211</v>
+        <v>15.20489328748064</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>15.70189823753979</v>
+        <v>16.23470405966073</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>15.42314883409179</v>
+        <v>15.95812210518943</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>15.81513828238719</v>
+        <v>16.35838150289018</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>18.62436243624363</v>
+        <v>19.1404504717601</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>17.96621913866307</v>
+        <v>18.45829608987504</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>17.04545454545455</v>
+        <v>17.50444859354319</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>16.91153740847707</v>
+        <v>17.40056818181818</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>16.80669670465589</v>
+        <v>17.26768407665658</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>15.5074365704287</v>
+        <v>15.96699478865084</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>16.45185813797248</v>
+        <v>16.93915699128557</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>15.1517362124307</v>
+        <v>15.61413673232909</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>15.0758902510216</v>
+        <v>15.5389742103738</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>17.62309223623092</v>
+        <v>18.05533596837945</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>16.78968422543189</v>
+        <v>17.13562121651423</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.03923</t>
+          <t>X &gt; 0.0392</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>92</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.880892017002814</v>
+        <v>2.979112402324184</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.3722021751747349</v>
+        <v>0.559292523142048</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.02113964788288314</v>
+        <v>0.3915549429896075</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.6918143715598575</v>
+        <v>-0.2008472558186156</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.581090808066783</v>
+        <v>7.132290256255963</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.594143950685904</v>
+        <v>5.115310818775789</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.996108310273812</v>
+        <v>6.494141850021329</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>10.06572295247726</v>
+        <v>10.53704749356923</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.020253612652823</v>
+        <v>9.578019881514201</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.68212054531199</v>
+        <v>14.21675099499052</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>15.04313670921304</v>
+        <v>15.57594253133398</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>13.67743078402592</v>
+        <v>14.21240405512356</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>13.64122523890892</v>
+        <v>14.18446845941191</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.5940594059406</v>
+        <v>16.11014744145707</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>16.02287263009918</v>
+        <v>16.51494958131115</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>15.53030303030303</v>
+        <v>15.98929707839167</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>17.57029893680382</v>
+        <v>18.05932971014493</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>18.55241475472177</v>
+        <v>19.01340212672245</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>16.59439309216784</v>
+        <v>17.05395131038998</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>16.78123890213587</v>
+        <v>17.26853775544896</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>18.41260577764809</v>
+        <v>18.87500629754648</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>18.33675981623899</v>
+        <v>18.79984377559119</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>20.78514757219931</v>
+        <v>21.21739130434784</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>21.79627184071516</v>
+        <v>22.1422088317975</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.04213</t>
+          <t>X &gt; 0.04208</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>6.653270533626852</v>
+        <v>7.326938489280714</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>3.377317264688806</v>
+        <v>2.733205566620313</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-2.472466490224534</v>
+        <v>-2.86931462222779</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-1.714832274373165</v>
+        <v>-2.012441458717163</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>6.772906664844271</v>
+        <v>6.407652575096535</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>4.018696380353411</v>
+        <v>3.666035456456939</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>4.717335931757184</v>
+        <v>5.7695041688619</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>8.850889192886456</v>
+        <v>9.812409812409797</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>5.951199904212928</v>
+        <v>7.041787997456225</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>15.47240187523526</v>
+        <v>16.39066403846877</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>17.2170497526913</v>
+        <v>18.11217441539196</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>13.99712387865507</v>
+        <v>13.48776637396413</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>15.81513828238719</v>
+        <v>15.27142498115104</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>14.12347117064648</v>
+        <v>15.02319091971793</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>11.99473963777181</v>
+        <v>12.89176117551404</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>9.647950089126553</v>
+        <v>10.55451446969602</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>12.45520942273733</v>
+        <v>13.3491847826087</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>13.82095695421026</v>
+        <v>14.66557603976592</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>12.56626009984047</v>
+        <v>11.98148754227402</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>11.28251767451438</v>
+        <v>12.19607398733301</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>13.68114797713658</v>
+        <v>14.52718021058995</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>15.0758902510216</v>
+        <v>15.90129305095352</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>18.29154143409188</v>
+        <v>17.59420289855073</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>21.15688565145685</v>
+        <v>20.33061462889895</v>
       </c>
     </row>
   </sheetData>
@@ -5824,1477 +5824,1477 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.04173</t>
+          <t>X &lt; -0.04167</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-2.170258878137851</v>
+        <v>-1.36871368463234</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.4361407941005666</v>
+        <v>-0.1653451580173595</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4687099803636983</v>
+        <v>0.0292361024098966</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>4.167520666803306</v>
+        <v>5.23393535287704</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.8905537236678001</v>
+        <v>2.059826488140018</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>5.489284615647534</v>
+        <v>6.564586181094619</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>6.1879241670513</v>
+        <v>7.218779531180736</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>8.850889192886456</v>
+        <v>9.812409812409797</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>11.83355284538939</v>
+        <v>11.38961408441276</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.119460698764669</v>
+        <v>9.144287226874567</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.393520340926592</v>
+        <v>7.967246879160072</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.52653564336096</v>
+        <v>12.03849101164529</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>11.40337357650484</v>
+        <v>10.92359889419452</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>15.5940594059406</v>
+        <v>15.02319091971793</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>10.52415140247769</v>
+        <v>9.993210450876354</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>12.5891265597148</v>
+        <v>12.00378983201486</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>3.631680010972616</v>
+        <v>3.204257246376805</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>3.526839307151434</v>
+        <v>3.071373141215204</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>5.213318923369876</v>
+        <v>4.735110730679814</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>6.870752968632019</v>
+        <v>6.398972538057649</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>4.857618565371872</v>
+        <v>4.382252674358064</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>6.252360839256887</v>
+        <v>5.756365514721629</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>10.9386002576213</v>
+        <v>10.34782608695652</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>15.27453271028038</v>
+        <v>14.53351317962358</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.03884</t>
+          <t>X &lt; -0.03878</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>83</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.6287989206608771</v>
+        <v>-0.5305785353395081</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2412435580977359</v>
+        <v>0.4283339060650491</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>1.212863063283621</v>
+        <v>1.583278358390345</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.524005429383045</v>
+        <v>7.014972545124287</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.573757125510468</v>
+        <v>3.124956573699649</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.580000420041571</v>
+        <v>8.101167288131457</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.012871013259662</v>
+        <v>8.51090455300718</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>10.14429812272346</v>
+        <v>10.61562266381543</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>10.18578530463816</v>
+        <v>10.74355157349954</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>7.0032310743848</v>
+        <v>7.537861524063331</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>6.072471439438281</v>
+        <v>6.605277261559223</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>9.408179867315596</v>
+        <v>9.943153138413237</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>8.285017800459478</v>
+        <v>8.828261020962465</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.67839675533818</v>
+        <v>12.19448479085465</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>7.405795626432329</v>
+        <v>7.8978725776443</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>10.40982110259219</v>
+        <v>10.86881515068083</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>1.842169025855675</v>
+        <v>2.331199799196781</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>1.737328322034493</v>
+        <v>2.19831569403518</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>3.158038980067261</v>
+        <v>3.617597198289396</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>5.754523344252149</v>
+        <v>6.241822197565241</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>2.802338622069257</v>
+        <v>3.264739141967645</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>5.136131214877018</v>
+        <v>5.599215174229222</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>10.22988303579281</v>
+        <v>10.66212676794134</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>12.5636893367864</v>
+        <v>12.90962632786874</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.03595</t>
+          <t>X &lt; -0.03589</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>112</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-4.533704256289113</v>
+        <v>-4.435483870967744</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.4041953403532119</v>
+        <v>-0.2171049923858988</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.8363570391872273</v>
+        <v>1.206772334293952</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.373403019744487</v>
+        <v>6.864370135485728</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.251898261482921</v>
+        <v>4.803097709672102</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>8.010293019008884</v>
+        <v>8.531459887098769</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>8.131201477975672</v>
+        <v>8.62923501772319</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>9.638704318936874</v>
+        <v>10.11002886002885</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>9.680191500851578</v>
+        <v>10.23795776971296</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.907275824815088</v>
+        <v>9.441906274493618</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>7.395621181262733</v>
+        <v>7.928427003383675</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8.902586063529014</v>
+        <v>9.437559334626656</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>8.67228113953005</v>
+        <v>9.215524360033037</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>11.12977369165489</v>
+        <v>11.64586172717136</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>8.68591610836004</v>
+        <v>9.17799305957201</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>10.17316017316017</v>
+        <v>10.63215422124881</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>3.789243036182697</v>
+        <v>4.278273809523803</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>2.791545189504376</v>
+        <v>3.252532561505063</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>3.007436570428702</v>
+        <v>3.466994788650837</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>4.97999666611102</v>
+        <v>5.467295519424113</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>2.651736212430698</v>
+        <v>3.114136732329086</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>3.468747393878736</v>
+        <v>3.93183135323094</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>7.314650677789359</v>
+        <v>7.746894409937887</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>9.024532710280376</v>
+        <v>9.370469701362715</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.03305</t>
+          <t>X &lt; -0.033</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-2.212275684860543</v>
+        <v>-1.429950671772573</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.738661802503934</v>
+        <v>1.141043900974267</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.586357039187227</v>
+        <v>4.111701911758736</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.730545876887341</v>
+        <v>7.040426473513904</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.251898261482921</v>
+        <v>4.65219227707653</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>10.15315016186602</v>
+        <v>11.1471540520887</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>10.8097729065471</v>
+        <v>11.76052274408133</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>9.817275747508305</v>
+        <v>10.75137694856004</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.858762929423008</v>
+        <v>10.87930585824414</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>9.085847253386518</v>
+        <v>10.08325436302481</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>7.217049752691302</v>
+        <v>8.242813321291123</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9.795443206386167</v>
+        <v>10.78313277527052</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>8.67228113953005</v>
+        <v>9.668240657819744</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>10.5940594059406</v>
+        <v>11.53268265272467</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>9.221630394074317</v>
+        <v>10.14630291872694</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>10.53030303030303</v>
+        <v>11.41183228965927</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>5.396385893325558</v>
+        <v>6.378374413145544</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>4.577259475218668</v>
+        <v>5.54126495587127</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>4.793150856142994</v>
+        <v>5.755727183017044</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>6.408568094682437</v>
+        <v>7.378764332301373</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>4.43745049814499</v>
+        <v>5.402869126695293</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>5.075890251021598</v>
+        <v>6.031931956852681</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>7.49322210636079</v>
+        <v>8.388242498469076</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>8.845961281708945</v>
+        <v>9.634554208404971</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.03016</t>
+          <t>X &lt; -0.03011</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.3364256138407598</v>
+        <v>0.3899575415523202</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.138012451854586</v>
+        <v>1.82944396427542</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.540902493732688</v>
+        <v>3.38373862642878</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.668857565199026</v>
+        <v>5.038527438856519</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>2.628521638106307</v>
+        <v>3.077576040330214</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>7.360942369658225</v>
+        <v>7.167093915991217</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>7.725357322131508</v>
+        <v>8.057405162185475</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.174418604651166</v>
+        <v>6.067091460349879</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>5.21590578656587</v>
+        <v>5.633222617224995</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>4.442990110529379</v>
+        <v>4.837171122005657</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.444322479964029</v>
+        <v>2.300417372565057</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.574663985606939</v>
+        <v>5.394621934947686</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>7.292411009659922</v>
+        <v>7.650516334350847</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>7.639513951395145</v>
+        <v>8.525877778535722</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>6.413188835632774</v>
+        <v>7.281925643841667</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>6.439393939393938</v>
+        <v>7.281431909852344</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>2.896385893325558</v>
+        <v>3.806764981273403</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>1.086999734958916</v>
+        <v>1.988487617684846</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>1.871072934065069</v>
+        <v>2.764747597639598</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>2.626100562214909</v>
+        <v>3.541131795507567</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.9471907578852381</v>
+        <v>1.85009178850887</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>1.439526614657964</v>
+        <v>2.336727019362563</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>3.418546781685471</v>
+        <v>4.26575476306791</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>4.479078164825829</v>
+        <v>5.227211274396431</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.02727</t>
+          <t>X &lt; -0.02723</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.991496464081322</v>
+        <v>-2.709293394777269</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.594671530829395</v>
+        <v>-1.288533563814468</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.73398928115909</v>
+        <v>-1.709894332372713</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5833597297012005</v>
+        <v>0.1977034688190642</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.782733773149104</v>
+        <v>-2.577854671280271</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.166137174853034</v>
+        <v>1.745745601384471</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.827088923863123</v>
+        <v>1.36733025581843</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.6830766133091757</v>
+        <v>0.6457431457431326</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.023265093925176</v>
+        <v>1.607005388760584</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.250349417888685</v>
+        <v>0.8109538935412459</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2257077613493124</v>
+        <v>-0.1668110918544272</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.97726138820434</v>
+        <v>2.889940287007612</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.317302784551693</v>
+        <v>5.525048169556847</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.230423042304231</v>
+        <v>4.860147441457059</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>4.005180177624105</v>
+        <v>4.594659726238682</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>3.300865800865793</v>
+        <v>4.322630411725001</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.569546066485735</v>
+        <v>1.718749999999993</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.4010955031363181</v>
+        <v>1.169199228171728</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.6181045551124171</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.4312587451443903</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-2.705406644712163</v>
+        <v>-1.052529934337578</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-1.915451740320393</v>
+        <v>-0.2943591229595341</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.775176162037468</v>
+        <v>0.7826086956521792</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.8510084152607433</v>
+        <v>0.6204697013627154</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.02438</t>
+          <t>X &lt; -0.02434</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.293624891209745</v>
+        <v>-2.712061944057439</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.8506239117817813</v>
+        <v>-0.3001614707912168</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.205309627479437</v>
+        <v>0.1062739954235141</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.512291908633372</v>
+        <v>0.8427754511003513</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1.254054119469451</v>
+        <v>-1.758364084347825</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.057912066627928</v>
+        <v>1.056376830620351</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.633185604959799</v>
+        <v>0.9257466456301628</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1.354974160206723</v>
+        <v>1.285278029464074</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.049239119899205</v>
+        <v>0.7487551119056519</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.970767888307158</v>
+        <v>0.6171554439288442</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>0.2249386312906481</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.04941146035442</v>
+        <v>2.938389899410708</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.051249393498303</v>
+        <v>5.145756918172566</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.135726072607262</v>
+        <v>4.565296943118199</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>2.088693886137818</v>
+        <v>2.886464820369348</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.9469696969696955</v>
+        <v>2.118865184703964</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.9230585511188849</v>
+        <v>0.3538552048726444</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-2.069565921606738</v>
+        <v>-0.1112548139102216</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-1.853674540682412</v>
+        <v>0.1032074132355518</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-2.014050952936607</v>
+        <v>-0.0144320553267292</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.25104156534708</v>
+        <v>-1.246328383949979</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-2.632443082311738</v>
+        <v>-0.6570390786627485</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-1.316301703163013</v>
+        <v>0.9154990611006895</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-1.044911734164067</v>
+        <v>1.085585980432477</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.02149</t>
+          <t>X &lt; -0.02145</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-2.807513780098638</v>
+        <v>-3.016310938636913</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.607935889497661</v>
+        <v>-1.420112511182893</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2604396181943898</v>
+        <v>-0.3063855604428838</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.6979155545634228</v>
+        <v>-0.1093140750405937</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.423390238318113</v>
+        <v>-3.016451162508346</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.5651148600201665</v>
+        <v>-1.280570188089207</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.6127971803234544</v>
+        <v>0.02961095757280674</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3345857355703785</v>
+        <v>0.2510063036378796</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3760729174850823</v>
+        <v>0.1157773185851383</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.1182912265179752</v>
+        <v>-0.1539583871605075</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.4013346484229032</v>
+        <v>-0.4080391620298656</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.82687973642993</v>
+        <v>1.946957830867262</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>3.489232989908075</v>
+        <v>3.726802555521758</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>2.432499517361208</v>
+        <v>2.952252704614963</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.217253155713799</v>
+        <v>2.006940427993065</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.1382206465771887</v>
+        <v>0.9892970783916724</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.943446975755229</v>
+        <v>-0.6935307017543835</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-2.32683921160983</v>
+        <v>-0.563256912179142</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-1.275293234585227</v>
+        <v>0.4406789991771518</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.5313443605503494</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-1.909545124616656</v>
+        <v>-0.175336951881448</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.871184957892055</v>
+        <v>0.802132105110644</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.7960474147571333</v>
+        <v>2.624713958810077</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.9987666935672905</v>
+        <v>2.725732859257455</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.0186</t>
+          <t>X &lt; -0.01856</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.528487562870161</v>
+        <v>-3.435099846390166</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.849497785655657</v>
+        <v>-2.390684101448869</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.914771628984326</v>
+        <v>-1.924948095813583</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.08107796331107409</v>
+        <v>-0.1517588967723356</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.286315218039803</v>
+        <v>-2.362800907839407</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.8455570133117405</v>
+        <v>-1.130598484637027</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.4862839777450816</v>
+        <v>-0.6353579162245921</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.7644954224981575</v>
+        <v>-0.5101708327514842</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.7230082405834537</v>
+        <v>-0.8123494499491031</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.04343522883714</v>
+        <v>-0.9632396548458573</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.448108618349423</v>
+        <v>-1.336165930564107</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.9880741048994182</v>
+        <v>1.18295103969578</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>2.353599820848729</v>
+        <v>2.648704083535335</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>2.132520944402138</v>
+        <v>2.61552378554309</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.5694002712559652</v>
+        <v>1.288208113335457</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.4199232140408569</v>
+        <v>0.5591895515099523</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-1.68506207047534</v>
+        <v>-0.6199596774193523</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.56365843040512</v>
+        <v>-0.1076824922583768</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.6690340178065881</v>
+        <v>0.7519410252099803</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.4227891677270463</v>
+        <v>1.826742524032397</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.1197570002389838</v>
+        <v>1.259298022651663</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.9356187578089248</v>
+        <v>2.259404317900682</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>1.662582158073789</v>
+        <v>3.148200093501643</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>2.491727280416121</v>
+        <v>4.061329916416476</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.0157</t>
+          <t>X &lt; -0.01567</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>540</v>
+        <v>567</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-3.182131517101695</v>
+        <v>-3.278076463560332</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.424153323546491</v>
+        <v>-3.171249613197183</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-3.295779240739108</v>
+        <v>-3.367742656887707</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5915416297020073</v>
+        <v>-0.9619085241262653</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-2.303422572950666</v>
+        <v>-2.648401408493683</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.905050896335041</v>
+        <v>-1.256899901261022</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.01033291355872024</v>
+        <v>-0.464680326192159</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.8225667527993181</v>
+        <v>0.6413339746672975</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.493683564343641</v>
+        <v>0.0637955122173679</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8318789994182723</v>
+        <v>0.502311918232607</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>0.2454464037364019</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.56792997887294</v>
+        <v>1.379799193533181</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.296619763868669</v>
+        <v>2.204942349451024</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.705170517051712</v>
+        <v>1.780341444984401</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.417397589841521</v>
+        <v>1.627287592199878</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.5303030303030312</v>
+        <v>0.9540237097849698</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.02601552295519127</v>
+        <v>0.4974096119929428</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.1063600043191855</v>
+        <v>0.8936260359318737</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.6926217556138852</v>
+        <v>1.460821949144666</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.249837935952279</v>
+        <v>2.028142080270669</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>1.262847323541813</v>
+        <v>1.98979810799046</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>1.927742102873445</v>
+        <v>2.796469801202726</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>2.572587185725872</v>
+        <v>3.392837972548122</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>3.052310488058154</v>
+        <v>4.112533193426202</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.01281</t>
+          <t>X &lt; -0.01279</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>638</v>
+        <v>667</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-3.175008604115192</v>
+        <v>-3.16781413440745</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.431300428111484</v>
+        <v>-3.1138708951488</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.298378163304982</v>
+        <v>-2.269614472302749</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2763629708951356</v>
+        <v>-0.4632160714108267</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.618637452802787</v>
+        <v>-1.788249473878977</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2191014250003889</v>
+        <v>0.01785954441296411</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7896206450155248</v>
+        <v>0.4221778320303216</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.45184807173581</v>
+        <v>1.316657688471778</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.023115817913833</v>
+        <v>0.6949614107495847</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.347378825262929</v>
+        <v>1.098310215380316</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.151219031688164</v>
+        <v>0.9207701175408829</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.126388123537978</v>
+        <v>1.993513500400915</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.884103799628569</v>
+        <v>2.827646870206515</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.192805487445305</v>
+        <v>2.279562733810891</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>2.004881625601421</v>
+        <v>2.197108501850877</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>2.129049111807738</v>
+        <v>2.458562445708012</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.681652351005809</v>
+        <v>2.05483195902049</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.890291271009083</v>
+        <v>2.52164800378393</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.322483592372272</v>
+        <v>1.986485043523402</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>2.136288649989204</v>
+        <v>2.80077163850742</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.90722210584763</v>
+        <v>2.533177212089207</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.615075203999652</v>
+        <v>3.357564915021484</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>3.203029540306161</v>
+        <v>3.901049475262376</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>3.440676910907335</v>
+        <v>4.338610630897939</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.009921</t>
+          <t>X &lt; -0.009898</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>749</v>
+        <v>780</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.515019298862434</v>
+        <v>-2.516985702469576</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.179867943612017</v>
+        <v>-2.762892538173446</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.027188777545845</v>
+        <v>-1.838099460577844</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.5414905972767912</v>
+        <v>-0.5074247363091402</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.735356826970559</v>
+        <v>-1.68041877384438</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.2579120666279309</v>
+        <v>0.2713866270255068</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.3625098891906262</v>
+        <v>0.2455353840235546</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.7518551867606433</v>
+        <v>0.838050838050826</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3928083232814927</v>
+        <v>0.3249541067092991</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.8214947834265729</v>
+        <v>0.6827487653361217</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5615090317300186</v>
+        <v>0.5703683953250689</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.217339067534361</v>
+        <v>1.319427466494794</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.295779136859821</v>
+        <v>1.4865866310953</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.009279699665569</v>
+        <v>2.263993595303226</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2.152204492872727</v>
+        <v>2.479275110854061</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>2.212546020957234</v>
+        <v>2.655963745058344</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>2.078628883979761</v>
+        <v>2.552083333333336</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>2.240810877087817</v>
+        <v>2.932019740992246</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>2.056168212618296</v>
+        <v>2.761866583522632</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>2.510036719515554</v>
+        <v>3.232863284991872</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>2.234513248478763</v>
+        <v>2.921829040021393</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>2.425689983998907</v>
+        <v>3.231281902681495</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.700164696480961</v>
+        <v>3.474916387959873</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.89135514018691</v>
+        <v>3.82559790649092</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.00703</t>
+          <t>X &lt; -0.00701</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>887</v>
+        <v>917</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.017106911864218</v>
+        <v>-1.961383543813973</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.518224808642771</v>
+        <v>-2.207290379517843</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.204888752058565</v>
+        <v>-1.062856891442138</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.8456981038510207</v>
+        <v>-0.7828490575349889</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.119305338067136</v>
+        <v>-1.058407197634324</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.2561102648261269</v>
+        <v>0.2980902033473996</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.001146726244016349</v>
+        <v>-0.06078679252762242</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.6225584017199424</v>
+        <v>0.7248053049579752</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.6640455836346462</v>
+        <v>0.6346317064632387</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7930464803151764</v>
+        <v>0.8200414980486954</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.728887407708207</v>
+        <v>0.7651227503847622</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.9010962906187316</v>
+        <v>1.033797066360577</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.469027797607026</v>
+        <v>1.663725014340557</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.811646779108578</v>
+        <v>2.069798477443982</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>1.942680482655412</v>
+        <v>2.260054128274305</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>1.747890403471011</v>
+        <v>2.167050622557433</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>2.064931552852052</v>
+        <v>2.499375227190107</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>2.185569992210127</v>
+        <v>2.802696138386196</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>2.965159231082595</v>
+        <v>3.562414635979088</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>3.039265469460993</v>
+        <v>3.667949826948636</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>3.173156731032734</v>
+        <v>3.754812850104436</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>2.871831626444369</v>
+        <v>3.570599074059736</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>3.146306338926422</v>
+        <v>3.814233559338113</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>3.295953228882411</v>
+        <v>4.088299581406339</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.004138</t>
+          <t>X &lt; -0.004122</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1045</v>
+        <v>1076</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-2.261208673850611</v>
+        <v>-2.148574683500939</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-3.404195340353212</v>
+        <v>-3.045039140022645</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.124796440317056</v>
+        <v>-1.883376364590802</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.26018476651506</v>
+        <v>-1.081726518789367</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.352549821475179</v>
+        <v>-1.171411052940748</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.06127212712605967</v>
+        <v>0.1007641887450745</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3966522472464717</v>
+        <v>-0.3225706115917362</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3777678869478081</v>
+        <v>0.5806873836613562</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.089111528192667</v>
+        <v>1.173300308215353</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.081746091390627</v>
+        <v>1.213680039761812</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5902554943181002</v>
+        <v>0.7424206305743226</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.5028936506787147</v>
+        <v>0.7446490850249603</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.7194445024828795</v>
+        <v>1.023809012183854</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.359609645175041</v>
+        <v>1.704942980490522</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>1.084241467211712</v>
+        <v>1.487472613475362</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.104465709728871</v>
+        <v>1.584092617425128</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.257629912464317</v>
+        <v>1.759022614622054</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>1.726951888068974</v>
+        <v>2.369632933252277</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.612699728323442</v>
+        <v>3.234652781215885</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.608157978482851</v>
+        <v>3.263365620326923</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>2.63977448994266</v>
+        <v>3.25354193679005</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>2.851009868246479</v>
+        <v>3.550126626730673</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>3.125484580728532</v>
+        <v>3.793761112009051</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>3.241039887313867</v>
+        <v>4.003369329615502</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.001247</t>
+          <t>X &lt; -0.001235</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1210</v>
+        <v>1242</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.407294481853015</v>
+        <v>-2.295643622720412</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-3.111426380917585</v>
+        <v>-2.702451504281079</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.695356305129081</v>
+        <v>-2.34813514760468</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.798484861541581</v>
+        <v>-1.492427933701727</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.089450159073415</v>
+        <v>-1.68753555087266</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.279550085863129</v>
+        <v>-0.8869977614473825</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.675469124149473</v>
+        <v>-1.360277681966508</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.044589659811642</v>
+        <v>-0.6193413273059392</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6725239655002468</v>
+        <v>-0.3305113717650272</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5363487324458305</v>
+        <v>-0.1611565918435787</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.8408014869781155</v>
+        <v>-0.4520752377380362</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.8716170061285879</v>
+        <v>-0.4068551004957399</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.4245311391004165</v>
+        <v>0.08726324062147484</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.2323868750511338</v>
+        <v>0.3217323167587622</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.2293731478383023</v>
+        <v>0.3636326412292945</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.1170798898071652</v>
+        <v>0.76403561419216</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.396385893325558</v>
+        <v>1.062407817109147</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.9527022142977657</v>
+        <v>1.734028941231529</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.416527479519615</v>
+        <v>2.1898427371625</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.520728661388461</v>
+        <v>2.243528136364681</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>1.226116377719954</v>
+        <v>1.917435203769145</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>1.563493556806719</v>
+        <v>2.244525296455855</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>1.755323641189598</v>
+        <v>2.488159781734232</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>2.092714528462189</v>
+        <v>2.939310281072856</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.001645</t>
+          <t>X &lt; 0.001653</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1418</v>
+        <v>1444</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.607186524371663</v>
+        <v>-1.64476613459783</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.46685198195722</v>
+        <v>-2.200135773759214</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.464204758565586</v>
+        <v>-2.175224901366029</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.296660226917496</v>
+        <v>-2.03950261693474</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.52427212228239</v>
+        <v>-2.176748170588709</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.384499380709627</v>
+        <v>-1.051626459473056</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.047369950595751</v>
+        <v>-1.708395885260408</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.582100070472158</v>
+        <v>-1.183440809996831</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.9371266534905445</v>
+        <v>-0.640574140976625</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.5816925410926217</v>
+        <v>-0.2609686514103515</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6602422078164523</v>
+        <v>-0.3345151029194326</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.8684697494873035</v>
+        <v>-0.4727844709453635</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.722238304354704</v>
+        <v>-0.2737070171651439</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.5907078719155407</v>
+        <v>-0.1070033192621551</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.5436325517245919</v>
+        <v>0.04071781752498538</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.01976749155875268</v>
+        <v>0.6020218363446475</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.08316276675907375</v>
+        <v>0.5672977178423224</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.2351277000826499</v>
+        <v>0.9185076652395026</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.6625846663384323</v>
+        <v>1.340438772053325</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.9199523380836041</v>
+        <v>1.555025217112309</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.6594936172261825</v>
+        <v>1.264205888622307</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.8657351029256901</v>
+        <v>1.603981126003127</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.7876005065219829</v>
+        <v>1.613058522641801</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.6412463915215554</v>
+        <v>1.63155003377269</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.004536</t>
+          <t>X &lt; 0.004541</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1715</v>
+        <v>1738</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.006220593455133</v>
+        <v>-0.9351768713770738</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.658126808653165</v>
+        <v>-1.322937233539236</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.370164699943203</v>
+        <v>-1.859062433348043</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.892258233155751</v>
+        <v>-1.387639049359279</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.602840151583983</v>
+        <v>-2.034105867910561</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.861948560549777</v>
+        <v>-1.30278972314165</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.079328114453979</v>
+        <v>-1.523489196603556</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.034883720930225</v>
+        <v>-1.483780116749678</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.554018588070548</v>
+        <v>-1.06865993768016</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.47959428993628</v>
+        <v>-0.9456993708661869</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.463788919411208</v>
+        <v>-0.9032173717701824</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.593168182225227</v>
+        <v>-1.007484564610223</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.609104141855234</v>
+        <v>-0.9736116045193626</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.480532668651477</v>
+        <v>-0.8197778888128937</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-1.497650325206401</v>
+        <v>-0.7552349702958807</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.078088578088575</v>
+        <v>-0.3088074592303869</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-1.153730656790984</v>
+        <v>-0.4126878709553949</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.9089210109618264</v>
+        <v>-0.1435041989774177</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.3433792803871469</v>
+        <v>0.4155875514308534</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.3896337035193511</v>
+        <v>0.3429827271044275</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.4077043470098616</v>
+        <v>0.3499207644945059</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.2739639763836479</v>
+        <v>0.5389742103738016</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.757506756612969</v>
+        <v>0.1270595294647165</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.8333390098362443</v>
+        <v>0.1716779867482217</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.007428</t>
+          <t>X &lt; 0.007429</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1990</v>
+        <v>2013</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.594938929799227</v>
+        <v>-1.538668291692979</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.454405739040894</v>
+        <v>-1.164771187576839</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.76728931445912</v>
+        <v>-1.303752678088415</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.304008274608336</v>
+        <v>-0.7793365047521306</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.162387452802783</v>
+        <v>-1.622640657067748</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.948257684914516</v>
+        <v>-1.339571858932985</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.742064645290448</v>
+        <v>-1.19219355370538</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.142807234106968</v>
+        <v>-1.596320346320347</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.873272570147549</v>
+        <v>-1.369185087429891</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.666032445861596</v>
+        <v>-1.123569915982564</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.664595182113104</v>
+        <v>-1.099350774394104</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.814835626672398</v>
+        <v>-1.177520030452705</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.805343645323653</v>
+        <v>-1.201142306633635</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.926020915344537</v>
+        <v>-1.250963669654048</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-1.931553771158029</v>
+        <v>-1.238673607094654</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-1.638371668492155</v>
+        <v>-0.9253854612908654</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-1.521284789405364</v>
+        <v>-0.880456349206348</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-1.174318264310891</v>
+        <v>-0.517308708336202</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-1.058828489812257</v>
+        <v>-0.3524496557936061</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-1.273589105547046</v>
+        <v>-0.5842917821631914</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.364328044597421</v>
+        <v>-0.5564981883058309</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-1.260121803222503</v>
+        <v>-0.4535816208917041</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.458680262626999</v>
+        <v>-0.6275204006735393</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-1.434010003287469</v>
+        <v>-0.5121681525866109</v>
       </c>
     </row>
     <row r="24">
@@ -7304,79 +7304,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2207</v>
+        <v>2227</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.300613090029621</v>
+        <v>-1.283118898132976</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.521774294492275</v>
+        <v>-1.281819150206587</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.764994312164127</v>
+        <v>-1.303863581514385</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.191941730142851</v>
+        <v>-0.7073144523278927</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.548050212045347</v>
+        <v>-1.003075050781241</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.516738361879071</v>
+        <v>-0.9112050712612572</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.541954788140885</v>
+        <v>-0.9439552449289508</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.840254081579083</v>
+        <v>-1.24887568833757</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.457535947851468</v>
+        <v>-0.8967315320167017</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.482224530229765</v>
+        <v>-0.8856081393436597</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.725084062860226</v>
+        <v>-1.106646667340215</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.752337371245162</v>
+        <v>-1.069327276520035</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.764047237974808</v>
+        <v>-1.107986210114305</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.004401436069358</v>
+        <v>-1.311377222220067</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-1.711888328036522</v>
+        <v>-0.9621414695759682</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-1.524925579927846</v>
+        <v>-0.7595818453751448</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.432495953664031</v>
+        <v>-0.7737761584454503</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.220451188947415</v>
+        <v>-0.5030728196608507</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-1.230906571264363</v>
+        <v>-0.4679827898245037</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.451484935130651</v>
+        <v>-0.7018268380390609</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-1.450798871317609</v>
+        <v>-0.6414686488368275</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.590776415645067</v>
+        <v>-0.7351397420712473</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-1.788284787289285</v>
+        <v>-0.9139801732885715</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-1.728185912284196</v>
+        <v>-0.7805181747037366</v>
       </c>
     </row>
     <row r="25">
@@ -7386,899 +7386,899 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2455</v>
+        <v>2473</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.011397275244263</v>
+        <v>-0.9068118387745798</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.243936335901566</v>
+        <v>-1.01075578603669</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.405545794820874</v>
+        <v>-0.9957045082352494</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9625629583843107</v>
+        <v>-0.518788607463506</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.194964438216076</v>
+        <v>-0.6109058603169544</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.026130630304927</v>
+        <v>-0.4316737534542341</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.329608393418141</v>
+        <v>-0.7203731191983849</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.706920137742337</v>
+        <v>-1.043118839729011</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.521107200447119</v>
+        <v>-0.8748348049440224</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.824772780254222</v>
+        <v>-1.146269673851819</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.649725226999998</v>
+        <v>-0.9951000345501484</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.418058854332472</v>
+        <v>-0.7067102376090091</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.258032449320133</v>
+        <v>-0.6109486020331545</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.130218755913816</v>
+        <v>-0.4556314124573788</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-1.178357986800592</v>
+        <v>-0.4517486676273492</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-1.112641255992216</v>
+        <v>-0.3747061500183335</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-1.205891455190098</v>
+        <v>-0.5592968119451172</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.9447297189950206</v>
+        <v>-0.2482745409969525</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-1.054173840307371</v>
+        <v>-0.3566533146582813</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-1.355331283694362</v>
+        <v>-0.602835399314003</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.264048978781673</v>
+        <v>-0.4601766763946671</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-1.478851303719964</v>
+        <v>-0.6327429613433679</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-1.547029173304168</v>
+        <v>-0.6886928403219486</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-1.517727982183978</v>
+        <v>-0.624981168026693</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.0161</t>
+          <t>X &lt; 0.01609</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2665</v>
+        <v>2688</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.258121871436437</v>
+        <v>-1.084216376909119</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.163705848467067</v>
+        <v>-0.9039181791990814</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.464313601647355</v>
+        <v>-1.029169212135947</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.076280170713957</v>
+        <v>-0.6763404492663057</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.428830405822922</v>
+        <v>-0.8945275085010636</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.370535030226485</v>
+        <v>-0.8283284726895985</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.263787861043518</v>
+        <v>-0.6767910236678034</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.558504127711657</v>
+        <v>-0.9980670840567143</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.458851494987528</v>
+        <v>-0.8865059201011221</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.613229538331282</v>
+        <v>-0.9941895288128606</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.355446510387914</v>
+        <v>-0.7590465023390891</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.865437968513703</v>
+        <v>-0.2196047179379832</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.882692682459485</v>
+        <v>-0.2959211677329705</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.8949043052453334</v>
+        <v>-0.2627653600271671</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-1.06670267203652</v>
+        <v>-0.3883334710402337</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.8993376882598483</v>
+        <v>-0.2351927175266866</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-1.086204896640744</v>
+        <v>-0.5246018862090267</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.9289714709224342</v>
+        <v>-0.3016619448052538</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.9906907703952612</v>
+        <v>-0.3623776584341982</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-1.119130882997801</v>
+        <v>-0.4603206979395082</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.002686576174995</v>
+        <v>-0.30002157313357</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-1.131458830343234</v>
+        <v>-0.3903938193659755</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-1.022478247299048</v>
+        <v>-0.2735460086988795</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-1.001264663077968</v>
+        <v>-0.2277445843515764</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.01899</t>
+          <t>X &lt; 0.01898</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2852</v>
+        <v>2876</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.049542765605885</v>
+        <v>-0.8856218971927206</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.052868170654435</v>
+        <v>-0.8026861354402897</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.219420893287541</v>
+        <v>-0.8305204833856052</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.182307286662194</v>
+        <v>-0.816977014773336</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.289973659699342</v>
+        <v>-0.8317132292162341</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.257999663917957</v>
+        <v>-0.7940055220168389</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.174243425674177</v>
+        <v>-0.6710514869201631</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.432973306088023</v>
+        <v>-0.9566435716556825</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.267351974159624</v>
+        <v>-0.8093729272717098</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.427561180468523</v>
+        <v>-0.9284022850672713</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.34315967139247</v>
+        <v>-0.8443272506725208</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.078459427293012</v>
+        <v>-0.5125247863095552</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.064009464731221</v>
+        <v>-0.5536378944080553</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9852557582802248</v>
+        <v>-0.4352441039344725</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.168592804607457</v>
+        <v>-0.5772062471870854</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.9731934731934757</v>
+        <v>-0.3768610353392603</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-1.156604662812953</v>
+        <v>-0.6338341137703836</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.9610790232318038</v>
+        <v>-0.3994452316941022</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.074642533526493</v>
+        <v>-0.5116584567500624</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-1.252496331087862</v>
+        <v>-0.6586965440679577</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-1.214288305958092</v>
+        <v>-0.5807225938258327</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-1.234551234612603</v>
+        <v>-0.5659597715580986</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-1.184861114309172</v>
+        <v>-0.5104048601351039</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-1.135004456620045</v>
+        <v>-0.443508045507933</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.02189</t>
+          <t>X &lt; 0.02187</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2959</v>
+        <v>2984</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.025152948442035</v>
+        <v>-0.8987956672526067</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.872638336471482</v>
+        <v>-0.6614543888310962</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.118340947389953</v>
+        <v>-0.7670213429107093</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.074566097408919</v>
+        <v>-0.7421544983358501</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.291131576375662</v>
+        <v>-0.8662329596585607</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.119223752429292</v>
+        <v>-0.6909632593750104</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.09978930543447</v>
+        <v>-0.6346413092154464</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.291967949970683</v>
+        <v>-0.8542568542568532</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.198014859029293</v>
+        <v>-0.7409995017584734</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.380252405447742</v>
+        <v>-0.8846209341216493</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.188064648385414</v>
+        <v>-0.693587868631198</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.9428844370239418</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.801023333774431</v>
+        <v>-0.2776785972767755</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.7666681117421206</v>
+        <v>-0.2058178224039864</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-0.8996634064647537</v>
+        <v>-0.3003731281994604</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.7571927566871963</v>
+        <v>-0.1537510499505714</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.871314713552394</v>
+        <v>-0.3382543463724588</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.7539860077974794</v>
+        <v>-0.183922287993262</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.8893245631745401</v>
+        <v>-0.3177158169028615</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-1.087695344881702</v>
+        <v>-0.4850854329568435</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-1.036650013092604</v>
+        <v>-0.3969111417921027</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-1.126406270423864</v>
+        <v>-0.4523184888894249</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-1.169905306766616</v>
+        <v>-0.4904231301434692</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-1.192179016654407</v>
+        <v>-0.498833247698947</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.02478</t>
+          <t>X &lt; 0.02476</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3031</v>
+        <v>3055</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.9230998966670683</v>
+        <v>-0.8135818938026063</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.9458171643202675</v>
+        <v>-0.7498595306652973</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.02307939593728</v>
+        <v>-0.6869207736384269</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.8660266754374248</v>
+        <v>-0.5461989702053245</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.183698928212621</v>
+        <v>-0.7713051158692963</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.142590830496815</v>
+        <v>-0.7265941317753075</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.141858139572136</v>
+        <v>-0.689961410848241</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.2704451958083</v>
+        <v>-0.8464418102972431</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.177725204898344</v>
+        <v>-0.7328426025532053</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.373922861556004</v>
+        <v>-0.891555067032229</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.31120254691448</v>
+        <v>-0.8290231735580278</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.012734813425112</v>
+        <v>-0.4677110552377926</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.8022187195851984</v>
+        <v>-0.29197727075627</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.9054473352629557</v>
+        <v>-0.3580417918218828</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-0.8535575758504947</v>
+        <v>-0.270440360793522</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-0.7332705136258895</v>
+        <v>-0.1468439598061764</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.7491045609206566</v>
+        <v>-0.231500381014591</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.6370027196164614</v>
+        <v>-0.08379543588141303</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.6980970264092363</v>
+        <v>-0.1441163224602704</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.7884194317943738</v>
+        <v>-0.2044926466432386</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.6854424296259936</v>
+        <v>-0.0660463938972029</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.8077233328887203</v>
+        <v>-0.1545161396425598</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.8765479652562433</v>
+        <v>-0.2187002048713822</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.8999971478522468</v>
+        <v>-0.2305941284245208</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.02767</t>
+          <t>X &lt; 0.02764</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3088</v>
+        <v>3113</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.860390668558928</v>
+        <v>-0.7365042791310117</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.8244985098525248</v>
+        <v>-0.6146898636549807</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.8945049743219471</v>
+        <v>-0.5441849088458071</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.7211915748501099</v>
+        <v>-0.3850712944536241</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.039149602786694</v>
+        <v>-0.6110602906927838</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.9631224901439097</v>
+        <v>-0.5322805883312682</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.9765164884379445</v>
+        <v>-0.5109977527012717</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.075581395348834</v>
+        <v>-0.6382133898912414</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.9837397177847578</v>
+        <v>-0.5242819087671222</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.125997639309439</v>
+        <v>-0.6307900569970712</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.123808035119083</v>
+        <v>-0.628263427107143</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.9326673926921814</v>
+        <v>-0.3747263796590516</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.7789243184517858</v>
+        <v>-0.2549347583134036</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.948871517235645</v>
+        <v>-0.3884116363527284</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.9100638722663703</v>
+        <v>-0.3151203292812923</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.8456659619450235</v>
+        <v>-0.2474860039537319</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.8637110372075583</v>
+        <v>-0.3325320512820511</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.7233222959513412</v>
+        <v>-0.1580156911400081</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.6823468114012314</v>
+        <v>-0.1170334345691799</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.8322376713497093</v>
+        <v>-0.2364489234926168</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.7088267121891576</v>
+        <v>-0.07905967331917907</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.7978961567453879</v>
+        <v>-0.1351830929969822</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.8927557875484666</v>
+        <v>-0.2257406942001055</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.9171771342792141</v>
+        <v>-0.2404361772110093</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.03056</t>
+          <t>X &lt; 0.03053</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3145</v>
+        <v>3169</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.6736753962602577</v>
+        <v>-0.5664362519201234</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.6759712436415839</v>
+        <v>-0.4823599505271048</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.8653169974520623</v>
+        <v>-0.5291210826339494</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.771146743288682</v>
+        <v>-0.4459152204252135</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.9630195640543704</v>
+        <v>-0.5473235127691893</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.8849691642710127</v>
+        <v>-0.4671505391865907</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.9436381352889924</v>
+        <v>-0.4915837429260819</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.109194176114414</v>
+        <v>-0.6847121132835525</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.9549802893834993</v>
+        <v>-0.5077349797486335</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.045297322202494</v>
+        <v>-0.5635355817964864</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.069840684294135</v>
+        <v>-0.587667995269463</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.9505181493312946</v>
+        <v>-0.4063239904732683</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.8198427062059608</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.9907266479421324</v>
+        <v>-0.4438003408644207</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.9328220019760352</v>
+        <v>-0.3523719498678872</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.8588501571374962</v>
+        <v>-0.2760475863864187</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.8155430406845952</v>
+        <v>-0.2984624265323319</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.8065189171284359</v>
+        <v>-0.2553414542429735</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.6989126359205002</v>
+        <v>-0.148317120611928</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.9062257174120987</v>
+        <v>-0.3248795289753375</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.8266627710508772</v>
+        <v>-0.2118405690580545</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.8519775595916883</v>
+        <v>-0.2052705073808525</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.8765898998148458</v>
+        <v>-0.226855026745298</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.8701413755701779</v>
+        <v>-0.2126006678389274</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.03345</t>
+          <t>X &lt; 0.03342</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3202</v>
+        <v>3227</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.524568043664523</v>
+        <v>-0.4041651896490634</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.5016785023525046</v>
+        <v>-0.2951509845593137</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.6820264544522345</v>
+        <v>-0.3326365327011231</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6331146711307483</v>
+        <v>-0.2922359624508317</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.9206302345475805</v>
+        <v>-0.4891300871767683</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.9027504592519904</v>
+        <v>-0.4692004694937921</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.9119241599775592</v>
+        <v>-0.4457605785424477</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.04839059360863</v>
+        <v>-0.6100385378831348</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.8961551397630103</v>
+        <v>-0.4339158532710812</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.998552178027829</v>
+        <v>-0.5029409948676786</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.048891149330466</v>
+        <v>-0.5526135609902241</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9988496196428187</v>
+        <v>-0.4412061573682209</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.8281857138779785</v>
+        <v>-0.3031379535644234</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.9376965093769627</v>
+        <v>-0.3788856138410566</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.8302003662584596</v>
+        <v>-0.2394976697234199</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.778108184650236</v>
+        <v>-0.1853551627211587</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.8314109281141384</v>
+        <v>-0.3019673778602368</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.8555869800716849</v>
+        <v>-0.2929360435057617</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.6837078012582367</v>
+        <v>-0.1221141222402551</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.8216252927161918</v>
+        <v>-0.2297465285928766</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.6594962368672768</v>
+        <v>-0.03601806643251848</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.7792907726987579</v>
+        <v>-0.123769673181485</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.8609993824220439</v>
+        <v>-0.2025214158719777</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.824780219138745</v>
+        <v>-0.1604413615440095</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.03634</t>
+          <t>X &lt; 0.03631</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3243</v>
+        <v>3268</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.487142275709985</v>
+        <v>-0.3673000796754664</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4074768979992385</v>
+        <v>-0.2019074239968432</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.5423194314010118</v>
+        <v>-0.1937293379468557</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.5335844151313935</v>
+        <v>-0.1915909350738829</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.7910201934526953</v>
+        <v>-0.3590127688363083</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.8323056579964287</v>
+        <v>-0.3981984034846633</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.820376085565087</v>
+        <v>-0.3545114488999843</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.9892819169812341</v>
+        <v>-0.5509681819060646</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.8384220219055933</v>
+        <v>-0.3754293761901764</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.9492420049142822</v>
+        <v>-0.4535189888475415</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.9647684291268774</v>
+        <v>-0.4686753608780947</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.918842507899555</v>
+        <v>-0.3620922333175898</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.8566502855292271</v>
+        <v>-0.3311579908579176</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.9675760075238955</v>
+        <v>-0.4090715945404924</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.9004922557236057</v>
+        <v>-0.3104872577914364</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.8723423095923835</v>
+        <v>-0.280544191449593</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.8959217989821369</v>
+        <v>-0.366491730279904</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.9211356353648128</v>
+        <v>-0.3592572979940201</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.7795092423791843</v>
+        <v>-0.2184619788407645</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.8825577797511031</v>
+        <v>-0.2915239007645098</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.7601553464109543</v>
+        <v>-0.137926856787395</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.8177923375762504</v>
+        <v>-0.1643897039992908</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.833358834276865</v>
+        <v>-0.1779296952930665</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.8293834167624823</v>
+        <v>-0.1690039828478191</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.03923</t>
+          <t>X &lt; 0.0392</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3283</v>
+        <v>3308</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2833153529963965</v>
+        <v>-0.1652625732021633</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.2388614306925163</v>
+        <v>-0.03477981006071218</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2683645104495724</v>
+        <v>0.07843048989623469</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2682863535525115</v>
+        <v>0.0735047508703417</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.496306289871228</v>
+        <v>-0.06508040016515793</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.5044427753391574</v>
+        <v>-0.07175289530824358</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.5625214657472739</v>
+        <v>-0.09820859129936821</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.6720500222054611</v>
+        <v>-0.2357249649668489</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.5830632855990814</v>
+        <v>-0.1208509659389918</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.7321691251394142</v>
+        <v>-0.2376112278715539</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.7441152958523887</v>
+        <v>-0.2492410828209941</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.6717148252635283</v>
+        <v>-0.1170878254421837</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.5934834541034064</v>
+        <v>-0.06975950343702664</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.6449323948489507</v>
+        <v>-0.08937034033919389</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.6169392986873419</v>
+        <v>-0.03025234290010559</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.6122068451147769</v>
+        <v>-0.02397192040205454</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.6978390306866018</v>
+        <v>-0.1703902714932113</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.7543654216236249</v>
+        <v>-0.1949629122426799</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.6117848407635194</v>
+        <v>-0.05322857386048696</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.6808317053957893</v>
+        <v>-0.09257335566216085</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.6577586141061218</v>
+        <v>-0.03823415259993368</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.715586156893167</v>
+        <v>-0.06525539687694959</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.6971380815633381</v>
+        <v>-0.04543603085129888</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.7550134365365579</v>
+        <v>-0.09899825510645144</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.04213</t>
+          <t>X &lt; 0.04208</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3307</v>
+        <v>3331</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.3375438101286576</v>
+        <v>-0.23314551165263</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.2958401929472956</v>
+        <v>-0.07544081105574207</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.215325653120459</v>
+        <v>0.1477031218834526</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2504322673009014</v>
+        <v>0.1089240000037819</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.4491583487739277</v>
+        <v>-0.0007402434195782348</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.4558723945249596</v>
+        <v>-0.00626992563851303</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.4890065330265685</v>
+        <v>-0.03798635111108695</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.5696379707325292</v>
+        <v>-0.1467576011944161</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.4508612212607446</v>
+        <v>-0.001880843556612888</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.6646581881758351</v>
+        <v>-0.1830670332151101</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.6745165123689389</v>
+        <v>-0.1927281572451705</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.574504712522284</v>
+        <v>-0.003543609691959659</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.5350726880769443</v>
+        <v>0.005897960101421518</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.4972881973153562</v>
+        <v>0.04459820470160736</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.4139029507473211</v>
+        <v>0.1585319817276982</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.3746743452625765</v>
+        <v>0.1986411933961634</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.4605845351596614</v>
+        <v>0.05258263431196042</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.5173893109483885</v>
+        <v>0.02733028401031135</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.404399178363569</v>
+        <v>0.1696326783390845</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.4413261970723141</v>
+        <v>0.1321059713410051</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4222819144575212</v>
+        <v>0.1822231150525369</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.5103895918312276</v>
+        <v>0.1249328062333888</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.4900219772460446</v>
+        <v>0.1763661986533762</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.5782039090120321</v>
+        <v>0.0920998424614865</v>
       </c>
     </row>
   </sheetData>
